--- a/laptop_tgdd_all.xlsx
+++ b/laptop_tgdd_all.xlsx
@@ -492,229 +492,229 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002MVN (Ultra 7 355, 32GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Asus Vivobook Go 14 E1404FA - EB012W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>55990000</v>
+        <v>18790000</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>64990000</v>
+        <v>22990000</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.95 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-7-355-83tc002mvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb012w</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:58:04</t>
+          <t>2026-09-14 14:18:06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 - 83QM0075VN (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
+          <t>Laptop Asus Vivobook Go 14 E1404FA - EB1832W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>40990000</v>
+        <v>18790000</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>46990000</v>
+        <v>22990000</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe 600nits (peak) Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 70 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 04/2026 | Kích thước:: Dài 221 mm - Rộng 312 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-14iph11-ultra-7-355-83qm0075vn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb1832w</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:58:18</t>
+          <t>2026-09-14 14:18:19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 - 83QM0076VN (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ893W (Core 3 304, 8GB, 512GB, Full HD, Win 11)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>40990000</v>
+        <v>17990000</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>46990000</v>
+        <v>22990000</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.00 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Khoảng 13 TOPS (NPU); tổng nền tảng AI của Intel đạt khoảng 99 TOPS (CPU + GPU + NPU) | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: 4 Xe-Cores | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7467 MT/s | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB PCIe 4.0 NVMe SSD | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: OLED Chuẩn DisplayHDR True Black 600 Low Blue Light Eyesafe Dolby Vision | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 2 x Thunderbolt 4 USB-C HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Chốt khóa webcam FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hệ thống quạt kép (Dual Fan) | Tính năng khác:: TPM 2.0 | Thông tin Pin:: 70 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 221 mm - Rộng 312 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Vỏ hợp kim Nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 3 Wildcat Lake - 304 | Số nhân:: 5 | Số luồng:: 5 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.30 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 15 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits Chứng nhận TÜV Rheinland | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.7 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-14iph11-ultra-7-355-83qm0076vn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-15-x1504ma-core-3-304-bq893w</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:58:31</t>
+          <t>2026-09-14 14:18:32</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK0015VN (Ultra 7 355, 32GB, 1TB, WQXGA+ 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Asus Vivobook S 16 S3607VA - RP155W (Core 5 210H, 16GB, 512GB, Full HD+ 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>62990000</v>
+        <v>26990000</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>72990000</v>
+        <v>34990000</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-23%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe 4.0x4 NVMe (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: 500 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.6 mm - Rộng 213.8 mm - Dày 13.9 mm - 0.975 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare LED Backlit | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 259.6 mm - Dày 15.9 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-7-355-83qk0015vn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-s-16-s3607va-core-5-210h-rp155w</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:58:46</t>
+          <t>2026-09-14 14:18:45</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK006GVN (Ultra 7 355, 32GB, 1TB, WQXGA+ 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Asus Vivobook S14 S3407VA - LY256W (Core 7 240H, 16GB, 512GB, WUXGA OLED, Win11)</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>64990000</v>
+        <v>26990000</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>66990000</v>
+        <v>29990000</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe 4.0x4 NVMe (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Eyesafe DisplayHDR True Black 1000 500 nits Corning Gorilla Glass 3 Dolby Vision PureSight Pro Flicker Free 1100 nits (peak) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.6 mm - Rộng 213.8 mm - Dày 13.9 mm - 0.975 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 17.9 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-7-355-83qk006gvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-s14-s3407va-core-7-240h-ly256w</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:58:59</t>
+          <t>2026-09-14 14:18:59</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK009PVN (Ultra X9 378H, 32GB, 1TB, WQXGA+ 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop Asus Zenbook 14 UM3406GA - QD075W (R7 AI 445, 16GB, 512GB, WUXGA OLED, Win11)</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>68990000</v>
+        <v>34590000</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>79990000</v>
+        <v>39990000</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -723,619 +723,607 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra X9 - 378H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.00 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 32 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 9600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe® 4.0x4 NVMe® (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Eyesafe 500 nits typical DisplayHDR True Black 1000 Corning Gorilla Glass 3 500 nits Glossy Dolby Vision PureSight Pro Flicker Free 1100 nits (peak) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 18/05/2026 | Kích thước:: Dài 213.8 mm - Rộng 312.6 mm - Dày 13.9 mm - 0.975 kg</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.0 GHz | NPU:: AMD XDNA | Card màn hình:: Card tích hợp | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 70% Less harmful blue light 400 nits 600 nits (Khi bật HDR) | Cổng giao tiếp:: 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 75 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.01 mm - Rộng 31.24 mm - Dày 1.49 mm - 1.2 kg | Chất liệu:: Nhôm nguyên khối</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-x9-378h-83qk009pvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-zenbook-14-um3406ga-r7-ai-445-qd075w</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:59:14</t>
+          <t>2026-09-14 14:19:13</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 Black Edition A13VEO - 2610VN (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Dell 14 DC14250 - DC14250-C3U085W11SLU-2Y (Core 3 100U, 8GB, 512GB, Full HD+, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>27890000</v>
+        <v>21490000</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>31990000</v>
+        <v>22590000</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell, 53.5Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 250.3 mm - Dày 22.9 mm - 1,.98 | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-black-edition-a13veo-i5-13420h-2610vn</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-3-100u-dc14250-c3u085w11slu-2y</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:59:28</t>
+          <t>2026-09-14 14:19:27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 Black Edition A13VEO - 2608VN (i7 13620H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Dell 14 DC14250 - DC4C5375W1-2Y (Core 5 120U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>29890000</v>
+        <v>28990000</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>33990000</v>
+        <v>32090000</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 1.8 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell, 53.5Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 250.3 mm - Dày 22.9 mm - 1,.98 | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226 mm - Dày 18 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-black-edition-a13veo-i7-13620h-2608vn</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-5-120u-dc4c5375w1-2y</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:59:42</t>
+          <t>2026-09-14 14:19:40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 C13WEO - 418VN (i5 13420H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Dell 14 DC14250 - 71100515 (Core 7 150U, 16GB, 512GB, Full HD+ 120Hz, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>30990000</v>
+        <v>31990000</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>34990000</v>
+        <v>35490000</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 70 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 1.982 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 320 mm - Rộng 215.97 mm - Dày 18.02 mm - 1.83 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-c13weo-i5-13420h-418vn</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-71100515</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:59:57</t>
+          <t>2026-09-14 14:19:53</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 Max C13WE - 422VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Dell 14 DC14250 - DC14250-C7U161W11SLU-2Y (Core 7 150U, 16GB, 1TB, Full HD+ ,OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>41590000</v>
+        <v>34990000</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>42990000</v>
+        <v>37990000</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x SuperSpeed USB Type-A LAN (RJ45) HDMI 2.1 2 x USB 3.2 1 x USB Type-C 3.2 (hỗ trợ Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: 3 ống đồng Cooler Boost 2 quạt | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 2 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 PCIe Gen 4 x 4 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (M.2 2230)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-max-c13we-422vn-i7-13620h</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-dc14250-c7u161w11slu-2y</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00:10</t>
+          <t>2026-09-14 14:20:07</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 Max C13WF - 421VN (i7 13620H, 16GB, 512GB, RTX 5060 8GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Dell 15 DC15250 - 71100520 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>43590000</v>
+        <v>21490000</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>44990000</v>
+        <v>22590000</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x SuperSpeed USB Type-A LAN (RJ45) HDMI 2.1 2 x USB 3.2 1 x USB Type-C 3.2 (hỗ trợ Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: 3 ống đồng Cooler Boost 2 quạt | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 2 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort 1.4, Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Bluetooth 5.0 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-max-c13wf-421vn-i7-13620h</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-71100520</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00:23</t>
+          <t>2026-09-14 14:20:21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Gaming Cyborg 15 C13WEO-417VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Dell 15 DC15250 - CPH993 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>34590000</v>
+        <v>21490000</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>36990000</v>
+        <v>22590000</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - Intel UHD Graphics (tích hợp) + NVIDIA GeForce RTX 5050 GPU, 8GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB Type-A 1 x Headphone/ Microphone combo audio jack 1 x USB Type C (chỉ hỗ trợ Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: DTS Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.98 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: Đang cập nhật | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 70% Less harmful blue light 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 16.96 mm đến 18.99 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-c13weo-417vn-i7-13620h</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-cph993</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00:36</t>
+          <t>2026-09-14 14:20:35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14S G3MG-003VN (Core 5 320, 16GB, 1TB, Full HD+ 120Hz, Win11)</t>
+          <t>Laptop Dell 15 DC15250 - DC5C3259W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>27990000</v>
+        <v>21490000</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>31490000</v>
+        <v>22590000</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: SSD 1TB, chuẩn M.2 2280 NVMe PCIe Gen4, tối đa hỗ trợ 2TB | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 50% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 2 x USB 3.2 gen 1 Type-A LAN (RJ45) HDMI 2.1 2 x USB Type-C 3.2 Gen 2 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD card reader | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: DTS | Tản nhiệt:: 2 ống đồng 1 x Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.39 mm - Rộng 31.59 mm - Dày 1.11 ~ 1.79 - 1.45 kg | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-modern-14s-g3mg-003vn-core-5-320</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3259w1-2y</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00:53</t>
+          <t>2026-09-14 14:20:49</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1264VN (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Dell 15 DC15250 - DC5C3851W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>19990000</v>
+        <v>21490000</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>22390000</v>
+        <v>22590000</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core thế hệ 12 - 120U | Số nhân:: Hãng không công bố | Số luồng:: 12 | Tốc độ CPU:: 1.45 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (2280) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: Hãng không công bố | Cổng giao tiếp:: 3 x USB 3.2 Gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell, 46.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.7 kg | Chất liệu:: Plastic (nhựa dẻo)</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x Headphone/ Microphone combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 2 x USB 2.0 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 235 mm - Rộng 358.5 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-modern-15-f1mg-1264vn-core-5-120u</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3851w1-2y</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:01:07</t>
+          <t>2026-09-14 14:21:03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Laptop SingPC M16-i382 (i3 1215U, 8GB, 256GB, WUXGA, Win11 Pro)</t>
+          <t>Laptop Dell 15 DC15255 - DC5R5973W1-2Y (R5 7530U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>13490000</v>
+        <v>23990000</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>15190000</v>
+        <v>25690000</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i3 Alder Lake - 1215U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.2GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 256 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 7530U | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/microphone combo 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/singpc-m16-i382-i3-1215u</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r5-7530u-dc5r5973w1-2y</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:01:20</t>
+          <t>2026-09-14 14:21:16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Laptop SingPC M16-i595 (i5 1235U, 16GB, 512GB, WUXGA, Win11 Pro)</t>
+          <t>Laptop Dell 15 DC15255 - X9YM42 (R7 7730U, 16GB, 1TB, Full HD 120Hz, OfficeH24+36, Win11)</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>17390000</v>
+        <v>29890000</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>19990000</v>
+        <v>30590000</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Alder Lake - 1235U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 72% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 8 x 2.0 GHz | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Bluetooth 5.0 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.635 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/singpc-m16-i595-i5-1235u</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r7-7730u-x9ym42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:01:33</t>
+          <t>2026-09-14 14:21:29</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook 7 14 fr0033TU - C1MN2PA (Ultra 5 225U, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>27490000</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>28990000</v>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-5%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
+          <t>Laptop Dell 16 DC16250 - 71100513 (Core 5 120U, 16GB, 1TB, Full HD+, OfficeH24+365B, Win11)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 3.80 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Công suất đồ hoạ - TGP:: 15 - 25W | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 2600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Thunderbolt 4 with USB Type - C (hỗ trợ truyền dữ liệu, Power Delivery 3.1, DisplayPort 2.1,  HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB 3.2 gen 2 Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Poly Studio Dual speakers HP Audio Boost DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 4-cell, 64 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.65 mm - Rộng 31.4 mm - Dày 1.49 mm - 1.41 kg | Chất liệu:: Khung và mặt lưng kim loại, nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits eDP Wide View Angle | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2W x 2 Realtek ALC3254 Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 05/2025 | Kích thước:: Dài 357.3 mm - Rộng 250.6 mm - Dày 18.23 mm - 2 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-7-14-fr0033tu-ultra-5-225u-c1mn2pa</t>
+          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-5-120u-71100513</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:46:06</t>
+          <t>2026-09-14 14:21:42</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook X Flip 14 fk0082AU - BZ7N8PA (R7 AI 350, 32GB, 1TB, 2K, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Dell Pro 15 Essential PV15250 - PV15250-100U-8512W-2Y (Core 3 100U, 8GB, 512GB, Full HD, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>39890000</v>
+        <v>22490000</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>40890000</v>
+        <v>23990000</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: 2K (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Corning Gorilla Glass 3 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB Type-C (hỗ trợ truyền dữ liệu, DisplayPort 2.1, Power delivery 3.1, HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E MT7922 Bluetooth 5.3 | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ | Thông tin Pin:: 3-cell Li-Po, 59 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 218.5 mm - Dày 14.6 mm - 1.39 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Rộng 358.5 mm - Dày 17.5 mm | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-x-flip-14-fk0082au-r7-ai-350-bz7n8pa</t>
+          <t>https://www.thegioididong.com/laptop/dell-pro-15-essential-pv15250-core-3-100u-pv15250-100u-8512w-2y</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:46:19</t>
+          <t>2026-09-14 14:21:56</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming Legion 5 15AHP11 - 83Q7001HVN (R7 250, 16GB, 512GB, RTX 5050 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
+          <t>Laptop HP Gaming HyperX Omen 15 ga0092TX - D72D8PA (i5 14450HX, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>52990000</v>
+        <v>45590000</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>56990000</v>
+        <v>46990000</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Boost Clock 2662MHz, TGP 115W, 440 AI TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: 2.5K | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: DisplayHDR True Black 1000 | Cổng giao tiếp:: 1x Ethernet 2 x USB Type-C (USB4 40Gbps) hỗ trợ USB PD 65 - 100W và DisplayPort 1.4 1 x Headphone/ Microphone combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) 2×2 Bluetooth 6.0 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 244.5 mm - Rộng 344 mm - Dày 19~20 - 1.87 kg | Chất liệu:: Mặt trên: nhôm + Mặt dưới: nhựa PC-ABS</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 421 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.37 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15ahp11-r7-250-83q7001hvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-gaming-hyperx-omen-15-ga0092tx-i5-14450hx-d72d8pa</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:46:32</t>
+          <t>2026-09-14 14:22:08</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002NVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop HP HyperX Omen 15 ga0091TX - D72D7PA (i5 14450HX, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>22990000</v>
+        <v>48590000</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>29990000</v>
+        <v>49990000</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-23%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3840 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 614 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.363 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002nvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-hyperx-omen-15-ga0091tx-i5-14450h-d72d7pa</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1345,40 +1333,40 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:46:45</t>
+          <t>2026-09-14 14:22:21</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002PVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002MVN (Ultra 7 355, 32GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>19190000</v>
+        <v>55990000</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>25990000</v>
+        <v>64990000</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.95 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002pvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-7-355-83tc002mvn</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1388,169 +1376,169 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:46:58</t>
+          <t>2026-09-14 16:03:16</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00A8VN (Core 3 304, 8GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 - 83QM0075VN (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>17490000</v>
+        <v>40990000</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>23990000</v>
+        <v>46990000</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-27%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core™ 3 - 304 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz (P-core), Turbo tối đa 4.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 2242 PCIe 4.0x4 NVMe | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 × USB-C (USB 5 Gbps), hỗ trợ USB PD 45–65W và DisplayPort 1.2 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Optimized with Dolby Audio 2W x 2 High Definition (HD) Audio Stereo speakers | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 240 mm - Rộng 343 mm - Dày 17 - 18 - 1.59 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe 600nits (peak) Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 70 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 04/2026 | Kích thước:: Dài 221 mm - Rộng 312 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-3-304-83rr00a8vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-14iph11-ultra-7-355-83qm0075vn</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:47:11</t>
+          <t>2026-09-14 16:03:30</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00AAVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 - 83QM0076VN (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>22990000</v>
+        <v>40990000</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>29990000</v>
+        <v>46990000</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-23%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.00 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Khoảng 13 TOPS (NPU); tổng nền tảng AI của Intel đạt khoảng 99 TOPS (CPU + GPU + NPU) | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: 4 Xe-Cores | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7467 MT/s | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB PCIe 4.0 NVMe SSD | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: OLED Chuẩn DisplayHDR True Black 600 Low Blue Light Eyesafe Dolby Vision | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 2 x Thunderbolt 4 USB-C HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Chốt khóa webcam FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hệ thống quạt kép (Dual Fan) | Tính năng khác:: TPM 2.0 | Thông tin Pin:: 70 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 221 mm - Rộng 312 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Vỏ hợp kim Nhôm</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00aavn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-14iph11-ultra-7-355-83qm0076vn</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:47:24</t>
+          <t>2026-09-14 16:03:44</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Ideapad Slim 3 15IWC11 - 83RR00CVVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK0015VN (Ultra 7 355, 32GB, 1TB, WQXGA+ 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>19190000</v>
+        <v>62990000</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>25990000</v>
+        <v>72990000</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe 4.0x4 NVMe (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: 500 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.6 mm - Rộng 213.8 mm - Dày 13.9 mm - 0.975 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00cvvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-7-355-83qk0015vn</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:47:37</t>
+          <t>2026-09-14 16:03:58</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US0040VN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK006GVN (Ultra 7 355, 32GB, 1TB, WQXGA+ 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>23690000</v>
+        <v>64990000</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>31990000</v>
+        <v>66990000</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 x USB-C (USB 5Gbps), with USB PD 45-65W and DisplayPort 1.2 1x Headphone / microphone combo jack (3.5 mm) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 18 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe 4.0x4 NVMe (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Eyesafe DisplayHDR True Black 1000 500 nits Corning Gorilla Glass 3 Dolby Vision PureSight Pro Flicker Free 1100 nits (peak) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.6 mm - Rộng 213.8 mm - Dày 13.9 mm - 0.975 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-5-322-83us0040vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-7-355-83qk006gvn</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1560,68 +1548,68 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:47:51</t>
+          <t>2026-09-14 16:04:12</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US003YVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK009PVN (Ultra X9 378H, 32GB, 1TB, WQXGA+ 120Hz, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>28990000</v>
+        <v>68990000</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>36990000</v>
+        <v>79990000</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-22%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra X9 - 378H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.00 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 32 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 9600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe® 4.0x4 NVMe® (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Eyesafe 500 nits typical DisplayHDR True Black 1000 Corning Gorilla Glass 3 500 nits Glossy Dolby Vision PureSight Pro Flicker Free 1100 nits (peak) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 18/05/2026 | Kích thước:: Dài 213.8 mm - Rộng 312.6 mm - Dày 13.9 mm - 0.975 kg</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us003yvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-x9-378h-83qk009pvn</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:48:04</t>
+          <t>2026-09-14 16:04:26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14IPH11 - 83S5004FVN (Ultra 7 355, 16GB, 512GB, WUXGA OLED, Win11)</t>
+          <t>Laptop MSI Cyborg 15 Black Edition A13VEO - 2610VN (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>34990000</v>
+        <v>27890000</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>37990000</v>
+        <v>31990000</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1631,40 +1619,40 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell, 53.5Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 250.3 mm - Dày 22.9 mm - 1,.98 | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14iph11-ultra-7-355-83s5004fvn</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-black-edition-a13veo-i5-13420h-2610vn</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:48:18</t>
+          <t>2026-09-14 16:04:39</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkBook 14 G9 - 21V0005PVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop MSI Cyborg 15 Black Edition A13VEO - 2608VN (i7 13620H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>33390000</v>
+        <v>29890000</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>35290000</v>
+        <v>33990000</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1674,83 +1662,83 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 1.8 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell, 53.5Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 250.3 mm - Dày 22.9 mm - 1,.98 | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-g9-r7-250-21v0005pvn</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-black-edition-a13veo-i7-13620h-2608vn</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:48:31</t>
+          <t>2026-09-14 16:04:52</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkBook 14 Gen 9 IRL - 21UY008TVN (i5 13420H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop MSI Cyborg 15 C13WEO - 418VN (i5 13420H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>31190000</v>
+        <v>30990000</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>32890000</v>
+        <v>34990000</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 70 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 1.982 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-gen-9-irl-i5-13420h-21uy008tvn</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-c13weo-i5-13420h-418vn</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:48:44</t>
+          <t>2026-09-14 16:05:06</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkBook 16 G9 - 21UT005MVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop MSI Cyborg 15 Max C13WE - 422VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>30190000</v>
+        <v>41590000</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>31590000</v>
+        <v>42990000</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1760,227 +1748,227 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356 mm - Rộng 253.5 mm - Dày 17.5 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x SuperSpeed USB Type-A LAN (RJ45) HDMI 2.1 2 x USB 3.2 1 x USB Type-C 3.2 (hỗ trợ Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: 3 ống đồng Cooler Boost 2 quạt | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 2 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-16-g9-r7-250-21ut005mvn</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-max-c13we-422vn-i7-13620h</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:48:57</t>
+          <t>2026-09-14 16:05:19</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad E14 - 21T90025VN (Gen 7 Core 7 240H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop MSI Cyborg 15 Max C13WF - 421VN (i7 13620H, 16GB, 512GB, RTX 5060 8GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>34190000</v>
+        <v>43590000</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>35590000</v>
+        <v>44990000</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: P-core 2.5/ 5.2 GHz, E-core 1.8/ 4.0 GHz | Card màn hình:: Card tích hợp - Integrated Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare 300 nits | Cổng giao tiếp:: 1x USB-A (USB 10Gbps / USB 3.2 Gen 2), Always On 1x Headphone / microphone combo jack (3.5 mm) 1x USB-C® (Thunderbolt™ 4 / USB4® 40 Gbps), with USB PD 15-65W and DisplayPort™ 2.1 1x HDMI® 2.1, up to 4K/6 0Hz 1x Ethernet (RJ-45) 1x USB-A (USB 5 Gbps / USB 3.2 Gen 1) | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: FHD 1080p + IR Hybrid with Privacy Shutter | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Stereo speakers, 2W x2, Dolby Atmos®, audio by HARMAN 2x, Array | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ Discrete TPM 2.0 Enabled | Thông tin Pin:: 3-cell, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 04/2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 10.1/15.25 (front/rear), 19.7 (maximum) mm - 1.34 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x SuperSpeed USB Type-A LAN (RJ45) HDMI 2.1 2 x USB 3.2 1 x USB Type-C 3.2 (hỗ trợ Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: 3 ống đồng Cooler Boost 2 quạt | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 2 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-core-7-240h-21t90025vn</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-max-c13wf-421vn-i7-13620h</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:49:10</t>
+          <t>2026-09-14 16:05:34</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad E14 - 21SX002YVN (Gen 7 Ultra 255H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop MSI Gaming Cyborg 15 C13WEO-417VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>39190000</v>
+        <v>34590000</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>40590000</v>
+        <v>36990000</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.10 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140T | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 1x USB-A (USB 10Gbps / USB 3.2 Gen 2), Always On 1x HDMI® 2.1, up to 4K/60 Hz 1x Headphone / microphone combo jack (3.5 mm) 1x USB-C® (Thunderbolt™ 4 / USB4® 40 Gbps), with USB PD 15-65W and DisplayPort™ 2.1 1x Ethernet (RJ-45) 1x USB-A (USB 5 Gbps / USB 3.2 Gen 1) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD 1080p + IR Hybrid with Privacy Shutter | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Stereo speakers, 2W x2, Dolby Atmos®, audio by HARMAN 2x, Array | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 04/2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 10.1/15.25 (front/rear), 19.7 (maximum) mm - 1.34 kg | Chất liệu:: Vỏ kim loại - Nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - Intel UHD Graphics (tích hợp) + NVIDIA GeForce RTX 5050 GPU, 8GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB Type-A 1 x Headphone/ Microphone combo audio jack 1 x USB Type C (chỉ hỗ trợ Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: DTS Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.98 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-255h-21sx002yvn</t>
+          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-c13weo-417vn-i7-13620h</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:49:24</t>
+          <t>2026-09-14 16:05:49</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX005NVN (Ultra 5 225U, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop MSI Modern 14S G3MG-003VN (Core 5 320, 16GB, 1TB, Full HD+ 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>36490000</v>
+        <v>27990000</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>38390000</v>
+        <v>31490000</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4 với USB Power Delivery và DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: SSD 1TB, chuẩn M.2 2280 NVMe PCIe Gen4, tối đa hỗ trợ 2TB | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 50% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 2 x USB 3.2 gen 1 Type-A LAN (RJ45) HDMI 2.1 2 x USB Type-C 3.2 Gen 2 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD card reader | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: DTS | Tản nhiệt:: 2 ống đồng 1 x Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.39 mm - Rộng 31.59 mm - Dày 1.11 ~ 1.79 - 1.45 kg | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-225u-21sx005nvn</t>
+          <t>https://www.thegioididong.com/laptop/msi-modern-14s-g3mg-003vn-core-5-320</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:49:37</t>
+          <t>2026-09-14 16:06:03</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad X9 14 Gen 1 - 21QA006JVN (Ultra 7 258V, 32GB, 512GB, WUXGA OLED, Win11Pro)</t>
+          <t>Laptop MSI Modern 15 F1MG-1264VN (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>53790000</v>
+        <v>19990000</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>55190000</v>
+        <v>22390000</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.80 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Chống chói Anti Glare Dolby Vision 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm HDMI 2.1 2 x USB-C (hỗ trợ Thunderbolt 4/USB 4, USB Power Delivery và DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.8 mm - Rộng 212.3 mm - Dày 17.18 mm - 1.21 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core thế hệ 12 - 120U | Số nhân:: Hãng không công bố | Số luồng:: 12 | Tốc độ CPU:: 1.45 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (2280) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: Hãng không công bố | Cổng giao tiếp:: 3 x USB 3.2 Gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell, 46.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.7 kg | Chất liệu:: Plastic (nhựa dẻo)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-x9-14-gen-1-ultra-7-258v-21qa006jvn</t>
+          <t>https://www.thegioididong.com/laptop/msi-modern-15-f1mg-1264vn-core-5-120u</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:49:50</t>
+          <t>2026-09-14 16:06:18</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo V14 G5 - 83HD0035VN (Core7 240H, 16G, 512GB, Full HD, Win11)</t>
+          <t>Laptop SingPC M16-i382 (i3 1215U, 8GB, 256GB, WUXGA, Win11 Pro)</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>31290000</v>
+        <v>13490000</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>32690000</v>
+        <v>15190000</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) LAN (RJ45) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Ion, 47 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324.2 mm - Rộng 215.2 mm - Dày 17.9 mm - 1.37 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i3 Alder Lake - 1215U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.2GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 256 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-v14-g5-core7-240h-83hd0035vn</t>
+          <t>https://www.thegioididong.com/laptop/singpc-m16-i382-i3-1215u</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1990,40 +1978,40 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:50:04</t>
+          <t>2026-09-14 16:06:31</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002LVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop SingPC M16-i595 (i5 1235U, 16GB, 512GB, WUXGA, Win11 Pro)</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>38490000</v>
+        <v>17390000</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>44990000</v>
+        <v>19990000</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i5 Alder Lake - 1235U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 72% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-5-322-83tc002lvn</t>
+          <t>https://www.thegioididong.com/laptop/singpc-m16-i595-i5-1235u</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2033,40 +2021,40 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:50:17</t>
+          <t>2026-09-14 16:06:44</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Air 14 SFA14-I31-52BV - NX.W49SV.002 (Core 5 320, 12GB, 512GB, Full HD 120Hz, Win11)</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-977M - NX.W26SV.001 (Ultra 9 185H, 16GB, 512GB, Full HD+, Win11)</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>24990000</v>
+        <v>29990000</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>26990000</v>
+        <v>31990000</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Đang cập nhật | RAM:: 12 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 350 nits | Cổng giao tiếp:: 1 x USB 3.2 2 x USB Type-C (hỗ trợ USB, Power Delivery, DisplayPort và Thunderbolt 4) | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.3 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 222.65 mm - Rộng 222.65 mm - Dày 12.99 mm - 1.19 kg | Chất liệu:: Khung và mặt lưng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 9 Meteor Lake - 185H | Số luồng:: 22 | Tốc độ CPU:: 2.30 GHz (Lên đến 5.10 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (1 khe onboard) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB Type-C (65W) 1 x USB Type-C LAN (RJ45) HDMI 2.1 USB Type-C | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Stereo speakers | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 10 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.6 mm - Rộng 227.7 mm - Dày 17.9 mm - 1.49 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-swift-air-14-sfa14-i31-52bv-core-5-320-nx-w49sv-002</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-go-14-ai-ag14-i71m-977m-ultra-9-185h-nx-w26sv-001</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2076,365 +2064,365 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:51:12</t>
+          <t>2026-09-14 11:54:42</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go AI SFG14-75-5264 - NX.JNBSV.001 (Ultra 5 226V, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR - NX.X0PSV.002 (Ryzen 5 3500U, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>29990000</v>
+        <v>17990000</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>31990000</v>
+        <v>20990000</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Lunar Lake - 226V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 3.50 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 40 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 130V | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: OLED | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe ACER CineCrystal 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 2 x USB4 Type-C (hỗ trợ truyền dữ liệu, DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 65Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 227.4 mm - Rộng 312.4 mm - Dày 15.95 mm - 1.24 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 3500U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz | Card màn hình:: Card tích hợp - AMD Radeon Vega Mobile Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 2400 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: IPS LED-backlit TFT LCD Wide viewing angle 250 nits | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A HDMI 1 x SuperSpeed USB Type-C (hỗ trợ DisplayPort 1.4) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP FHD 1080p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: 2 loa 2 microphones | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Phím Copilot | Thông tin Pin:: 2-cell Li-ion, 45.6 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 210.2 mm - Rộng 322.6 mm - Dày 19.8 mm - 1.3 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-swift-go-ai-sfg14-75-5264-ultra-5-226v-nxjnbsv001</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-nx-x0psv-002</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:51:26</t>
+          <t>2026-09-14 11:54:57</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go AI SFG14-75-765M - NX.JNBSV.004 (Ultra 7 258V, 32GB, 512GB, Full HD+, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN - NX.DDASV.001 (Core 3 N350, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>39990000</v>
+        <v>16990000</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>41990000</v>
+        <v>18990000</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số luồng:: 8 | Tốc độ CPU:: 2.2 GHz | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: Lên đến 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Wide viewing angle ACER CineCrystal 400 nits | Cổng giao tiếp:: 1 x USB 3.2 Gen 1 (hỗ trợ Power-off USB charging) HDMI 2.1 Micro SD 2 x USB Type-C (hỗ trợ DisplayPort, Thunderbolt 4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD card reader | Webcam:: HP True Vision 1080p FHD camera ToF Sensor Camera with Dual Microphone Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Công nghệ âm thanh:: Hi-Res Audio Spatial Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: Li-ion, 65 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 227.4 mm - Rộng 312.4 mm - Dày 9.7/15.95 (H) - 1.24 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - N350 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 3.90 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB 3.2 HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.0 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.8 mm - Rộng 235.6 mm - Dày 19.7 mm - 1.53 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-swift-go-ai-sfg14-75-765m-ultra-7-258v-nx-jnbsv-004</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-36p-30tn-core-3-n350-nx-ddasv-001</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:51:41</t>
+          <t>2026-09-14 11:55:11</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP - U716S8W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 - NX.X0RSV.001 (Ryzen 5 3500U, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>32990000</v>
+        <v>17990000</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>34990000</v>
+        <v>20990000</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 430 mm - Rộng 316 mm - Dày 19.9 mm - 2.61 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 3500U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz | Card màn hình:: Card tích hợp - AMD Radeon Vega Mobile Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 2400 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: IPS Màn hình Wide View Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A HDMI 1 x SuperSpeed USB Type-C (hỗ trợ DisplayPort 1.4) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP FHD 1080p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: 2 loa 2 microphones | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Phím Copilot | Thông tin Pin:: 2-cell Li-ion, 45.6 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 229.3 mm - Rộng 357.4 mm - Dày 19.85 mm - 1.5 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-p3-p3406ccap-ultra-7-255h-u716s8w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-nx-x0rsv-001</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:51:56</t>
+          <t>2026-09-14 11:55:24</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA - NZ1368W (Ultra 5 226V, 16GB, 512GB, WQXGA 144Hz, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-44P-R4UH - NX.DJVSV.002 (R7 7730U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>30090000</v>
+        <v>21990000</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>31990000</v>
+        <v>23990000</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Lunar Lake - 226V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 40 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 130V | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Anti-Glare Màn hình Wide View 400 nits | Cổng giao tiếp:: 2 x Thunderbolt 4 1 x 3.5mm combo audio jack HDMI 2 x USB 3.2 gen 2 Type-A | Kết nối không dây:: Hãng không công bố | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in array microphone Dolby Atmos | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 223 mm - Dày 12.8 ~ 16.4 mm - 1.2 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB Type - C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 230.2 mm - Dày 18.6 mm - 1.49 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-p5-p5405csa-ultra-5-226v-nz1368w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-44p-r4uh-r7-7730u-nx-djvsv-002</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:52:09</t>
+          <t>2026-09-14 11:55:37</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA - NZ1371W (Ultra 7 258V, 32GB, 512GB, WQXGA 144Hz, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC - NX.DG3SV.002.16G (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>37490000</v>
+        <v>21990000</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>39490000</v>
+        <v>24990000</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Intel Arc 140V | Số nhân GPU:: Hãng không công bố | RAM:: 32 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Anti-Glare Màn hình Wide View 400 nits | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 Type-A 1 x Thunderbolt 4 (hỗ trợ DisplayPort) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Smart Amp Technology Built-in array microphone Dolby Atmos | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 223 mm - Dày 12.8 ~ 16.4 mm - 1.2 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 357.6 mm - Rộng 228.5 mm - Dày 18.7 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-p5-p5405csa-ultra-7-258v-nz1371w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-53p-56ec-core-5-120u-nx-dg3sv-002-16g</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:52:22</t>
+          <t>2026-09-14 11:55:51</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook Ultra B9 B9406CAA - X7642TW (Ultra X7 358H, 64GB, 2TB, WQXGA+ OLED 120Hz, Win11)</t>
+          <t>Laptop Acer Aspire Lite 16 AL16-71P-582Q - NX.DRSSV.001 (Ultra 5 125H, 16GB, 512GB, Full HD+ 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>97990000</v>
+        <v>24990000</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>100000000</v>
+        <v>26990000</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra X7 Panther Lake | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 2 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 1 x USB Type-C (hỗ trợ cổng Thunderbolt 4) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Có | Công nghệ âm thanh:: Built-in speaker Built-in array microphone Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 28.8 mm - Rộng 12.7 mm - Dày 38.9 mm - 1.131 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 125H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357 mm - Rộng 245.5 mm - Dày 18.9 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-b9-b9406caa-ultra-x7-358h-x7642tw</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-16-al16-71p-582q-ultra-5-125h-nx-drssv-001</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:52:35</t>
+          <t>2026-09-14 11:56:05</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook Ultra B9 B9406CAA - X7321TW (Ultra X7 358H, 32GB, 1TB, WQXGA+ OLED 120Hz, Win11)</t>
+          <t>Laptop Acer Gaming Aspire 7 A715-59G-59RD - NH.DXUSV.001 (Core 5 210H, 16GB, 512GB, RTX 3050 4GB, Fulll HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>65990000</v>
+        <v>26990000</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>68000000</v>
+        <v>31990000</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra X7 Panther Lake - 358H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare 600 nits Pantone Validated | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x Thunderbolt 4 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Built-in speaker Built-in array microphone Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.9 mm - Dày 16.4 mm - 1.1 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 4 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35W - 80W | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 4 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle 350 nits Acer ComfyView | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C (hỗ trợ DisplayPort 1.4) LAN (RJ45) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn LED - 15 chế độ màu | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 359.5 mm - Rộng 238 mm - Dày 22.7 mm - 1.99 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-b9-b9406caa-x7321tw-ultra-x7-358h-32gb-1tb-wqxga-oled-120hz-win11</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-aspire-7-a715-59g-59rd-core-5-210h-nh-dxusv-001</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:52:48</t>
+          <t>2026-09-14 11:56:18</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0045W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel AN16S-61-R9CN - NH.QXGSV.001 (Ryzen AI 7 350, 16GB, 512GB, RTX 5070 8GB, 2K+ 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>30990000</v>
+        <v>57990000</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>33990000</v>
+        <v>64990000</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 1 x USB Type-C with Thunderbolt 5 (hỗ trợ USB 4, DisplayPort 2.1 và Power Delivery 3.0) | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.0 GHz (Lên đến 5.2 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits 3ms | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: NVIDIA Optimus | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-5-225h-sf0045w</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-an16s-61-r9cn-ryzen-ai-7-350-nh-qxgsv-001</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:53:02</t>
+          <t>2026-09-14 11:56:31</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0241W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-556L - NH.QZ9SV.006 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>35990000</v>
+        <v>38990000</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>37990000</v>
+        <v>40990000</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
@@ -2443,490 +2431,490 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display Màn hình Wide View | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 60W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 16:9 aspect ratio Ultra-slim design Mercury free, environment friendly Thời gian phản hồi: 3 ms LED-backlit TFT LCD Wide viewing angle 300 nits Acer ComfyView | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Ethernet (LAN) Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: 720p at 30 fps HD camera | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High SNR DAC 2.1 Vrms Hỗ trợ tai nghe đến 600 Ω Compatible with Cortana with Voice 2 microphones Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Tính năng khác:: NitroSense Key Copilot Key | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 239.89 mm - Rộng 362.3 mm - Dày 115.7/23.5 - 2.1 kg | Chất liệu:: Nhựa nguyên khối</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-7-255-sf0241w</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-556l-core-5-210h-nh-qz9sv-006</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:53:15</t>
+          <t>2026-09-14 11:56:44</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming ROG Strix G16 G614PM - TS147W (R9 8940HX, 16GB, 512GB, RTX 5060 8GB, WQXGA 300Hz, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-73Z8 - NH.QUASV.001 (Core 7 240H, 16GB, 512GB, RTX 4050 6GB, Full HD  180Hz, Win11)</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>54990000</v>
+        <v>35990000</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>57990000</v>
+        <v>39990000</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115W - 140W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.288 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: IPS | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1x Ethernet 3 x USB 3.2 Gen 1 Type-A 1 x USB Type-C (65W) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: 720p at 30 fps HD camera Camera with Dual Microphone | Đèn bàn phím:: Đơn sắc - Màu cam | Công nghệ âm thanh:: Windows Spatial Sound High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pm-r9-8940hx-ts147w</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-73z8-core-7-240h-nh-quasv-001</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:53:29</t>
+          <t>2026-09-14 11:56:59</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming ROG Strix G16 G614PR - TS103W (R9 8940HX, 16GB, 512GB, RTX 5070Ti 12GB, WQXGA 300Hz, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-78MD - NH.QZ9SV.007 (Core 7 240H, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>70590000</v>
+        <v>40990000</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>71990000</v>
+        <v>43990000</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070Ti, 12 GB | Số nhân GPU:: 5888 CUDA Cores | Công suất đồ hoạ - TGP:: 140 W | Hiệu năng xử lý AI (TOPS):: Lên đến 992 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.34 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms 300 nits Acer ComfyView | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2 microphones Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Nhựa nguyên khối</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pr-r9-8940hx-ts103w</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-78md-core-7-240h-nh-qz9sv-007</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:53:43</t>
+          <t>2026-09-14 11:57:13</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming V16 V3607VJ Core 5 - TK189W (Core 5 210H, 16GB, 512GB, RTX 3050 6GB, WUXGA 144Hz, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-61-R0B8 - NH.QXQSV.001 (Ryzen AI 5 340, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>25990000</v>
+        <v>42990000</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>36990000</v>
+        <v>47990000</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 6 GB | Công suất đồ hoạ - TGP:: 65 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% Adobe | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x 3.5mm combo audio jack HDMI 2.1 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: 1080p with Privacy Shutter | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in microphone | Tản nhiệt:: 2 quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 63 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 251 mm - Dày 22 mm - 1.95 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.40 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-v16-v3607vj-core-5-core-5-210h-tk189w</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-61-r0b8-ryzen-ai-5-340-nh-qxqsv-001</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:53:56</t>
+          <t>2026-09-14 11:57:27</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming V16 V3607VU - TK416W (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, WUXGA 144Hz, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-71-58WQ - NH.QXBSV.001 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, 2K+ 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>32990000</v>
+        <v>44990000</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>41990000</v>
+        <v>46990000</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 65 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 2 khe (1 khe 16 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x 3.5mm combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.3 | Webcam:: 1080p FHD camera | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: Mô-đun bảo mật TPM (Firmware TPM) Mật khẩu thiết lập BIOS | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in microphone | Tản nhiệt:: 2 quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 63 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 250.7 mm - Dày 18 mm - 1.95 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-v16-v3607vu-core-5-210h-tk416w</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-71-58wq-core-5-210h-nh-qxbsv-001</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:54:09</t>
+          <t>2026-09-14 11:57:40</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ProArt P1 H7606WP - SR335W (R9 AI HX 370, 64GB, 2TB, RTX 5070 8GB, 3K 120Hz, Cảm ứng, Win11)</t>
+          <t>Laptop Acer Gaming Predator Helios Neo 16S PHN16S-I51-97T9 - NH.U3SSV.006 (Ultra 9 386H, 16GB, 512GB, RTX 5070 8GB, 2K+ 165Hz, Win11)</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>114890000</v>
+        <v>75990000</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>124990000</v>
+        <v>77990000</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 9 - Hãng không công bố | Số nhân:: 12 | Số luồng:: 24 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 2 TB SSD M.2 NVMe PCIe Gen 4 | Kích thước màn hình:: 16" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 500 nits (Khi bật HDR) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354.9 mm - Rộng 246.9 mm - Dày 17.3 mm - 1.85 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 9 Panther Lake - 386H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 50 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: LED-backlit TFT LCD 500 nits Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 18.9 mm - 2.2 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-proart-p1-h7606wp-r9-ai-hx-370-sr335w</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16s-phn16s-i51-97t9-ultra-9-386h</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:54:22</t>
+          <t>2026-09-14 11:57:53</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1404MA - EB028W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Acer Nitro ProPanel AN16S-61-R7ZJ - NH.QXFSV.002 (R7 AI 350, 16GB, 512GB, RTX 5060 8GB, 2K, Win11)</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>24990000</v>
+        <v>49990000</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>31990000</v>
+        <v>51990000</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>-22%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe RAM) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Hãng không công bố | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 21.39 mm - Rộng 32.49 mm - Dày 1.79 mm - 1.4 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Nhôm &amp; Nhựa</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1404ma-core-5-320-eb028w</t>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-an16s-61-r7zj-r7-ai-350-nhqxfsv002</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:54:35</t>
+          <t>2026-09-14 11:58:07</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1407CA - LY203W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Acer Nitro ProPanel ANV15-52-50RB - NH.QUASV.002 (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>24490000</v>
+        <v>33490000</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>33490000</v>
+        <v>37990000</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>-27%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 19.9 mm - 1.46 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 60W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 300 nits Acer ComfyView 3ms | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2 microphones Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Tính năng khác:: Copilot Key | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1407ca-ultra-5-225h-ly203w</t>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv15-52-50rb-core-5-210h-nh-quasv-002</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:54:47</t>
+          <t>2026-09-14 11:58:20</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ385W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Acer Nitro ProPanel ANV16-72-782F - NH.QUPSV.001 (Core 7 240H, 16GB, 512GB, RTX 5050 8GB, Full HD+ 180 Hz, Win11)</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>24990000</v>
+        <v>43990000</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>31990000</v>
+        <v>45990000</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>-22%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 80 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 360 mm - Rộng 274.5 mm - Dày 24.5 mm - 2.4 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-5-320-bq385w</t>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv16-72-782f-core-7-240h-nhqupsv001</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:55:00</t>
+          <t>2026-09-14 11:58:35</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ395W (Core 7 350, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Acer Nitro ProPanel ANV16S-61-R7KQ - NH.QXPSV.001 (R5 AI 340, 16GB, 512GB, RTX 5060 8GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>28990000</v>
+        <v>46990000</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>35490000</v>
+        <v>48990000</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Wildcat Lake - 350 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 17 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 400 nits | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB Type C 3.2 Gen 2 (Hỗ trợ Power Delivery và DisplayPort™ 2.1) LAN (RJ45) HDMI 2.1 3 x USB A | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD 1080p Camera IR | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Hi-Res certification Spatial Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-7-350-bq395w</t>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv16s-61-r7kq-r5-ai-340-nhqxpsv001</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:55:13</t>
+          <t>2026-09-14 11:58:49</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 16 X1607CA - MB387W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Acer Swift Air 14 SFA14-I31-34NF - NX.W49SV.001 (Core 3 304, 12GB, 512GB, WUXGA 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>25090000</v>
+        <v>21990000</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>33490000</v>
+        <v>23990000</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 SO-DIMM | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 25.06 mm - Rộng 35.7 mm - Dày 1.79 ~ 1.99 - 1.88 kg | Chất liệu:: Khung nhôm - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - 304 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 12 GB | Loại RAM:: LPDDR5 (1 khe onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Wide viewing angle 350 nits LED Backlight Acer ComfyView | Cổng giao tiếp:: 1 x USB 3.2 2 x USB Type-C (hỗ trợ USB, Power Delivery, DisplayPort và Thunderbolt 4) | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.3 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.99 mm - Rộng 222.65 mm - Dày 12.99 mm - 1.19 kg | Chất liệu:: Khung và mặt lưng kim loại</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-16-x1607ca-ultra-5-225h-mb387w</t>
+          <t>https://www.thegioididong.com/laptop/acer-swift-air-14-sfa14-i31-34nf-core-3-304-nx-w49sv-001</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:55:27</t>
+          <t>2026-09-14 11:59:03</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-977M - NX.W26SV.001 (Ultra 9 185H, 16GB, 512GB, Full HD+, Win11)</t>
+          <t>Laptop Acer Swift Air 14 SFA14-I31-52BV - NX.W49SV.002 (Core 5 320, 12GB, 512GB, Full HD 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>29990000</v>
+        <v>24990000</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>31990000</v>
+        <v>26990000</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 9 Meteor Lake - 185H | Số luồng:: 22 | Tốc độ CPU:: 2.30 GHz (Lên đến 5.10 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (1 khe onboard) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB Type-C (65W) 1 x USB Type-C LAN (RJ45) HDMI 2.1 USB Type-C | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Stereo speakers | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 10 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.6 mm - Rộng 227.7 mm - Dày 17.9 mm - 1.49 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Đang cập nhật | RAM:: 12 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 350 nits | Cổng giao tiếp:: 1 x USB 3.2 2 x USB Type-C (hỗ trợ USB, Power Delivery, DisplayPort và Thunderbolt 4) | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.3 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 222.65 mm - Rộng 222.65 mm - Dày 12.99 mm - 1.19 kg | Chất liệu:: Khung và mặt lưng kim loại</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-go-14-ai-ag14-i71m-977m-ultra-9-185h-nx-w26sv-001</t>
+          <t>https://www.thegioididong.com/laptop/acer-swift-air-14-sfa14-i31-52bv-core-5-320-nx-w49sv-002</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2936,365 +2924,365 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:53:57</t>
+          <t>2026-09-14 13:27:18</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR - NX.X0PSV.002 (Ryzen 5 3500U, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Acer Swift Go AI SFG14-75-5264 - NX.JNBSV.001 (Ultra 5 226V, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>17990000</v>
+        <v>29990000</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>20990000</v>
+        <v>31990000</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 3500U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz | Card màn hình:: Card tích hợp - AMD Radeon Vega Mobile Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 2400 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: IPS LED-backlit TFT LCD Wide viewing angle 250 nits | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A HDMI 1 x SuperSpeed USB Type-C (hỗ trợ DisplayPort 1.4) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP FHD 1080p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: 2 loa 2 microphones | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Phím Copilot | Thông tin Pin:: 2-cell Li-ion, 45.6 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 210.2 mm - Rộng 322.6 mm - Dày 19.8 mm - 1.3 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Lunar Lake - 226V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 3.50 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 40 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 130V | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: OLED | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe ACER CineCrystal 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 2 x USB4 Type-C (hỗ trợ truyền dữ liệu, DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 65Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 227.4 mm - Rộng 312.4 mm - Dày 15.95 mm - 1.24 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-nx-x0psv-002</t>
+          <t>https://www.thegioididong.com/laptop/acer-swift-go-ai-sfg14-75-5264-ultra-5-226v-nxjnbsv001</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:54:11</t>
+          <t>2026-09-14 13:27:32</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN - NX.DDASV.001 (Core 3 N350, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Acer Swift Go AI SFG14-75-765M - NX.JNBSV.004 (Ultra 7 258V, 32GB, 512GB, Full HD+, Win11)</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>16990000</v>
+        <v>39990000</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>18990000</v>
+        <v>41990000</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - N350 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 3.90 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB 3.2 HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.0 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.8 mm - Rộng 235.6 mm - Dày 19.7 mm - 1.53 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số luồng:: 8 | Tốc độ CPU:: 2.2 GHz | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: Lên đến 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Wide viewing angle ACER CineCrystal 400 nits | Cổng giao tiếp:: 1 x USB 3.2 Gen 1 (hỗ trợ Power-off USB charging) HDMI 2.1 Micro SD 2 x USB Type-C (hỗ trợ DisplayPort, Thunderbolt 4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD card reader | Webcam:: HP True Vision 1080p FHD camera ToF Sensor Camera with Dual Microphone Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Công nghệ âm thanh:: Hi-Res Audio Spatial Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: Li-ion, 65 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 227.4 mm - Rộng 312.4 mm - Dày 9.7/15.95 (H) - 1.24 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-36p-30tn-core-3-n350-nx-ddasv-001</t>
+          <t>https://www.thegioididong.com/laptop/acer-swift-go-ai-sfg14-75-765m-ultra-7-258v-nx-jnbsv-004</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:54:24</t>
+          <t>2026-09-14 13:27:46</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 - NX.X0RSV.001 (Ryzen 5 3500U, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP - U716S8W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>17990000</v>
+        <v>32990000</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>20990000</v>
+        <v>34990000</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 3500U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz | Card màn hình:: Card tích hợp - AMD Radeon Vega Mobile Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 2400 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: IPS Màn hình Wide View Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A HDMI 1 x SuperSpeed USB Type-C (hỗ trợ DisplayPort 1.4) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP FHD 1080p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: 2 loa 2 microphones | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Phím Copilot | Thông tin Pin:: 2-cell Li-ion, 45.6 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 229.3 mm - Rộng 357.4 mm - Dày 19.85 mm - 1.5 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 430 mm - Rộng 316 mm - Dày 19.9 mm - 2.61 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-nx-x0rsv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-p3-p3406ccap-ultra-7-255h-u716s8w</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:54:38</t>
+          <t>2026-09-14 13:28:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-44P-R4UH - NX.DJVSV.002 (R7 7730U, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA - NZ1368W (Ultra 5 226V, 16GB, 512GB, WQXGA 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>21990000</v>
+        <v>30090000</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>23990000</v>
+        <v>31990000</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB Type - C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 230.2 mm - Dày 18.6 mm - 1.49 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Lunar Lake - 226V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 40 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 130V | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Anti-Glare Màn hình Wide View 400 nits | Cổng giao tiếp:: 2 x Thunderbolt 4 1 x 3.5mm combo audio jack HDMI 2 x USB 3.2 gen 2 Type-A | Kết nối không dây:: Hãng không công bố | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in array microphone Dolby Atmos | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 223 mm - Dày 12.8 ~ 16.4 mm - 1.2 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-44p-r4uh-r7-7730u-nx-djvsv-002</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-p5-p5405csa-ultra-5-226v-nz1368w</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:54:51</t>
+          <t>2026-09-14 13:28:14</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC - NX.DG3SV.002.16G (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA - NZ1371W (Ultra 7 258V, 32GB, 512GB, WQXGA 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>21990000</v>
+        <v>37490000</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>24990000</v>
+        <v>39490000</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 357.6 mm - Rộng 228.5 mm - Dày 18.7 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Intel Arc 140V | Số nhân GPU:: Hãng không công bố | RAM:: 32 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Anti-Glare Màn hình Wide View 400 nits | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 Type-A 1 x Thunderbolt 4 (hỗ trợ DisplayPort) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Smart Amp Technology Built-in array microphone Dolby Atmos | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 223 mm - Dày 12.8 ~ 16.4 mm - 1.2 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-53p-56ec-core-5-120u-nx-dg3sv-002-16g</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-p5-p5405csa-ultra-7-258v-nz1371w</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:55:05</t>
+          <t>2026-09-14 13:28:27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AL16-71P-582Q - NX.DRSSV.001 (Ultra 5 125H, 16GB, 512GB, Full HD+ 120Hz, Win11)</t>
+          <t>Laptop Asus ExpertBook Ultra B9 B9406CAA - X7642TW (Ultra X7 358H, 64GB, 2TB, WQXGA+ OLED 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>24990000</v>
+        <v>97990000</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>26990000</v>
+        <v>100000000</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 125H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357 mm - Rộng 245.5 mm - Dày 18.9 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra X7 Panther Lake | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 2 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 1 x USB Type-C (hỗ trợ cổng Thunderbolt 4) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Có | Công nghệ âm thanh:: Built-in speaker Built-in array microphone Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 28.8 mm - Rộng 12.7 mm - Dày 38.9 mm - 1.131 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-16-al16-71p-582q-ultra-5-125h-nx-drssv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-b9-b9406caa-ultra-x7-358h-x7642tw</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:55:18</t>
+          <t>2026-09-14 13:28:40</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Aspire 7 A715-59G-59RD - NH.DXUSV.001 (Core 5 210H, 16GB, 512GB, RTX 3050 4GB, Fulll HD 144Hz, Win11)</t>
+          <t>Laptop Asus ExpertBook Ultra B9 B9406CAA - X7321TW (Ultra X7 358H, 32GB, 1TB, WQXGA+ OLED 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>26990000</v>
+        <v>65990000</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>31990000</v>
+        <v>68000000</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 4 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35W - 80W | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 4 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle 350 nits Acer ComfyView | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C (hỗ trợ DisplayPort 1.4) LAN (RJ45) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn LED - 15 chế độ màu | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 359.5 mm - Rộng 238 mm - Dày 22.7 mm - 1.99 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra X7 Panther Lake - 358H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare 600 nits Pantone Validated | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x Thunderbolt 4 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Built-in speaker Built-in array microphone Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.9 mm - Dày 16.4 mm - 1.1 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-aspire-7-a715-59g-59rd-core-5-210h-nh-dxusv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-b9-b9406caa-x7321tw-ultra-x7-358h-32gb-1tb-wqxga-oled-120hz-win11</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:55:32</t>
+          <t>2026-09-14 13:28:53</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel AN16S-61-R9CN - NH.QXGSV.001 (Ryzen AI 7 350, 16GB, 512GB, RTX 5070 8GB, 2K+ 180Hz, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0045W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>57990000</v>
+        <v>30990000</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>64990000</v>
+        <v>33990000</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.0 GHz (Lên đến 5.2 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits 3ms | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: NVIDIA Optimus | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 1 x USB Type-C with Thunderbolt 5 (hỗ trợ USB 4, DisplayPort 2.1 và Power Delivery 3.0) | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-an16s-61-r9cn-ryzen-ai-7-350-nh-qxgsv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-5-225h-sf0045w</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:55:45</t>
+          <t>2026-09-14 13:29:08</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-556L - NH.QZ9SV.006 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0241W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>38990000</v>
+        <v>35990000</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>40990000</v>
+        <v>37990000</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
@@ -3303,600 +3291,600 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 60W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 16:9 aspect ratio Ultra-slim design Mercury free, environment friendly Thời gian phản hồi: 3 ms LED-backlit TFT LCD Wide viewing angle 300 nits Acer ComfyView | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Ethernet (LAN) Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: 720p at 30 fps HD camera | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High SNR DAC 2.1 Vrms Hỗ trợ tai nghe đến 600 Ω Compatible with Cortana with Voice 2 microphones Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Tính năng khác:: NitroSense Key Copilot Key | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 239.89 mm - Rộng 362.3 mm - Dày 115.7/23.5 - 2.1 kg | Chất liệu:: Nhựa nguyên khối</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display Màn hình Wide View | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-556l-core-5-210h-nh-qz9sv-006</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-7-255-sf0241w</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:56:00</t>
+          <t>2026-09-14 13:29:22</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-73Z8 - NH.QUASV.001 (Core 7 240H, 16GB, 512GB, RTX 4050 6GB, Full HD  180Hz, Win11)</t>
+          <t>Laptop Asus Gaming ROG Strix G16 G614PM - TS147W (R9 8940HX, 16GB, 512GB, RTX 5060 8GB, WQXGA 300Hz, Win11)</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>35990000</v>
+        <v>54990000</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>39990000</v>
+        <v>57990000</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: IPS | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1x Ethernet 3 x USB 3.2 Gen 1 Type-A 1 x USB Type-C (65W) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: 720p at 30 fps HD camera Camera with Dual Microphone | Đèn bàn phím:: Đơn sắc - Màu cam | Công nghệ âm thanh:: Windows Spatial Sound High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115W - 140W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.288 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-73z8-core-7-240h-nh-quasv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pm-r9-8940hx-ts147w</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:56:14</t>
+          <t>2026-09-14 13:29:35</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-78MD - NH.QZ9SV.007 (Core 7 240H, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
+          <t>Laptop Asus Gaming ROG Strix G16 G614PR - TS103W (R9 8940HX, 16GB, 512GB, RTX 5070Ti 12GB, WQXGA 300Hz, Win11)</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>40990000</v>
+        <v>70590000</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>43990000</v>
+        <v>71990000</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms 300 nits Acer ComfyView | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2 microphones Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Nhựa nguyên khối</t>
+          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070Ti, 12 GB | Số nhân GPU:: 5888 CUDA Cores | Công suất đồ hoạ - TGP:: 140 W | Hiệu năng xử lý AI (TOPS):: Lên đến 992 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.34 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-78md-core-7-240h-nh-qz9sv-007</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pr-r9-8940hx-ts103w</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:56:27</t>
+          <t>2026-09-14 13:29:49</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-61-R0B8 - NH.QXQSV.001 (Ryzen AI 5 340, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
+          <t>Laptop Asus Gaming V16 V3607VJ Core 5 - TK189W (Core 5 210H, 16GB, 512GB, RTX 3050 6GB, WUXGA 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>42990000</v>
+        <v>25990000</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>47990000</v>
+        <v>36990000</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-30%</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.40 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 6 GB | Công suất đồ hoạ - TGP:: 65 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% Adobe | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x 3.5mm combo audio jack HDMI 2.1 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: 1080p with Privacy Shutter | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in microphone | Tản nhiệt:: 2 quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 63 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 251 mm - Dày 22 mm - 1.95 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-61-r0b8-ryzen-ai-5-340-nh-qxqsv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-v16-v3607vj-core-5-core-5-210h-tk189w</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:56:41</t>
+          <t>2026-09-14 13:30:03</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-71-58WQ - NH.QXBSV.001 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, 2K+ 180Hz, Win11)</t>
+          <t>Laptop Asus Gaming V16 V3607VU - TK416W (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, WUXGA 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>44990000</v>
+        <v>32990000</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>46990000</v>
+        <v>41990000</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 65 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 2 khe (1 khe 16 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x 3.5mm combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.3 | Webcam:: 1080p FHD camera | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: Mô-đun bảo mật TPM (Firmware TPM) Mật khẩu thiết lập BIOS | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in microphone | Tản nhiệt:: 2 quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 63 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 250.7 mm - Dày 18 mm - 1.95 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-71-58wq-core-5-210h-nh-qxbsv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-v16-v3607vu-core-5-210h-tk416w</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:56:57</t>
+          <t>2026-09-14 13:30:17</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Predator Helios Neo 16S PHN16S-I51-97T9 - NH.U3SSV.006 (Ultra 9 386H, 16GB, 512GB, RTX 5070 8GB, 2K+ 165Hz, Win11)</t>
+          <t>Laptop Asus ProArt P1 H7606WP - SR335W (R9 AI HX 370, 64GB, 2TB, RTX 5070 8GB, 3K 120Hz, Cảm ứng, Win11)</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>75990000</v>
+        <v>114890000</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>77990000</v>
+        <v>124990000</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 9 Panther Lake - 386H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 50 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: LED-backlit TFT LCD 500 nits Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 18.9 mm - 2.2 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 9 - Hãng không công bố | Số nhân:: 12 | Số luồng:: 24 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 2 TB SSD M.2 NVMe PCIe Gen 4 | Kích thước màn hình:: 16" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 500 nits (Khi bật HDR) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354.9 mm - Rộng 246.9 mm - Dày 17.3 mm - 1.85 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16s-phn16s-i51-97t9-ultra-9-386h</t>
+          <t>https://www.thegioididong.com/laptop/asus-proart-p1-h7606wp-r9-ai-hx-370-sr335w</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:57:12</t>
+          <t>2026-09-14 13:30:30</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Nitro ProPanel AN16S-61-R7ZJ - NH.QXFSV.002 (R7 AI 350, 16GB, 512GB, RTX 5060 8GB, 2K, Win11)</t>
+          <t>Laptop Asus Vivobook 14 X1404MA - EB028W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>49990000</v>
+        <v>23990000</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>51990000</v>
+        <v>31990000</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Nhôm &amp; Nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe RAM) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Hãng không công bố | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 21.39 mm - Rộng 32.49 mm - Dày 1.79 mm - 1.4 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-an16s-61-r7zj-r7-ai-350-nhqxfsv002</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1404ma-core-5-320-eb028w</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:57:26</t>
+          <t>2026-09-14 13:30:43</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Nitro ProPanel ANV15-52-50RB - NH.QUASV.002 (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, Full HD 180Hz, Win11)</t>
+          <t>Laptop Asus Vivobook 14 X1407CA - LY203W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
+        <v>24490000</v>
+      </c>
+      <c r="C74" s="2" t="n">
         <v>33490000</v>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>37990000</v>
-      </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-27%</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 60W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 300 nits Acer ComfyView 3ms | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2 microphones Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Tính năng khác:: Copilot Key | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 19.9 mm - 1.46 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv15-52-50rb-core-5-210h-nh-quasv-002</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1407ca-ultra-5-225h-ly203w</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:57:40</t>
+          <t>2026-09-14 13:30:55</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Nitro ProPanel ANV16-72-782F - NH.QUPSV.001 (Core 7 240H, 16GB, 512GB, RTX 5050 8GB, Full HD+ 180 Hz, Win11)</t>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ385W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>43990000</v>
+        <v>23990000</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>45990000</v>
+        <v>31990000</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 80 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 360 mm - Rộng 274.5 mm - Dày 24.5 mm - 2.4 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv16-72-782f-core-7-240h-nhqupsv001</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-5-320-bq385w</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:57:53</t>
+          <t>2026-09-14 13:31:09</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Nitro ProPanel ANV16S-61-R7KQ - NH.QXPSV.001 (R5 AI 340, 16GB, 512GB, RTX 5060 8GB, Full HD 180Hz, Win11)</t>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ395W (Core 7 350, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46990000</v>
+        <v>27990000</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>48990000</v>
+        <v>35490000</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 400 nits | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB Type C 3.2 Gen 2 (Hỗ trợ Power Delivery và DisplayPort™ 2.1) LAN (RJ45) HDMI 2.1 3 x USB A | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD 1080p Camera IR | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Hi-Res certification Spatial Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 7 Wildcat Lake - 350 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 17 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv16s-61-r7kq-r5-ai-340-nhqxpsv001</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-7-350-bq395w</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:58:07</t>
+          <t>2026-09-14 13:31:22</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Air 14 SFA14-I31-34NF - NX.W49SV.001 (Core 3 304, 12GB, 512GB, WUXGA 120Hz, Win11)</t>
+          <t>Laptop Asus Vivobook 16 X1607CA - MB387W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>21990000</v>
+        <v>24590000</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>23990000</v>
+        <v>33490000</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-27%</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - 304 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 12 GB | Loại RAM:: LPDDR5 (1 khe onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Wide viewing angle 350 nits LED Backlight Acer ComfyView | Cổng giao tiếp:: 1 x USB 3.2 2 x USB Type-C (hỗ trợ USB, Power Delivery, DisplayPort và Thunderbolt 4) | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.3 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.99 mm - Rộng 222.65 mm - Dày 12.99 mm - 1.19 kg | Chất liệu:: Khung và mặt lưng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 SO-DIMM | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 25.06 mm - Rộng 35.7 mm - Dày 1.79 ~ 1.99 - 1.88 kg | Chất liệu:: Khung nhôm - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-swift-air-14-sfa14-i31-34nf-core-3-304-nx-w49sv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-16-x1607ca-ultra-5-225h-mb387w</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:58:22</t>
+          <t>2026-09-14 13:31:36</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook Go 14 E1404FA - EB012W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop HP OmniBook 7 14 fr0033TU - C1MN2PA (Ultra 5 225U, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>18790000</v>
+        <v>27490000</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>22990000</v>
+        <v>28990000</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 3.80 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Công suất đồ hoạ - TGP:: 15 - 25W | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 2600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Thunderbolt 4 with USB Type - C (hỗ trợ truyền dữ liệu, Power Delivery 3.1, DisplayPort 2.1,  HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB 3.2 gen 2 Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Poly Studio Dual speakers HP Audio Boost DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 4-cell, 64 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.65 mm - Rộng 31.4 mm - Dày 1.49 mm - 1.41 kg | Chất liệu:: Khung và mặt lưng kim loại, nhựa</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb012w</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-7-14-fr0033tu-ultra-5-225u-c1mn2pa</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:48:41</t>
+          <t>2026-09-14 15:57:56</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook Go 14 E1404FA - EB1832W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop HP OmniBook X Flip 14 fk0082AU - BZ7N8PA (R7 AI 350, 32GB, 1TB, 2K, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>18790000</v>
+        <v>39890000</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>22990000</v>
+        <v>40890000</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: 2K (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Corning Gorilla Glass 3 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB Type-C (hỗ trợ truyền dữ liệu, DisplayPort 2.1, Power delivery 3.1, HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E MT7922 Bluetooth 5.3 | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ | Thông tin Pin:: 3-cell Li-Po, 59 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 218.5 mm - Dày 14.6 mm - 1.39 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb1832w</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-x-flip-14-fk0082au-r7-ai-350-bz7n8pa</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:48:56</t>
+          <t>2026-09-14 15:58:11</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ893W (Core 3 304, 8GB, 512GB, Full HD, Win 11)</t>
+          <t>Laptop Lenovo Gaming Legion 5 15AHP11 - 83Q7001HVN (R7 250, 16GB, 512GB, RTX 5050 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>18990000</v>
+        <v>52990000</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>22990000</v>
+        <v>56990000</v>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Wildcat Lake - 304 | Số nhân:: 5 | Số luồng:: 5 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.30 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 15 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits Chứng nhận TÜV Rheinland | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.7 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Boost Clock 2662MHz, TGP 115W, 440 AI TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: 2.5K | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: DisplayHDR True Black 1000 | Cổng giao tiếp:: 1x Ethernet 2 x USB Type-C (USB4 40Gbps) hỗ trợ USB PD 65 - 100W và DisplayPort 1.4 1 x Headphone/ Microphone combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) 2×2 Bluetooth 6.0 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 244.5 mm - Rộng 344 mm - Dày 19~20 - 1.87 kg | Chất liệu:: Mặt trên: nhôm + Mặt dưới: nhựa PC-ABS</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-15-x1504ma-core-3-304-bq893w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15ahp11-r7-250-83q7001hvn</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:49:09</t>
+          <t>2026-09-14 15:58:24</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook S 16 S3607VA - RP155W (Core 5 210H, 16GB, 512GB, Full HD+ 144Hz, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002NVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>26990000</v>
+        <v>22990000</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>34990000</v>
+        <v>29990000</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
@@ -3905,103 +3893,103 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare LED Backlit | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 259.6 mm - Dày 15.9 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-s-16-s3607va-core-5-210h-rp155w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002nvn</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:49:22</t>
+          <t>2026-09-14 15:58:38</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook S14 S3407VA - LY256W (Core 7 240H, 16GB, 512GB, WUXGA OLED, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002PVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>26990000</v>
+        <v>19190000</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>29990000</v>
+        <v>25990000</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 17.9 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-s14-s3407va-core-7-240h-ly256w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002pvn</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:49:36</t>
+          <t>2026-09-14 15:58:52</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Zenbook 14 UM3406GA - QD075W (R7 AI 445, 16GB, 512GB, WUXGA OLED, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00A8VN (Core 3 304, 8GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>34590000</v>
+        <v>17490000</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>39990000</v>
+        <v>23990000</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-27%</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.0 GHz | NPU:: AMD XDNA | Card màn hình:: Card tích hợp | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 70% Less harmful blue light 400 nits 600 nits (Khi bật HDR) | Cổng giao tiếp:: 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 75 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.01 mm - Rộng 31.24 mm - Dày 1.49 mm - 1.2 kg | Chất liệu:: Nhôm nguyên khối</t>
+          <t>Công nghệ CPU:: Intel Core™ 3 - 304 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz (P-core), Turbo tối đa 4.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 2242 PCIe 4.0x4 NVMe | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 × USB-C (USB 5 Gbps), hỗ trợ USB PD 45–65W và DisplayPort 1.2 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Optimized with Dolby Audio 2W x 2 High Definition (HD) Audio Stereo speakers | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 240 mm - Rộng 343 mm - Dày 17 - 18 - 1.59 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-zenbook-14-um3406ga-r7-ai-445-qd075w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-3-304-83rr00a8vn</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4011,236 +3999,236 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:49:49</t>
+          <t>2026-09-14 15:59:05</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC14250-C3U085W11SLU-2Y (Core 3 100U, 8GB, 512GB, Full HD+, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00AAVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>21490000</v>
+        <v>22990000</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>22590000</v>
+        <v>29990000</v>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-23%</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-3-100u-dc14250-c3u085w11slu-2y</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00aavn</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:50:02</t>
+          <t>2026-09-14 15:59:18</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC4C5375W1-2Y (Core 5 120U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+          <t>Laptop Lenovo Ideapad Slim 3 15IWC11 - 83RR00CVVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>28990000</v>
+        <v>19190000</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>32090000</v>
+        <v>25990000</v>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226 mm - Dày 18 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-5-120u-dc4c5375w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00cvvn</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:50:17</t>
+          <t>2026-09-14 15:59:32</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - 71100515 (Core 7 150U, 16GB, 512GB, Full HD+ 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US0040VN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
+        <v>23690000</v>
+      </c>
+      <c r="C86" s="2" t="n">
         <v>31990000</v>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>35490000</v>
-      </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 320 mm - Rộng 215.97 mm - Dày 18.02 mm - 1.83 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 x USB-C (USB 5Gbps), with USB PD 45-65W and DisplayPort 1.2 1x Headphone / microphone combo jack (3.5 mm) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 18 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-71100515</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-5-322-83us0040vn</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:50:30</t>
+          <t>2026-09-14 15:59:45</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC14250-C7U161W11SLU-2Y (Core 7 150U, 16GB, 1TB, Full HD+ ,OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US003YVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>34990000</v>
+        <v>28990000</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>37990000</v>
+        <v>36990000</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 PCIe Gen 4 x 4 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (M.2 2230)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-dc14250-c7u161w11slu-2y</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us003yvn</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:50:44</t>
+          <t>2026-09-14 15:59:59</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - 71100520 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14IPH11 - 83S5004FVN (Ultra 7 355, 16GB, 512GB, WUXGA OLED, Win11)</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>21490000</v>
+        <v>34990000</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>22590000</v>
+        <v>37990000</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort 1.4, Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Bluetooth 5.0 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-71100520</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14iph11-ultra-7-355-83s5004fvn</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:50:58</t>
+          <t>2026-09-14 16:00:14</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - CPH993 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo ThinkBook 14 G9 - 21V0005PVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>21490000</v>
+        <v>33390000</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>22590000</v>
+        <v>35290000</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
@@ -4249,41 +4237,41 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: Đang cập nhật | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 70% Less harmful blue light 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 16.96 mm đến 18.99 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-cph993</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-g9-r7-250-21v0005pvn</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:51:12</t>
+          <t>2026-09-14 16:00:29</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC5C3259W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+          <t>Laptop Lenovo ThinkBook 14 Gen 9 IRL - 21UY008TVN (i5 13420H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>21490000</v>
+        <v>31190000</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>22590000</v>
+        <v>32890000</v>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
@@ -4292,263 +4280,275 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3259w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-gen-9-irl-i5-13420h-21uy008tvn</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:51:26</t>
+          <t>2026-09-14 16:00:43</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC5C3851W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo ThinkBook 16 G9 - 21UT005MVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>21490000</v>
+        <v>30190000</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>22590000</v>
+        <v>31590000</v>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x Headphone/ Microphone combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 2 x USB 2.0 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 235 mm - Rộng 358.5 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356 mm - Rộng 253.5 mm - Dày 17.5 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3851w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-16-g9-r7-250-21ut005mvn</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:51:39</t>
+          <t>2026-09-14 16:00:57</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15255 - DC5R5973W1-2Y (R5 7530U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+          <t>Laptop Lenovo ThinkPad E14 - 21T90025VN (Gen 7 Core 7 240H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>23990000</v>
+        <v>34190000</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>25690000</v>
+        <v>35590000</v>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 7530U | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/microphone combo 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: P-core 2.5/ 5.2 GHz, E-core 1.8/ 4.0 GHz | Card màn hình:: Card tích hợp - Integrated Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare 300 nits | Cổng giao tiếp:: 1x USB-A (USB 10Gbps / USB 3.2 Gen 2), Always On 1x Headphone / microphone combo jack (3.5 mm) 1x USB-C® (Thunderbolt™ 4 / USB4® 40 Gbps), with USB PD 15-65W and DisplayPort™ 2.1 1x HDMI® 2.1, up to 4K/6 0Hz 1x Ethernet (RJ-45) 1x USB-A (USB 5 Gbps / USB 3.2 Gen 1) | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: FHD 1080p + IR Hybrid with Privacy Shutter | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Stereo speakers, 2W x2, Dolby Atmos®, audio by HARMAN 2x, Array | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ Discrete TPM 2.0 Enabled | Thông tin Pin:: 3-cell, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 04/2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 10.1/15.25 (front/rear), 19.7 (maximum) mm - 1.34 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r5-7530u-dc5r5973w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-core-7-240h-21t90025vn</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:51:53</t>
+          <t>2026-09-14 16:01:12</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15255 - X9YM42 (R7 7730U, 16GB, 1TB, Full HD 120Hz, OfficeH24+36, Win11)</t>
+          <t>Laptop Lenovo ThinkPad E14 - 21SX002YVN (Gen 7 Ultra 255H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>29890000</v>
+        <v>39190000</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>30590000</v>
+        <v>40590000</v>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 8 x 2.0 GHz | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Bluetooth 5.0 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.635 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.10 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140T | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 1x USB-A (USB 10Gbps / USB 3.2 Gen 2), Always On 1x HDMI® 2.1, up to 4K/60 Hz 1x Headphone / microphone combo jack (3.5 mm) 1x USB-C® (Thunderbolt™ 4 / USB4® 40 Gbps), with USB PD 15-65W and DisplayPort™ 2.1 1x Ethernet (RJ-45) 1x USB-A (USB 5 Gbps / USB 3.2 Gen 1) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD 1080p + IR Hybrid with Privacy Shutter | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Stereo speakers, 2W x2, Dolby Atmos®, audio by HARMAN 2x, Array | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 04/2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 10.1/15.25 (front/rear), 19.7 (maximum) mm - 1.34 kg | Chất liệu:: Vỏ kim loại - Nhôm</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r7-7730u-x9ym42</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-255h-21sx002yvn</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:52:06</t>
+          <t>2026-09-14 16:01:26</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 16 DC16250 - 71100513 (Core 5 120U, 16GB, 1TB, Full HD+, OfficeH24+365B, Win11)</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr"/>
-      <c r="C94" s="2" t="inlineStr"/>
-      <c r="D94" s="2" t="inlineStr"/>
-      <c r="E94" s="2" t="inlineStr"/>
+          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX005NVN (Ultra 5 225U, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>36490000</v>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>38390000</v>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits eDP Wide View Angle | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2W x 2 Realtek ALC3254 Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 05/2025 | Kích thước:: Dài 357.3 mm - Rộng 250.6 mm - Dày 18.23 mm - 2 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4 với USB Power Delivery và DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-5-120u-71100513</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-225u-21sx005nvn</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:52:20</t>
+          <t>2026-09-14 16:01:39</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell Pro 15 Essential PV15250 - PV15250-100U-8512W-2Y (Core 3 100U, 8GB, 512GB, Full HD, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo ThinkPad X9 14 Gen 1 - 21QA006JVN (Ultra 7 258V, 32GB, 512GB, WUXGA OLED, Win11Pro)</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>22490000</v>
+        <v>53790000</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>23990000</v>
+        <v>55190000</v>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Rộng 358.5 mm - Dày 17.5 mm | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.80 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Chống chói Anti Glare Dolby Vision 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm HDMI 2.1 2 x USB-C (hỗ trợ Thunderbolt 4/USB 4, USB Power Delivery và DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.8 mm - Rộng 212.3 mm - Dày 17.18 mm - 1.21 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-pro-15-essential-pv15250-core-3-100u-pv15250-100u-8512w-2y</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-x9-14-gen-1-ultra-7-258v-21qa006jvn</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:52:34</t>
+          <t>2026-09-14 16:01:54</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP Gaming HyperX Omen 15 ga0092TX - D72D8PA (i5 14450HX, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
+          <t>Laptop Lenovo V14 G5 - 83HD0035VN (Core7 240H, 16G, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>45590000</v>
+        <v>31290000</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>46990000</v>
+        <v>32690000</v>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 421 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.37 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) LAN (RJ45) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Ion, 47 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324.2 mm - Rộng 215.2 mm - Dày 17.9 mm - 1.37 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-gaming-hyperx-omen-15-ga0092tx-i5-14450hx-d72d8pa</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-v14-g5-core7-240h-83hd0035vn</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -4558,40 +4558,40 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:52:45</t>
+          <t>2026-09-14 16:02:08</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP HyperX Omen 15 ga0091TX - D72D7PA (i5 14450HX, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
+          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002LVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>48590000</v>
+        <v>38490000</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>49990000</v>
+        <v>44990000</v>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3840 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 614 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.363 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-hyperx-omen-15-ga0091tx-i5-14450h-d72d7pa</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-5-322-83tc002lvn</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:53:00</t>
+          <t>2026-09-14 16:02:23</t>
         </is>
       </c>
     </row>

--- a/laptop_tgdd_all.xlsx
+++ b/laptop_tgdd_all.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I97"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -492,1292 +492,1304 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook Go 14 E1404FA - EB012W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-977M - NX.W26SV.001 (Ultra 9 185H, 16GB, 512GB, Full HD+, Win11)</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>18790000</v>
+        <v>29990000</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>22990000</v>
+        <v>31990000</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 9 Meteor Lake - 185H | Số luồng:: 22 | Tốc độ CPU:: 2.30 GHz (Lên đến 5.10 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (1 khe onboard) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB Type-C (65W) 1 x USB Type-C LAN (RJ45) HDMI 2.1 USB Type-C | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Stereo speakers | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 10 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.6 mm - Rộng 227.7 mm - Dày 17.9 mm - 1.49 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb012w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-go-14-ai-ag14-i71m-977m-ultra-9-185h-nx-w26sv-001</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:18:06</t>
+          <t>2026-09-15 12:15:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook Go 14 E1404FA - EB1832W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR - NX.X0PSV.002 (Ryzen 5 3500U, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>18790000</v>
+        <v>17990000</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>22990000</v>
+        <v>20990000</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 3500U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz | Card màn hình:: Card tích hợp - AMD Radeon Vega Mobile Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 2400 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: IPS LED-backlit TFT LCD Wide viewing angle 250 nits | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A HDMI 1 x SuperSpeed USB Type-C (hỗ trợ DisplayPort 1.4) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP FHD 1080p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: 2 loa 2 microphones | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Phím Copilot | Thông tin Pin:: 2-cell Li-ion, 45.6 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 210.2 mm - Rộng 322.6 mm - Dày 19.8 mm - 1.3 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb1832w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-nx-x0psv-002</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:18:19</t>
+          <t>2026-09-15 12:15:14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ893W (Core 3 304, 8GB, 512GB, Full HD, Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN - NX.DDASV.001 (Core 3 N350, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>17990000</v>
+        <v>16990000</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>22990000</v>
+        <v>18990000</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-22%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Wildcat Lake - 304 | Số nhân:: 5 | Số luồng:: 5 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.30 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 15 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits Chứng nhận TÜV Rheinland | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.7 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - N350 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 3.90 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB 3.2 HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.0 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.8 mm - Rộng 235.6 mm - Dày 19.7 mm - 1.53 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-15-x1504ma-core-3-304-bq893w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-36p-30tn-core-3-n350-nx-ddasv-001</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:18:32</t>
+          <t>2026-09-15 12:15:28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook S 16 S3607VA - RP155W (Core 5 210H, 16GB, 512GB, Full HD+ 144Hz, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 - NX.X0RSV.001 (Ryzen 5 3500U, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>26990000</v>
+        <v>17990000</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>34990000</v>
+        <v>20990000</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare LED Backlit | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 259.6 mm - Dày 15.9 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 3500U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz | Card màn hình:: Card tích hợp - AMD Radeon Vega Mobile Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 2400 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: IPS Màn hình Wide View Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A HDMI 1 x SuperSpeed USB Type-C (hỗ trợ DisplayPort 1.4) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP FHD 1080p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: 2 loa 2 microphones | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Phím Copilot | Thông tin Pin:: 2-cell Li-ion, 45.6 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 229.3 mm - Rộng 357.4 mm - Dày 19.85 mm - 1.5 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-s-16-s3607va-core-5-210h-rp155w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-nx-x0rsv-001</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:18:45</t>
+          <t>2026-09-15 12:15:42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook S14 S3407VA - LY256W (Core 7 240H, 16GB, 512GB, WUXGA OLED, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-44P-R4UH - NX.DJVSV.002 (R7 7730U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>26990000</v>
+        <v>21990000</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>29990000</v>
+        <v>23990000</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 17.9 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB Type - C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 230.2 mm - Dày 18.6 mm - 1.49 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-s14-s3407va-core-7-240h-ly256w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-44p-r4uh-r7-7730u-nx-djvsv-002</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:18:59</t>
+          <t>2026-09-15 12:15:55</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Zenbook 14 UM3406GA - QD075W (R7 AI 445, 16GB, 512GB, WUXGA OLED, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC - NX.DG3SV.002.16G (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>34590000</v>
+        <v>21990000</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>39990000</v>
+        <v>24990000</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.0 GHz | NPU:: AMD XDNA | Card màn hình:: Card tích hợp | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 70% Less harmful blue light 400 nits 600 nits (Khi bật HDR) | Cổng giao tiếp:: 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 75 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.01 mm - Rộng 31.24 mm - Dày 1.49 mm - 1.2 kg | Chất liệu:: Nhôm nguyên khối</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 357.6 mm - Rộng 228.5 mm - Dày 18.7 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-zenbook-14-um3406ga-r7-ai-445-qd075w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-53p-56ec-core-5-120u-nx-dg3sv-002-16g</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:19:13</t>
+          <t>2026-09-15 12:16:09</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC14250-C3U085W11SLU-2Y (Core 3 100U, 8GB, 512GB, Full HD+, OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Aspire Lite 16 AL16-71P-582Q - NX.DRSSV.001 (Ultra 5 125H, 16GB, 512GB, Full HD+ 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>21490000</v>
+        <v>24990000</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>22590000</v>
+        <v>26990000</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 125H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357 mm - Rộng 245.5 mm - Dày 18.9 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-3-100u-dc14250-c3u085w11slu-2y</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-16-al16-71p-582q-ultra-5-125h-nx-drssv-001</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:19:27</t>
+          <t>2026-09-15 12:16:22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC4C5375W1-2Y (Core 5 120U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+          <t>Laptop Acer Gaming Aspire 7 A715-59G-59RD - NH.DXUSV.001 (Core 5 210H, 16GB, 512GB, RTX 3050 4GB, Fulll HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>28990000</v>
+        <v>26990000</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>32090000</v>
+        <v>31990000</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226 mm - Dày 18 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 4 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35W - 80W | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 4 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle 350 nits Acer ComfyView | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C (hỗ trợ DisplayPort 1.4) LAN (RJ45) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn LED - 15 chế độ màu | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 359.5 mm - Rộng 238 mm - Dày 22.7 mm - 1.99 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-5-120u-dc4c5375w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-aspire-7-a715-59g-59rd-core-5-210h-nh-dxusv-001</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:19:40</t>
+          <t>2026-09-15 12:16:35</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - 71100515 (Core 7 150U, 16GB, 512GB, Full HD+ 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel AN16S-61-R9CN - NH.QXGSV.001 (Ryzen AI 7 350, 16GB, 512GB, RTX 5070 8GB, 2K+ 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>31990000</v>
+        <v>57990000</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>35490000</v>
+        <v>64990000</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 320 mm - Rộng 215.97 mm - Dày 18.02 mm - 1.83 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.0 GHz (Lên đến 5.2 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits 3ms | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: NVIDIA Optimus | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-71100515</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-an16s-61-r9cn-ryzen-ai-7-350-nh-qxgsv-001</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:19:53</t>
+          <t>2026-09-15 12:16:49</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC14250-C7U161W11SLU-2Y (Core 7 150U, 16GB, 1TB, Full HD+ ,OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-556L - NH.QZ9SV.006 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>34990000</v>
+        <v>38990000</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>37990000</v>
+        <v>40990000</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 PCIe Gen 4 x 4 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (M.2 2230)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 60W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 16:9 aspect ratio Ultra-slim design Mercury free, environment friendly Thời gian phản hồi: 3 ms LED-backlit TFT LCD Wide viewing angle 300 nits Acer ComfyView | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Ethernet (LAN) Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: 720p at 30 fps HD camera | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High SNR DAC 2.1 Vrms Hỗ trợ tai nghe đến 600 Ω Compatible with Cortana with Voice 2 microphones Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Tính năng khác:: NitroSense Key Copilot Key | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 239.89 mm - Rộng 362.3 mm - Dày 115.7/23.5 - 2.1 kg | Chất liệu:: Nhựa nguyên khối</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-dc14250-c7u161w11slu-2y</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-556l-core-5-210h-nh-qz9sv-006</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:20:07</t>
+          <t>2026-09-15 12:17:02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - 71100520 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-73Z8 - NH.QUASV.001 (Core 7 240H, 16GB, 512GB, RTX 4050 6GB, Full HD  180Hz, Win11)</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>21490000</v>
+        <v>35990000</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>22590000</v>
+        <v>39990000</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort 1.4, Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Bluetooth 5.0 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: IPS | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1x Ethernet 3 x USB 3.2 Gen 1 Type-A 1 x USB Type-C (65W) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: 720p at 30 fps HD camera Camera with Dual Microphone | Đèn bàn phím:: Đơn sắc - Màu cam | Công nghệ âm thanh:: Windows Spatial Sound High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-71100520</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-73z8-core-7-240h-nh-quasv-001</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:20:21</t>
+          <t>2026-09-15 12:17:16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - CPH993 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-78MD - NH.QZ9SV.007 (Core 7 240H, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>21490000</v>
+        <v>40990000</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>22590000</v>
+        <v>43990000</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: Đang cập nhật | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 70% Less harmful blue light 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 16.96 mm đến 18.99 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms 300 nits Acer ComfyView | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2 microphones Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Nhựa nguyên khối</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-cph993</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-78md-core-7-240h-nh-qz9sv-007</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:20:35</t>
+          <t>2026-09-15 12:17:30</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC5C3259W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-61-R0B8 - NH.QXQSV.001 (Ryzen AI 5 340, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>21490000</v>
+        <v>42990000</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>22590000</v>
+        <v>47990000</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.40 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3259w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-61-r0b8-ryzen-ai-5-340-nh-qxqsv-001</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:20:49</t>
+          <t>2026-09-15 12:17:43</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC5C3851W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-71-58WQ - NH.QXBSV.001 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, 2K+ 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>21490000</v>
+        <v>44990000</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>22590000</v>
+        <v>46990000</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x Headphone/ Microphone combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 2 x USB 2.0 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 235 mm - Rộng 358.5 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3851w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-71-58wq-core-5-210h-nh-qxbsv-001</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:21:03</t>
+          <t>2026-09-15 12:17:57</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15255 - DC5R5973W1-2Y (R5 7530U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+          <t>Laptop Acer Gaming Predator Helios Neo 16S PHN16S-I51-97T9 - NH.U3SSV.006 (Ultra 9 386H, 16GB, 512GB, RTX 5070 8GB, 2K+ 165Hz, Win11)</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>23990000</v>
+        <v>75990000</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>25690000</v>
+        <v>77990000</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 7530U | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/microphone combo 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 9 Panther Lake - 386H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 50 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: LED-backlit TFT LCD 500 nits Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 18.9 mm - 2.2 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r5-7530u-dc5r5973w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16s-phn16s-i51-97t9-ultra-9-386h</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:21:16</t>
+          <t>2026-09-15 12:18:11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15255 - X9YM42 (R7 7730U, 16GB, 1TB, Full HD 120Hz, OfficeH24+36, Win11)</t>
+          <t>Laptop Acer Nitro ProPanel AN16S-61-R7ZJ - NH.QXFSV.002 (R7 AI 350, 16GB, 512GB, RTX 5060 8GB, 2K, Win11)</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>29890000</v>
+        <v>49990000</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>30590000</v>
+        <v>51990000</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 8 x 2.0 GHz | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Bluetooth 5.0 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.635 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Nhôm &amp; Nhựa</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r7-7730u-x9ym42</t>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-an16s-61-r7zj-r7-ai-350-nhqxfsv002</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:21:29</t>
+          <t>2026-09-15 12:18:25</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 16 DC16250 - 71100513 (Core 5 120U, 16GB, 1TB, Full HD+, OfficeH24+365B, Win11)</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
+          <t>Laptop Acer Nitro ProPanel ANV15-52-50RB - NH.QUASV.002 (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, Full HD 180Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>33490000</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>37990000</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-12%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits eDP Wide View Angle | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2W x 2 Realtek ALC3254 Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 05/2025 | Kích thước:: Dài 357.3 mm - Rộng 250.6 mm - Dày 18.23 mm - 2 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 60W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 300 nits Acer ComfyView 3ms | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2 microphones Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Tính năng khác:: Copilot Key | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-5-120u-71100513</t>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv15-52-50rb-core-5-210h-nh-quasv-002</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:21:42</t>
+          <t>2026-09-15 12:18:39</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell Pro 15 Essential PV15250 - PV15250-100U-8512W-2Y (Core 3 100U, 8GB, 512GB, Full HD, OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Nitro ProPanel ANV16-72-782F - NH.QUPSV.001 (Core 7 240H, 16GB, 512GB, RTX 5050 8GB, Full HD+ 180 Hz, Win11)</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>22490000</v>
+        <v>43990000</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>23990000</v>
+        <v>45990000</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Rộng 358.5 mm - Dày 17.5 mm | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 80 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 360 mm - Rộng 274.5 mm - Dày 24.5 mm - 2.4 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-pro-15-essential-pv15250-core-3-100u-pv15250-100u-8512w-2y</t>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv16-72-782f-core-7-240h-nhqupsv001</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:21:56</t>
+          <t>2026-09-15 12:18:52</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP Gaming HyperX Omen 15 ga0092TX - D72D8PA (i5 14450HX, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
+          <t>Laptop Acer Nitro ProPanel ANV16S-61-R7KQ - NH.QXPSV.001 (R5 AI 340, 16GB, 512GB, RTX 5060 8GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45590000</v>
+        <v>46990000</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46990000</v>
+        <v>48990000</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 421 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.37 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 400 nits | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB Type C 3.2 Gen 2 (Hỗ trợ Power Delivery và DisplayPort™ 2.1) LAN (RJ45) HDMI 2.1 3 x USB A | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD 1080p Camera IR | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Hi-Res certification Spatial Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-gaming-hyperx-omen-15-ga0092tx-i5-14450hx-d72d8pa</t>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv16s-61-r7kq-r5-ai-340-nhqxpsv001</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:22:08</t>
+          <t>2026-09-15 12:19:06</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP HyperX Omen 15 ga0091TX - D72D7PA (i5 14450HX, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
+          <t>Laptop Acer Swift Air 14 SFA14-I31-34NF - NX.W49SV.001 (Core 3 304, 12GB, 512GB, WUXGA 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>48590000</v>
+        <v>21990000</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>49990000</v>
+        <v>23990000</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3840 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 614 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.363 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - 304 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 12 GB | Loại RAM:: LPDDR5 (1 khe onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Wide viewing angle 350 nits LED Backlight Acer ComfyView | Cổng giao tiếp:: 1 x USB 3.2 2 x USB Type-C (hỗ trợ USB, Power Delivery, DisplayPort và Thunderbolt 4) | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.3 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.99 mm - Rộng 222.65 mm - Dày 12.99 mm - 1.19 kg | Chất liệu:: Khung và mặt lưng kim loại</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-hyperx-omen-15-ga0091tx-i5-14450h-d72d7pa</t>
+          <t>https://www.thegioididong.com/laptop/acer-swift-air-14-sfa14-i31-34nf-core-3-304-nx-w49sv-001</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:22:21</t>
+          <t>2026-09-15 12:19:20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002MVN (Ultra 7 355, 32GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Swift Air 14 SFA14-I31-52BV - NX.W49SV.002 (Core 5 320, 12GB, 512GB, Full HD 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>55990000</v>
+        <v>24990000</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>64990000</v>
+        <v>26990000</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.95 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Đang cập nhật | RAM:: 12 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 350 nits | Cổng giao tiếp:: 1 x USB 3.2 2 x USB Type-C (hỗ trợ USB, Power Delivery, DisplayPort và Thunderbolt 4) | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.3 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 222.65 mm - Rộng 222.65 mm - Dày 12.99 mm - 1.19 kg | Chất liệu:: Khung và mặt lưng kim loại</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-7-355-83tc002mvn</t>
+          <t>https://www.thegioididong.com/laptop/acer-swift-air-14-sfa14-i31-52bv-core-5-320-nx-w49sv-002</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:03:16</t>
+          <t>2026-09-15 12:19:34</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 - 83QM0075VN (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Swift Go AI SFG14-75-5264 - NX.JNBSV.001 (Ultra 5 226V, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>40990000</v>
+        <v>29990000</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46990000</v>
+        <v>31990000</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe 600nits (peak) Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 70 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 04/2026 | Kích thước:: Dài 221 mm - Rộng 312 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Lunar Lake - 226V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 3.50 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 40 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 130V | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: OLED | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe ACER CineCrystal 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 2 x USB4 Type-C (hỗ trợ truyền dữ liệu, DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 65Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 227.4 mm - Rộng 312.4 mm - Dày 15.95 mm - 1.24 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-14iph11-ultra-7-355-83qm0075vn</t>
+          <t>https://www.thegioididong.com/laptop/acer-swift-go-ai-sfg14-75-5264-ultra-5-226v-nxjnbsv001</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:03:30</t>
+          <t>2026-09-15 12:19:47</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 - 83QM0076VN (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
+          <t>Laptop HP OmniBook 5 14 hh0075TU - D72CTPA (Ultra 5 322, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>40990000</v>
+        <v>35990000</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46990000</v>
+        <v>36690000</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.00 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Khoảng 13 TOPS (NPU); tổng nền tảng AI của Intel đạt khoảng 99 TOPS (CPU + GPU + NPU) | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: 4 Xe-Cores | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7467 MT/s | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB PCIe 4.0 NVMe SSD | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: OLED Chuẩn DisplayHDR True Black 600 Low Blue Light Eyesafe Dolby Vision | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 2 x Thunderbolt 4 USB-C HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Chốt khóa webcam FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hệ thống quạt kép (Dual Fan) | Tính năng khác:: TPM 2.0 | Thông tin Pin:: 70 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 221 mm - Rộng 312 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Vỏ hợp kim Nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.90 GHz (Lên đến 4.40 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 2 x Thunderbolt 4 (hỗ trợ truyền dữ liệu,Power Delivery,DisplayPort,HP Sleep and Charge) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 59.16 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 217.5 mm - Dày 13.6 mm - 1.337 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-14iph11-ultra-7-355-83qm0076vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-5-14-hh0075tu-ultra-5-322-d72ctpa</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:03:44</t>
+          <t>2026-09-15 13:11:37</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK0015VN (Ultra 7 355, 32GB, 1TB, WQXGA+ 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop HP OmniBook 7 14 fr0033TU - C1MN2PA (Ultra 5 225U, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>62990000</v>
+        <v>27490000</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>72990000</v>
+        <v>28990000</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe 4.0x4 NVMe (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: 500 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.6 mm - Rộng 213.8 mm - Dày 13.9 mm - 0.975 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 3.80 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Công suất đồ hoạ - TGP:: 15 - 25W | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 2600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Thunderbolt 4 with USB Type - C (hỗ trợ truyền dữ liệu, Power Delivery 3.1, DisplayPort 2.1,  HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB 3.2 gen 2 Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Poly Studio Dual speakers HP Audio Boost DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 4-cell, 64 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.65 mm - Rộng 31.4 mm - Dày 1.49 mm - 1.41 kg | Chất liệu:: Khung và mặt lưng kim loại, nhựa</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-7-355-83qk0015vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-7-14-fr0033tu-ultra-5-225u-c1mn2pa</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:03:58</t>
+          <t>2026-09-15 13:11:51</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK006GVN (Ultra 7 355, 32GB, 1TB, WQXGA+ 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop HP OmniBook Ultra 14 kd0036TU - D72C6PA (Ultra 9 386H, 32GB, 1TB, 3K OLED 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>64990000</v>
+        <v>65190000</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>66990000</v>
+        <v>65890000</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe 4.0x4 NVMe (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Eyesafe DisplayHDR True Black 1000 500 nits Corning Gorilla Glass 3 Dolby Vision PureSight Pro Flicker Free 1100 nits (peak) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.6 mm - Rộng 213.8 mm - Dày 13.9 mm - 0.975 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 9 Panther Lake - 386H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: up to 120 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light 500 nits Corning Gorilla Glass 3 | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery 3.1, DisplayPort 2.1) 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.1 mm - Rộng 215.6 mm - Dày 10.7 mm - 1.282 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-7-355-83qk006gvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-ultra-14-kd0036tu-ultra-9-386h-d72c6pa</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:04:12</t>
+          <t>2026-09-15 13:12:04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK009PVN (Ultra X9 378H, 32GB, 1TB, WQXGA+ 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop HP OmniBook Ultra 14 kd0039TU - D72C7PA (Ultra 7 356H, 32GB, 1TB, 3K OLED 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>68990000</v>
+        <v>59190000</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>79990000</v>
+        <v>59890000</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra X9 - 378H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.00 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 32 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 9600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe® 4.0x4 NVMe® (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Eyesafe 500 nits typical DisplayHDR True Black 1000 Corning Gorilla Glass 3 500 nits Glossy Dolby Vision PureSight Pro Flicker Free 1100 nits (peak) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 18/05/2026 | Kích thước:: Dài 213.8 mm - Rộng 312.6 mm - Dày 13.9 mm - 0.975 kg</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 356H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz (Lên đến 4.7 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: up to 120 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 500 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery 3.1, DisplayPort 2.1) 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.1 mm - Rộng 215.6 mm - Dày 10.7 mm - 1.288 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-x9-378h-83qk009pvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-ultra-14-kd0039tu-ultra-7-356h-d72c7pa</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:04:26</t>
+          <t>2026-09-15 13:12:17</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 Black Edition A13VEO - 2610VN (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop HP OmniBook X Flip 14 fk0082AU - BZ7N8PA (R7 AI 350, 32GB, 1TB, 2K, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>27890000</v>
+        <v>39890000</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>31990000</v>
+        <v>40890000</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell, 53.5Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 250.3 mm - Dày 22.9 mm - 1,.98 | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: 2K (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Corning Gorilla Glass 3 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB Type-C (hỗ trợ truyền dữ liệu, DisplayPort 2.1, Power delivery 3.1, HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E MT7922 Bluetooth 5.3 | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ | Thông tin Pin:: 3-cell Li-Po, 59 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 218.5 mm - Dày 14.6 mm - 1.39 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-black-edition-a13veo-i5-13420h-2610vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-x-flip-14-fk0082au-r7-ai-350-bz7n8pa</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:04:39</t>
+          <t>2026-09-15 13:12:31</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 Black Edition A13VEO - 2608VN (i7 13620H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop HP ProBook 4 G1a 14 - D9CP7AT (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>29890000</v>
+        <v>30590000</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>33990000</v>
+        <v>31990000</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 1.8 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell, 53.5Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 250.3 mm - Dày 22.9 mm - 1,.98 | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB Type-C (hỗ trợ cổng Thunderbolt 4) LAN (RJ45) 2 x USB 3.2 Gen 2 Type-C (hỗ trợ Power Delivery 3.0, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) | Webcam:: Camera HP FHD, tích hợp màn che và micro kép | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: fTPM 2.0 TPM Embedded Security Smart Cover Secure Platform Management (SPM) Secure Boot Configuration POST Power-On Password Microsoft Pluton Processor BIOS Sure Start AMD PSP 11.0 Device Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hard Drive Utilities | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 31.86 cm - Rộng 22.43 cm - Dày 1.70 cm - 1.465 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-black-edition-a13veo-i7-13620h-2608vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-probook-4-g1a-14-r7-250-d9cp7at</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:04:52</t>
+          <t>2026-09-15 13:12:45</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 C13WEO - 418VN (i5 13420H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop HP Probook 4 G1ah 16 - D9CP8AT (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>30990000</v>
+        <v>30590000</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>34990000</v>
+        <v>31990000</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 70 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 1.982 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (2280) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI 2 x USB 3.2 Gen 2 Type-C (hỗ trợ Power Delivery 3.0, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) | Webcam:: Camera HP FHD, tích hợp màn che và micro kép | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM Embedded Security Smart Cover Secure Platform Management (SPM) Secure Boot Configuration POST Power-On Password Microsoft Pluton Processor fTPM 2.0 BIOS Sure Start AMD PSP 11.0 Device Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hard Drive Utilities | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 35.94 cm - Rộng 25.1 cm - Dày 1.7 cm - 1.783 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-c13weo-i5-13420h-418vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-probook-4-g1ah-16-r7-250-d9cp8at</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:05:06</t>
+          <t>2026-09-15 13:12:59</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 Max C13WE - 422VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop HP ProBook 4 G2i 16 - DK2X9AT (Ultra 5 325, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>41590000</v>
+        <v>35190000</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>42990000</v>
+        <v>36590000</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x SuperSpeed USB Type-A LAN (RJ45) HDMI 2.1 2 x USB 3.2 1 x USB Type-C 3.2 (hỗ trợ Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: 3 ống đồng Cooler Boost 2 quạt | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 2 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 325 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell, 68.03 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.4 mm - Rộng 251 mm - Dày 17.5 mm - 1.848 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-max-c13we-422vn-i7-13620h</t>
+          <t>https://www.thegioididong.com/laptop/hp-probook-4-g2i-16-ultra-5-325-dk2x9at</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:05:19</t>
+          <t>2026-09-15 13:13:13</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 Max C13WF - 421VN (i7 13620H, 16GB, 512GB, RTX 5060 8GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop HP ProBook 4 G2i 16 - DK2Y5AT (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>43590000</v>
+        <v>39190000</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>44990000</v>
+        <v>40590000</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
@@ -1786,131 +1798,131 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x SuperSpeed USB Type-A LAN (RJ45) HDMI 2.1 2 x USB 3.2 1 x USB Type-C 3.2 (hỗ trợ Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: 3 ống đồng Cooler Boost 2 quạt | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 2 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell, 68.03 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.4 mm - Rộng 251 mm - Dày 17.5 mm - 1.846 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-max-c13wf-421vn-i7-13620h</t>
+          <t>https://www.thegioididong.com/laptop/hp-probook-4-g2i-16-ultra-7-355-dk2y5at</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:05:34</t>
+          <t>2026-09-15 13:13:26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Gaming Cyborg 15 C13WEO-417VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Lenovo Gaming Legion 5 15AHP11 - 83Q7001HVN (R7 250, 16GB, 512GB, RTX 5050 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>34590000</v>
+        <v>52990000</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>36990000</v>
+        <v>56990000</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - Intel UHD Graphics (tích hợp) + NVIDIA GeForce RTX 5050 GPU, 8GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB Type-A 1 x Headphone/ Microphone combo audio jack 1 x USB Type C (chỉ hỗ trợ Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: DTS Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.98 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Boost Clock 2662MHz, TGP 115W, 440 AI TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: 2.5K | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: DisplayHDR True Black 1000 | Cổng giao tiếp:: 1x Ethernet 2 x USB Type-C (USB4 40Gbps) hỗ trợ USB PD 65 - 100W và DisplayPort 1.4 1 x Headphone/ Microphone combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) 2×2 Bluetooth 6.0 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 244.5 mm - Rộng 344 mm - Dày 19~20 - 1.87 kg | Chất liệu:: Mặt trên: nhôm + Mặt dưới: nhựa PC-ABS</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-c13weo-417vn-i7-13620h</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15ahp11-r7-250-83q7001hvn</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:05:49</t>
+          <t>2026-09-15 13:13:39</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14S G3MG-003VN (Core 5 320, 16GB, 1TB, Full HD+ 120Hz, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002NVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>27990000</v>
+        <v>22990000</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>31490000</v>
+        <v>29990000</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-23%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: SSD 1TB, chuẩn M.2 2280 NVMe PCIe Gen4, tối đa hỗ trợ 2TB | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 50% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 2 x USB 3.2 gen 1 Type-A LAN (RJ45) HDMI 2.1 2 x USB Type-C 3.2 Gen 2 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD card reader | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: DTS | Tản nhiệt:: 2 ống đồng 1 x Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.39 mm - Rộng 31.59 mm - Dày 1.11 ~ 1.79 - 1.45 kg | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-modern-14s-g3mg-003vn-core-5-320</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002nvn</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:03</t>
+          <t>2026-09-15 13:13:53</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1264VN (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002PVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>19990000</v>
+        <v>19190000</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>22390000</v>
+        <v>25990000</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1920,98 +1932,98 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core thế hệ 12 - 120U | Số nhân:: Hãng không công bố | Số luồng:: 12 | Tốc độ CPU:: 1.45 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (2280) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: Hãng không công bố | Cổng giao tiếp:: 3 x USB 3.2 Gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell, 46.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.7 kg | Chất liệu:: Plastic (nhựa dẻo)</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-modern-15-f1mg-1264vn-core-5-120u</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002pvn</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:18</t>
+          <t>2026-09-15 13:14:06</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Laptop SingPC M16-i382 (i3 1215U, 8GB, 256GB, WUXGA, Win11 Pro)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00A8VN (Core 3 304, 8GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>13490000</v>
+        <v>17490000</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>15190000</v>
+        <v>23990000</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-27%</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i3 Alder Lake - 1215U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.2GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 256 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core™ 3 - 304 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz (P-core), Turbo tối đa 4.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 2242 PCIe 4.0x4 NVMe | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 × USB-C (USB 5 Gbps), hỗ trợ USB PD 45–65W và DisplayPort 1.2 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Optimized with Dolby Audio 2W x 2 High Definition (HD) Audio Stereo speakers | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 240 mm - Rộng 343 mm - Dày 17 - 18 - 1.59 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/singpc-m16-i382-i3-1215u</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-3-304-83rr00a8vn</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:31</t>
+          <t>2026-09-15 13:14:19</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Laptop SingPC M16-i595 (i5 1235U, 16GB, 512GB, WUXGA, Win11 Pro)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00AAVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>17390000</v>
+        <v>22990000</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>19990000</v>
+        <v>29990000</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-23%</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Alder Lake - 1235U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 72% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/singpc-m16-i595-i5-1235u</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00aavn</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2021,408 +2033,408 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:44</t>
+          <t>2026-09-15 13:14:32</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-977M - NX.W26SV.001 (Ultra 9 185H, 16GB, 512GB, Full HD+, Win11)</t>
+          <t>Laptop Lenovo Ideapad Slim 3 15IWC11 - 83RR00CVVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>29990000</v>
+        <v>19190000</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>31990000</v>
+        <v>25990000</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 9 Meteor Lake - 185H | Số luồng:: 22 | Tốc độ CPU:: 2.30 GHz (Lên đến 5.10 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (1 khe onboard) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB Type-C (65W) 1 x USB Type-C LAN (RJ45) HDMI 2.1 USB Type-C | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Stereo speakers | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 10 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.6 mm - Rộng 227.7 mm - Dày 17.9 mm - 1.49 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-go-14-ai-ag14-i71m-977m-ultra-9-185h-nx-w26sv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00cvvn</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:54:42</t>
+          <t>2026-09-15 13:14:46</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR - NX.X0PSV.002 (Ryzen 5 3500U, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US0040VN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>17990000</v>
+        <v>23690000</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>20990000</v>
+        <v>31990000</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 3500U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz | Card màn hình:: Card tích hợp - AMD Radeon Vega Mobile Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 2400 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: IPS LED-backlit TFT LCD Wide viewing angle 250 nits | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A HDMI 1 x SuperSpeed USB Type-C (hỗ trợ DisplayPort 1.4) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP FHD 1080p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: 2 loa 2 microphones | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Phím Copilot | Thông tin Pin:: 2-cell Li-ion, 45.6 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 210.2 mm - Rộng 322.6 mm - Dày 19.8 mm - 1.3 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 x USB-C (USB 5Gbps), with USB PD 45-65W and DisplayPort 1.2 1x Headphone / microphone combo jack (3.5 mm) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 18 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-nx-x0psv-002</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-5-322-83us0040vn</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:54:57</t>
+          <t>2026-09-15 13:14:59</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN - NX.DDASV.001 (Core 3 N350, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US003YVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>16990000</v>
+        <v>28990000</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>18990000</v>
+        <v>36990000</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - N350 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 3.90 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB 3.2 HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.0 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.8 mm - Rộng 235.6 mm - Dày 19.7 mm - 1.53 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-36p-30tn-core-3-n350-nx-ddasv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us003yvn</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:55:11</t>
+          <t>2026-09-15 13:15:14</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 - NX.X0RSV.001 (Ryzen 5 3500U, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14IPH11 - 83S5004FVN (Ultra 7 355, 16GB, 512GB, WUXGA OLED, Win11)</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>17990000</v>
+        <v>34990000</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>20990000</v>
+        <v>37990000</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 3500U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz | Card màn hình:: Card tích hợp - AMD Radeon Vega Mobile Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 2400 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: IPS Màn hình Wide View Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A HDMI 1 x SuperSpeed USB Type-C (hỗ trợ DisplayPort 1.4) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP FHD 1080p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: 2 loa 2 microphones | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Phím Copilot | Thông tin Pin:: 2-cell Li-ion, 45.6 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 229.3 mm - Rộng 357.4 mm - Dày 19.85 mm - 1.5 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-nx-x0rsv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14iph11-ultra-7-355-83s5004fvn</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:55:24</t>
+          <t>2026-09-15 13:15:27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-44P-R4UH - NX.DJVSV.002 (R7 7730U, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Lenovo ThinkBook 14 G9 - 21V0005PVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>21990000</v>
+        <v>33390000</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>23990000</v>
+        <v>35290000</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB Type - C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 230.2 mm - Dày 18.6 mm - 1.49 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-44p-r4uh-r7-7730u-nx-djvsv-002</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-g9-r7-250-21v0005pvn</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:55:37</t>
+          <t>2026-09-15 13:15:40</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC - NX.DG3SV.002.16G (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Lenovo ThinkBook 14 Gen 9 IRL - 21UY008TVN (i5 13420H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>21990000</v>
+        <v>31190000</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>24990000</v>
+        <v>32890000</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 357.6 mm - Rộng 228.5 mm - Dày 18.7 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-53p-56ec-core-5-120u-nx-dg3sv-002-16g</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-gen-9-irl-i5-13420h-21uy008tvn</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:55:51</t>
+          <t>2026-09-15 13:15:53</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AL16-71P-582Q - NX.DRSSV.001 (Ultra 5 125H, 16GB, 512GB, Full HD+ 120Hz, Win11)</t>
+          <t>Laptop Lenovo ThinkBook 16 G9 - 21UT005MVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>24990000</v>
+        <v>30190000</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>26990000</v>
+        <v>31590000</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 125H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357 mm - Rộng 245.5 mm - Dày 18.9 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356 mm - Rộng 253.5 mm - Dày 17.5 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-16-al16-71p-582q-ultra-5-125h-nx-drssv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-16-g9-r7-250-21ut005mvn</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:56:05</t>
+          <t>2026-09-15 13:16:07</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Aspire 7 A715-59G-59RD - NH.DXUSV.001 (Core 5 210H, 16GB, 512GB, RTX 3050 4GB, Fulll HD 144Hz, Win11)</t>
+          <t>Laptop Lenovo ThinkPad E14 - 21T90025VN (Gen 7 Core 7 240H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>26990000</v>
+        <v>34190000</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>31990000</v>
+        <v>35590000</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 4 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35W - 80W | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 4 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle 350 nits Acer ComfyView | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C (hỗ trợ DisplayPort 1.4) LAN (RJ45) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn LED - 15 chế độ màu | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 359.5 mm - Rộng 238 mm - Dày 22.7 mm - 1.99 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 7 - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: P-core 2.5/ 5.2 GHz, E-core 1.8/ 4.0 GHz | Card màn hình:: Card tích hợp - Integrated Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare 300 nits | Cổng giao tiếp:: 1x USB-A (USB 10Gbps / USB 3.2 Gen 2), Always On 1x Headphone / microphone combo jack (3.5 mm) 1x USB-C® (Thunderbolt™ 4 / USB4® 40 Gbps), with USB PD 15-65W and DisplayPort™ 2.1 1x HDMI® 2.1, up to 4K/6 0Hz 1x Ethernet (RJ-45) 1x USB-A (USB 5 Gbps / USB 3.2 Gen 1) | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: FHD 1080p + IR Hybrid with Privacy Shutter | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Stereo speakers, 2W x2, Dolby Atmos®, audio by HARMAN 2x, Array | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ Discrete TPM 2.0 Enabled | Thông tin Pin:: 3-cell, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 04/2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 10.1/15.25 (front/rear), 19.7 (maximum) mm - 1.34 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-aspire-7-a715-59g-59rd-core-5-210h-nh-dxusv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-core-7-240h-21t90025vn</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:56:18</t>
+          <t>2026-09-15 13:16:22</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel AN16S-61-R9CN - NH.QXGSV.001 (Ryzen AI 7 350, 16GB, 512GB, RTX 5070 8GB, 2K+ 180Hz, Win11)</t>
+          <t>Laptop Lenovo ThinkPad E14 - 21SX002YVN (Gen 7 Ultra 255H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>57990000</v>
+        <v>39190000</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>64990000</v>
+        <v>40590000</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.0 GHz (Lên đến 5.2 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits 3ms | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: NVIDIA Optimus | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.10 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140T | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 1x USB-A (USB 10Gbps / USB 3.2 Gen 2), Always On 1x HDMI® 2.1, up to 4K/60 Hz 1x Headphone / microphone combo jack (3.5 mm) 1x USB-C® (Thunderbolt™ 4 / USB4® 40 Gbps), with USB PD 15-65W and DisplayPort™ 2.1 1x Ethernet (RJ-45) 1x USB-A (USB 5 Gbps / USB 3.2 Gen 1) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD 1080p + IR Hybrid with Privacy Shutter | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Stereo speakers, 2W x2, Dolby Atmos®, audio by HARMAN 2x, Array | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 04/2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 10.1/15.25 (front/rear), 19.7 (maximum) mm - 1.34 kg | Chất liệu:: Vỏ kim loại - Nhôm</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-an16s-61-r9cn-ryzen-ai-7-350-nh-qxgsv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-255h-21sx002yvn</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:56:31</t>
+          <t>2026-09-15 14:03:50</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-556L - NH.QZ9SV.006 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
+          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX005NVN (Ultra 5 225U, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>38990000</v>
+        <v>36490000</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>40990000</v>
+        <v>38390000</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
@@ -2431,533 +2443,533 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 60W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 16:9 aspect ratio Ultra-slim design Mercury free, environment friendly Thời gian phản hồi: 3 ms LED-backlit TFT LCD Wide viewing angle 300 nits Acer ComfyView | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Ethernet (LAN) Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: 720p at 30 fps HD camera | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High SNR DAC 2.1 Vrms Hỗ trợ tai nghe đến 600 Ω Compatible with Cortana with Voice 2 microphones Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Tính năng khác:: NitroSense Key Copilot Key | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 239.89 mm - Rộng 362.3 mm - Dày 115.7/23.5 - 2.1 kg | Chất liệu:: Nhựa nguyên khối</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4 với USB Power Delivery và DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-556l-core-5-210h-nh-qz9sv-006</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-225u-21sx005nvn</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:56:44</t>
+          <t>2026-09-15 14:04:03</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-73Z8 - NH.QUASV.001 (Core 7 240H, 16GB, 512GB, RTX 4050 6GB, Full HD  180Hz, Win11)</t>
+          <t>Laptop Lenovo ThinkPad X9 14 Gen 1 - 21QA006JVN (Ultra 7 258V, 32GB, 512GB, WUXGA OLED, Win11Pro)</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>35990000</v>
+        <v>53790000</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>39990000</v>
+        <v>55190000</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: IPS | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1x Ethernet 3 x USB 3.2 Gen 1 Type-A 1 x USB Type-C (65W) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: 720p at 30 fps HD camera Camera with Dual Microphone | Đèn bàn phím:: Đơn sắc - Màu cam | Công nghệ âm thanh:: Windows Spatial Sound High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.80 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Chống chói Anti Glare Dolby Vision 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm HDMI 2.1 2 x USB-C (hỗ trợ Thunderbolt 4/USB 4, USB Power Delivery và DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.8 mm - Rộng 212.3 mm - Dày 17.18 mm - 1.21 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-73z8-core-7-240h-nh-quasv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-x9-14-gen-1-ultra-7-258v-21qa006jvn</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:56:59</t>
+          <t>2026-09-15 14:04:17</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-78MD - NH.QZ9SV.007 (Core 7 240H, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
+          <t>Laptop Lenovo V14 G5 - 83HD0035VN (Core7 240H, 16G, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>40990000</v>
+        <v>31290000</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>43990000</v>
+        <v>32690000</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms 300 nits Acer ComfyView | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2 microphones Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Nhựa nguyên khối</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) LAN (RJ45) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Ion, 47 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324.2 mm - Rộng 215.2 mm - Dày 17.9 mm - 1.37 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-78md-core-7-240h-nh-qz9sv-007</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-v14-g5-core7-240h-83hd0035vn</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:57:13</t>
+          <t>2026-09-15 14:04:31</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-61-R0B8 - NH.QXQSV.001 (Ryzen AI 5 340, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
+          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002LVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>42990000</v>
+        <v>38490000</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>47990000</v>
+        <v>44990000</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.40 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-61-r0b8-ryzen-ai-5-340-nh-qxqsv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-5-322-83tc002lvn</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:57:27</t>
+          <t>2026-09-15 14:04:45</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-71-58WQ - NH.QXBSV.001 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, 2K+ 180Hz, Win11)</t>
+          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002MVN (Ultra 7 355, 32GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>44990000</v>
+        <v>55990000</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>46990000</v>
+        <v>64990000</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.95 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-71-58wq-core-5-210h-nh-qxbsv-001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-7-355-83tc002mvn</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:57:40</t>
+          <t>2026-09-15 14:04:58</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Predator Helios Neo 16S PHN16S-I51-97T9 - NH.U3SSV.006 (Ultra 9 386H, 16GB, 512GB, RTX 5070 8GB, 2K+ 165Hz, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 - 83QM0075VN (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>75990000</v>
+        <v>40990000</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>77990000</v>
+        <v>46990000</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 9 Panther Lake - 386H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 50 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: LED-backlit TFT LCD 500 nits Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 18.9 mm - 2.2 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe 600nits (peak) Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 70 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 04/2026 | Kích thước:: Dài 221 mm - Rộng 312 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16s-phn16s-i51-97t9-ultra-9-386h</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-14iph11-ultra-7-355-83qm0075vn</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:57:53</t>
+          <t>2026-09-15 14:05:13</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Nitro ProPanel AN16S-61-R7ZJ - NH.QXFSV.002 (R7 AI 350, 16GB, 512GB, RTX 5060 8GB, 2K, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 - 83QM0076VN (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>49990000</v>
+        <v>40990000</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>51990000</v>
+        <v>46990000</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Nhôm &amp; Nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.00 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Khoảng 13 TOPS (NPU); tổng nền tảng AI của Intel đạt khoảng 99 TOPS (CPU + GPU + NPU) | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: 4 Xe-Cores | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7467 MT/s | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB PCIe 4.0 NVMe SSD | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: OLED Chuẩn DisplayHDR True Black 600 Low Blue Light Eyesafe Dolby Vision | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 2 x Thunderbolt 4 USB-C HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Chốt khóa webcam FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hệ thống quạt kép (Dual Fan) | Tính năng khác:: TPM 2.0 | Thông tin Pin:: 70 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 221 mm - Rộng 312 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Vỏ hợp kim Nhôm</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-an16s-61-r7zj-r7-ai-350-nhqxfsv002</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-14iph11-ultra-7-355-83qm0076vn</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:58:07</t>
+          <t>2026-09-15 14:05:27</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Nitro ProPanel ANV15-52-50RB - NH.QUASV.002 (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, Full HD 180Hz, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK0015VN (Ultra 7 355, 32GB, 1TB, WQXGA+ 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>33490000</v>
+        <v>62990000</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>37990000</v>
+        <v>72990000</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 60W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 300 nits Acer ComfyView 3ms | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2 microphones Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Tính năng khác:: Copilot Key | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe 4.0x4 NVMe (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: 500 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.6 mm - Rộng 213.8 mm - Dày 13.9 mm - 0.975 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv15-52-50rb-core-5-210h-nh-quasv-002</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-7-355-83qk0015vn</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:58:20</t>
+          <t>2026-09-15 14:05:40</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Nitro ProPanel ANV16-72-782F - NH.QUPSV.001 (Core 7 240H, 16GB, 512GB, RTX 5050 8GB, Full HD+ 180 Hz, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK006GVN (Ultra 7 355, 32GB, 1TB, WQXGA+ 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>43990000</v>
+        <v>64990000</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>45990000</v>
+        <v>66990000</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 80 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 360 mm - Rộng 274.5 mm - Dày 24.5 mm - 2.4 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe 4.0x4 NVMe (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Eyesafe DisplayHDR True Black 1000 500 nits Corning Gorilla Glass 3 Dolby Vision PureSight Pro Flicker Free 1100 nits (peak) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.6 mm - Rộng 213.8 mm - Dày 13.9 mm - 0.975 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv16-72-782f-core-7-240h-nhqupsv001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-7-355-83qk006gvn</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:58:35</t>
+          <t>2026-09-15 14:05:54</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Nitro ProPanel ANV16S-61-R7KQ - NH.QXPSV.001 (R5 AI 340, 16GB, 512GB, RTX 5060 8GB, Full HD 180Hz, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK009PVN (Ultra X9 378H, 32GB, 1TB, WQXGA+ 120Hz, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46990000</v>
+        <v>68990000</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>48990000</v>
+        <v>79990000</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 400 nits | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB Type C 3.2 Gen 2 (Hỗ trợ Power Delivery và DisplayPort™ 2.1) LAN (RJ45) HDMI 2.1 3 x USB A | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD 1080p Camera IR | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Hi-Res certification Spatial Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra X9 - 378H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.00 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 32 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 9600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe® 4.0x4 NVMe® (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Eyesafe 500 nits typical DisplayHDR True Black 1000 Corning Gorilla Glass 3 500 nits Glossy Dolby Vision PureSight Pro Flicker Free 1100 nits (peak) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 18/05/2026 | Kích thước:: Dài 213.8 mm - Rộng 312.6 mm - Dày 13.9 mm - 0.975 kg</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv16s-61-r7kq-r5-ai-340-nhqxpsv001</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-x9-378h-83qk009pvn</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:58:49</t>
+          <t>2026-09-15 14:06:07</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Air 14 SFA14-I31-34NF - NX.W49SV.001 (Core 3 304, 12GB, 512GB, WUXGA 120Hz, Win11)</t>
+          <t>Laptop MSI Cyborg 15 Black Edition A13VEO - 2610VN (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>21990000</v>
+        <v>27890000</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>23990000</v>
+        <v>31990000</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - 304 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 12 GB | Loại RAM:: LPDDR5 (1 khe onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Wide viewing angle 350 nits LED Backlight Acer ComfyView | Cổng giao tiếp:: 1 x USB 3.2 2 x USB Type-C (hỗ trợ USB, Power Delivery, DisplayPort và Thunderbolt 4) | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.3 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.99 mm - Rộng 222.65 mm - Dày 12.99 mm - 1.19 kg | Chất liệu:: Khung và mặt lưng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell, 53.5Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 250.3 mm - Dày 22.9 mm - 1,.98 | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-swift-air-14-sfa14-i31-34nf-core-3-304-nx-w49sv-001</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-black-edition-a13veo-i5-13420h-2610vn</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:59:03</t>
+          <t>2026-09-15 14:06:21</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Air 14 SFA14-I31-52BV - NX.W49SV.002 (Core 5 320, 12GB, 512GB, Full HD 120Hz, Win11)</t>
+          <t>Laptop MSI Cyborg 15 Black Edition A13VEO - 2608VN (i7 13620H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>24990000</v>
+        <v>29890000</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>26990000</v>
+        <v>33990000</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Đang cập nhật | RAM:: 12 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 350 nits | Cổng giao tiếp:: 1 x USB 3.2 2 x USB Type-C (hỗ trợ USB, Power Delivery, DisplayPort và Thunderbolt 4) | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.3 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 222.65 mm - Rộng 222.65 mm - Dày 12.99 mm - 1.19 kg | Chất liệu:: Khung và mặt lưng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 1.8 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell, 53.5Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 250.3 mm - Dày 22.9 mm - 1,.98 | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-swift-air-14-sfa14-i31-52bv-core-5-320-nx-w49sv-002</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-black-edition-a13veo-i7-13620h-2608vn</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:27:18</t>
+          <t>2026-09-15 14:06:34</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go AI SFG14-75-5264 - NX.JNBSV.001 (Ultra 5 226V, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop MSI Cyborg 15 C13WEO - 418VN (i5 13420H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>29990000</v>
+        <v>30990000</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>31990000</v>
+        <v>34990000</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Lunar Lake - 226V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 3.50 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 40 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 130V | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: OLED | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe ACER CineCrystal 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 2 x USB4 Type-C (hỗ trợ truyền dữ liệu, DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 65Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 227.4 mm - Rộng 312.4 mm - Dày 15.95 mm - 1.24 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 70 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 1.982 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-swift-go-ai-sfg14-75-5264-ultra-5-226v-nxjnbsv001</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-c13weo-i5-13420h-418vn</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2967,107 +2979,107 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:27:32</t>
+          <t>2026-09-15 14:06:48</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go AI SFG14-75-765M - NX.JNBSV.004 (Ultra 7 258V, 32GB, 512GB, Full HD+, Win11)</t>
+          <t>Laptop MSI Cyborg 15 Max C13WE - 422VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>39990000</v>
+        <v>41590000</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>41990000</v>
+        <v>42990000</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số luồng:: 8 | Tốc độ CPU:: 2.2 GHz | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: Lên đến 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Wide viewing angle ACER CineCrystal 400 nits | Cổng giao tiếp:: 1 x USB 3.2 Gen 1 (hỗ trợ Power-off USB charging) HDMI 2.1 Micro SD 2 x USB Type-C (hỗ trợ DisplayPort, Thunderbolt 4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD card reader | Webcam:: HP True Vision 1080p FHD camera ToF Sensor Camera with Dual Microphone Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Công nghệ âm thanh:: Hi-Res Audio Spatial Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: Li-ion, 65 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 227.4 mm - Rộng 312.4 mm - Dày 9.7/15.95 (H) - 1.24 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x SuperSpeed USB Type-A LAN (RJ45) HDMI 2.1 2 x USB 3.2 1 x USB Type-C 3.2 (hỗ trợ Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: 3 ống đồng Cooler Boost 2 quạt | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 2 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-swift-go-ai-sfg14-75-765m-ultra-7-258v-nx-jnbsv-004</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-max-c13we-422vn-i7-13620h</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:27:46</t>
+          <t>2026-09-15 14:07:02</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP - U716S8W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop MSI Cyborg 15 Max C13WF - 421VN (i7 13620H, 16GB, 512GB, RTX 5060 8GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>32990000</v>
+        <v>43590000</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>34990000</v>
+        <v>44990000</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 430 mm - Rộng 316 mm - Dày 19.9 mm - 2.61 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x SuperSpeed USB Type-A LAN (RJ45) HDMI 2.1 2 x USB 3.2 1 x USB Type-C 3.2 (hỗ trợ Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: 3 ống đồng Cooler Boost 2 quạt | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 2 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-p3-p3406ccap-ultra-7-255h-u716s8w</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-max-c13wf-421vn-i7-13620h</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:28:00</t>
+          <t>2026-09-15 14:07:15</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA - NZ1368W (Ultra 5 226V, 16GB, 512GB, WQXGA 144Hz, Win11)</t>
+          <t>Laptop MSI Gaming Cyborg 15 C13WEO-417VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>30090000</v>
+        <v>34590000</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>31990000</v>
+        <v>36990000</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
@@ -3076,213 +3088,213 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Lunar Lake - 226V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 40 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 130V | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Anti-Glare Màn hình Wide View 400 nits | Cổng giao tiếp:: 2 x Thunderbolt 4 1 x 3.5mm combo audio jack HDMI 2 x USB 3.2 gen 2 Type-A | Kết nối không dây:: Hãng không công bố | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in array microphone Dolby Atmos | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 223 mm - Dày 12.8 ~ 16.4 mm - 1.2 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - Intel UHD Graphics (tích hợp) + NVIDIA GeForce RTX 5050 GPU, 8GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB Type-A 1 x Headphone/ Microphone combo audio jack 1 x USB Type C (chỉ hỗ trợ Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: DTS Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.98 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-p5-p5405csa-ultra-5-226v-nz1368w</t>
+          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-c13weo-417vn-i7-13620h</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:28:14</t>
+          <t>2026-09-15 14:07:29</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA - NZ1371W (Ultra 7 258V, 32GB, 512GB, WQXGA 144Hz, Win11)</t>
+          <t>Laptop MSI Modern 14S G3MG-003VN (Core 5 320, 16GB, 1TB, Full HD+ 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>37490000</v>
+        <v>27990000</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>39490000</v>
+        <v>31490000</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Intel Arc 140V | Số nhân GPU:: Hãng không công bố | RAM:: 32 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Anti-Glare Màn hình Wide View 400 nits | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 Type-A 1 x Thunderbolt 4 (hỗ trợ DisplayPort) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Smart Amp Technology Built-in array microphone Dolby Atmos | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 223 mm - Dày 12.8 ~ 16.4 mm - 1.2 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: SSD 1TB, chuẩn M.2 2280 NVMe PCIe Gen4, tối đa hỗ trợ 2TB | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 50% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 2 x USB 3.2 gen 1 Type-A LAN (RJ45) HDMI 2.1 2 x USB Type-C 3.2 Gen 2 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD card reader | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: DTS | Tản nhiệt:: 2 ống đồng 1 x Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.39 mm - Rộng 31.59 mm - Dày 1.11 ~ 1.79 - 1.45 kg | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-p5-p5405csa-ultra-7-258v-nz1371w</t>
+          <t>https://www.thegioididong.com/laptop/msi-modern-14s-g3mg-003vn-core-5-320</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:28:27</t>
+          <t>2026-09-15 14:07:43</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook Ultra B9 B9406CAA - X7642TW (Ultra X7 358H, 64GB, 2TB, WQXGA+ OLED 120Hz, Win11)</t>
+          <t>Laptop MSI Modern 15 F1MG-1264VN (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>97990000</v>
+        <v>19990000</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>100000000</v>
+        <v>22390000</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra X7 Panther Lake | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 2 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 1 x USB Type-C (hỗ trợ cổng Thunderbolt 4) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Có | Công nghệ âm thanh:: Built-in speaker Built-in array microphone Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 28.8 mm - Rộng 12.7 mm - Dày 38.9 mm - 1.131 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
+          <t>Công nghệ CPU:: Intel Core thế hệ 12 - 120U | Số nhân:: Hãng không công bố | Số luồng:: 12 | Tốc độ CPU:: 1.45 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (2280) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: Hãng không công bố | Cổng giao tiếp:: 3 x USB 3.2 Gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell, 46.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.7 kg | Chất liệu:: Plastic (nhựa dẻo)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-b9-b9406caa-ultra-x7-358h-x7642tw</t>
+          <t>https://www.thegioididong.com/laptop/msi-modern-15-f1mg-1264vn-core-5-120u</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:28:40</t>
+          <t>2026-09-15 14:07:58</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook Ultra B9 B9406CAA - X7321TW (Ultra X7 358H, 32GB, 1TB, WQXGA+ OLED 120Hz, Win11)</t>
+          <t>Laptop SingPC M16-i382 (i3 1215U, 8GB, 256GB, WUXGA, Win11 Pro)</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>65990000</v>
+        <v>13490000</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>68000000</v>
+        <v>15190000</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra X7 Panther Lake - 358H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare 600 nits Pantone Validated | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x Thunderbolt 4 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Built-in speaker Built-in array microphone Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.9 mm - Dày 16.4 mm - 1.1 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
+          <t>Công nghệ CPU:: Intel Core i3 Alder Lake - 1215U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.2GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 256 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-b9-b9406caa-x7321tw-ultra-x7-358h-32gb-1tb-wqxga-oled-120hz-win11</t>
+          <t>https://www.thegioididong.com/laptop/singpc-m16-i382-i3-1215u</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:28:53</t>
+          <t>2026-09-15 14:08:11</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0045W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop SingPC M16-i595 (i5 1235U, 16GB, 512GB, WUXGA, Win11 Pro)</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>30990000</v>
+        <v>17390000</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>33990000</v>
+        <v>19990000</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 1 x USB Type-C with Thunderbolt 5 (hỗ trợ USB 4, DisplayPort 2.1 và Power Delivery 3.0) | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i5 Alder Lake - 1235U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 72% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-5-225h-sf0045w</t>
+          <t>https://www.thegioididong.com/laptop/singpc-m16-i595-i5-1235u</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:29:08</t>
+          <t>2026-09-15 14:08:25</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0241W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Acer Swift Go AI SFG14-75-765M - NX.JNBSV.004 (Ultra 7 258V, 32GB, 512GB, Full HD+, Win11)</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>35990000</v>
+        <v>39990000</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>37990000</v>
+        <v>41990000</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
@@ -3291,217 +3303,217 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display Màn hình Wide View | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số luồng:: 8 | Tốc độ CPU:: 2.2 GHz | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: Lên đến 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Wide viewing angle ACER CineCrystal 400 nits | Cổng giao tiếp:: 1 x USB 3.2 Gen 1 (hỗ trợ Power-off USB charging) HDMI 2.1 Micro SD 2 x USB Type-C (hỗ trợ DisplayPort, Thunderbolt 4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD card reader | Webcam:: HP True Vision 1080p FHD camera ToF Sensor Camera with Dual Microphone Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Công nghệ âm thanh:: Hi-Res Audio Spatial Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: Li-ion, 65 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 227.4 mm - Rộng 312.4 mm - Dày 9.7/15.95 (H) - 1.24 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-7-255-sf0241w</t>
+          <t>https://www.thegioididong.com/laptop/acer-swift-go-ai-sfg14-75-765m-ultra-7-258v-nx-jnbsv-004</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:29:22</t>
+          <t>2026-09-15 13:37:19</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming ROG Strix G16 G614PM - TS147W (R9 8940HX, 16GB, 512GB, RTX 5060 8GB, WQXGA 300Hz, Win11)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP - U716S8W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>54990000</v>
+        <v>32990000</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>57990000</v>
+        <v>34990000</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115W - 140W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.288 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 430 mm - Rộng 316 mm - Dày 19.9 mm - 2.61 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pm-r9-8940hx-ts147w</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-p3-p3406ccap-ultra-7-255h-u716s8w</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:29:35</t>
+          <t>2026-09-15 13:37:32</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming ROG Strix G16 G614PR - TS103W (R9 8940HX, 16GB, 512GB, RTX 5070Ti 12GB, WQXGA 300Hz, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA - NZ1368W (Ultra 5 226V, 16GB, 512GB, WQXGA 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>70590000</v>
+        <v>30090000</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>71990000</v>
+        <v>31990000</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070Ti, 12 GB | Số nhân GPU:: 5888 CUDA Cores | Công suất đồ hoạ - TGP:: 140 W | Hiệu năng xử lý AI (TOPS):: Lên đến 992 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.34 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Lunar Lake - 226V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 40 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 130V | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Anti-Glare Màn hình Wide View 400 nits | Cổng giao tiếp:: 2 x Thunderbolt 4 1 x 3.5mm combo audio jack HDMI 2 x USB 3.2 gen 2 Type-A | Kết nối không dây:: Hãng không công bố | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in array microphone Dolby Atmos | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 223 mm - Dày 12.8 ~ 16.4 mm - 1.2 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pr-r9-8940hx-ts103w</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-p5-p5405csa-ultra-5-226v-nz1368w</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:29:49</t>
+          <t>2026-09-15 13:37:45</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming V16 V3607VJ Core 5 - TK189W (Core 5 210H, 16GB, 512GB, RTX 3050 6GB, WUXGA 144Hz, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA - NZ1371W (Ultra 7 258V, 32GB, 512GB, WQXGA 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>25990000</v>
+        <v>37490000</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>36990000</v>
+        <v>39490000</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 6 GB | Công suất đồ hoạ - TGP:: 65 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% Adobe | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x 3.5mm combo audio jack HDMI 2.1 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: 1080p with Privacy Shutter | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in microphone | Tản nhiệt:: 2 quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 63 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 251 mm - Dày 22 mm - 1.95 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Intel Arc 140V | Số nhân GPU:: Hãng không công bố | RAM:: 32 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Anti-Glare Màn hình Wide View 400 nits | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 Type-A 1 x Thunderbolt 4 (hỗ trợ DisplayPort) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Smart Amp Technology Built-in array microphone Dolby Atmos | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 223 mm - Dày 12.8 ~ 16.4 mm - 1.2 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-v16-v3607vj-core-5-core-5-210h-tk189w</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-p5-p5405csa-ultra-7-258v-nz1371w</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:03</t>
+          <t>2026-09-15 13:37:58</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming V16 V3607VU - TK416W (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, WUXGA 144Hz, Win11)</t>
+          <t>Laptop Asus ExpertBook Ultra B9 B9406CAA - X7642TW (Ultra X7 358H, 64GB, 2TB, WQXGA+ OLED 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>32990000</v>
+        <v>97990000</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>41990000</v>
+        <v>100000000</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 65 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 2 khe (1 khe 16 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x 3.5mm combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.3 | Webcam:: 1080p FHD camera | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: Mô-đun bảo mật TPM (Firmware TPM) Mật khẩu thiết lập BIOS | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in microphone | Tản nhiệt:: 2 quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 63 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 250.7 mm - Dày 18 mm - 1.95 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra X7 Panther Lake | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 2 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 1 x USB Type-C (hỗ trợ cổng Thunderbolt 4) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Có | Công nghệ âm thanh:: Built-in speaker Built-in array microphone Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 28.8 mm - Rộng 12.7 mm - Dày 38.9 mm - 1.131 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-v16-v3607vu-core-5-210h-tk416w</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-b9-b9406caa-ultra-x7-358h-x7642tw</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:17</t>
+          <t>2026-09-15 13:38:11</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ProArt P1 H7606WP - SR335W (R9 AI HX 370, 64GB, 2TB, RTX 5070 8GB, 3K 120Hz, Cảm ứng, Win11)</t>
+          <t>Laptop Asus ExpertBook Ultra B9 B9406CAA - X7321TW (Ultra X7 358H, 32GB, 1TB, WQXGA+ OLED 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>114890000</v>
+        <v>65990000</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>124990000</v>
+        <v>68000000</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3511,55 +3523,55 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 9 - Hãng không công bố | Số nhân:: 12 | Số luồng:: 24 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 2 TB SSD M.2 NVMe PCIe Gen 4 | Kích thước màn hình:: 16" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 500 nits (Khi bật HDR) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354.9 mm - Rộng 246.9 mm - Dày 17.3 mm - 1.85 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra X7 Panther Lake - 358H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare 600 nits Pantone Validated | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x Thunderbolt 4 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Built-in speaker Built-in array microphone Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.9 mm - Dày 16.4 mm - 1.1 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-proart-p1-h7606wp-r9-ai-hx-370-sr335w</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-b9-b9406caa-x7321tw-ultra-x7-358h-32gb-1tb-wqxga-oled-120hz-win11</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:30</t>
+          <t>2026-09-15 13:38:25</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1404MA - EB028W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0045W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>23990000</v>
+        <v>30990000</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>31990000</v>
+        <v>33990000</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe RAM) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Hãng không công bố | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 21.39 mm - Rộng 32.49 mm - Dày 1.79 mm - 1.4 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 1 x USB Type-C with Thunderbolt 5 (hỗ trợ USB 4, DisplayPort 2.1 và Power Delivery 3.0) | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1404ma-core-5-320-eb028w</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-5-225h-sf0045w</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3569,126 +3581,126 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:43</t>
+          <t>2026-09-15 13:38:38</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1407CA - LY203W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0241W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>24490000</v>
+        <v>35990000</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>33490000</v>
+        <v>37990000</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-27%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 19.9 mm - 1.46 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display Màn hình Wide View | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1407ca-ultra-5-225h-ly203w</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-7-255-sf0241w</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:55</t>
+          <t>2026-09-15 13:38:51</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ385W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0047W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>23990000</v>
+        <v>35990000</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>31990000</v>
+        <v>37990000</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display Màn hình Wide View | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-5-320-bq385w</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-7-255h-sf0047w</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:31:09</t>
+          <t>2026-09-15 13:39:04</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ395W (Core 7 350, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Asus Gaming ROG Strix G16 G614PM - TS147W (R9 8940HX, 16GB, 512GB, RTX 5060 8GB, WQXGA 300Hz, Win11)</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>27990000</v>
+        <v>54990000</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>35490000</v>
+        <v>57990000</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Wildcat Lake - 350 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 17 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115W - 140W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.288 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-7-350-bq395w</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pm-r9-8940hx-ts147w</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3698,279 +3710,279 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:31:22</t>
+          <t>2026-09-15 13:39:17</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 16 X1607CA - MB387W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Gaming ROG Strix G16 G614PR - TS103W (R9 8940HX, 16GB, 512GB, RTX 5070Ti 12GB, WQXGA 300Hz, Win11)</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>24590000</v>
+        <v>70590000</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>33490000</v>
+        <v>71990000</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>-27%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 SO-DIMM | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 25.06 mm - Rộng 35.7 mm - Dày 1.79 ~ 1.99 - 1.88 kg | Chất liệu:: Khung nhôm - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070Ti, 12 GB | Số nhân GPU:: 5888 CUDA Cores | Công suất đồ hoạ - TGP:: 140 W | Hiệu năng xử lý AI (TOPS):: Lên đến 992 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.34 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-16-x1607ca-ultra-5-225h-mb387w</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pr-r9-8940hx-ts103w</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:31:36</t>
+          <t>2026-09-15 13:39:31</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook 7 14 fr0033TU - C1MN2PA (Ultra 5 225U, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
+          <t>Laptop Asus Gaming V16 V3607VJ Core 5 - TK189W (Core 5 210H, 16GB, 512GB, RTX 3050 6GB, WUXGA 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>27490000</v>
+        <v>25990000</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>28990000</v>
+        <v>36990000</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-30%</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 3.80 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Công suất đồ hoạ - TGP:: 15 - 25W | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 2600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Thunderbolt 4 with USB Type - C (hỗ trợ truyền dữ liệu, Power Delivery 3.1, DisplayPort 2.1,  HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB 3.2 gen 2 Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Poly Studio Dual speakers HP Audio Boost DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 4-cell, 64 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.65 mm - Rộng 31.4 mm - Dày 1.49 mm - 1.41 kg | Chất liệu:: Khung và mặt lưng kim loại, nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 6 GB | Công suất đồ hoạ - TGP:: 65 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% Adobe | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x 3.5mm combo audio jack HDMI 2.1 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: 1080p with Privacy Shutter | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in microphone | Tản nhiệt:: 2 quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 63 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 251 mm - Dày 22 mm - 1.95 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-7-14-fr0033tu-ultra-5-225u-c1mn2pa</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-v16-v3607vj-core-5-core-5-210h-tk189w</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 15:57:56</t>
+          <t>2026-09-15 13:39:45</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook X Flip 14 fk0082AU - BZ7N8PA (R7 AI 350, 32GB, 1TB, 2K, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Asus Gaming V16 V3607VU - TK416W (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, WUXGA 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>39890000</v>
+        <v>32990000</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>40890000</v>
+        <v>41990000</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: 2K (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Corning Gorilla Glass 3 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB Type-C (hỗ trợ truyền dữ liệu, DisplayPort 2.1, Power delivery 3.1, HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E MT7922 Bluetooth 5.3 | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ | Thông tin Pin:: 3-cell Li-Po, 59 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 218.5 mm - Dày 14.6 mm - 1.39 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 65 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 2 khe (1 khe 16 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x 3.5mm combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.3 | Webcam:: 1080p FHD camera | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: Mô-đun bảo mật TPM (Firmware TPM) Mật khẩu thiết lập BIOS | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in microphone | Tản nhiệt:: 2 quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 63 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 250.7 mm - Dày 18 mm - 1.95 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-x-flip-14-fk0082au-r7-ai-350-bz7n8pa</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-v16-v3607vu-core-5-210h-tk416w</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 15:58:11</t>
+          <t>2026-09-15 13:39:58</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming Legion 5 15AHP11 - 83Q7001HVN (R7 250, 16GB, 512GB, RTX 5050 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
+          <t>Laptop Asus ProArt P1 H7606WP - SR335W (R9 AI HX 370, 64GB, 2TB, RTX 5070 8GB, 3K 120Hz, Cảm ứng, Win11)</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>52990000</v>
+        <v>114890000</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>56990000</v>
+        <v>124990000</v>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Boost Clock 2662MHz, TGP 115W, 440 AI TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: 2.5K | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: DisplayHDR True Black 1000 | Cổng giao tiếp:: 1x Ethernet 2 x USB Type-C (USB4 40Gbps) hỗ trợ USB PD 65 - 100W và DisplayPort 1.4 1 x Headphone/ Microphone combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) 2×2 Bluetooth 6.0 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 244.5 mm - Rộng 344 mm - Dày 19~20 - 1.87 kg | Chất liệu:: Mặt trên: nhôm + Mặt dưới: nhựa PC-ABS</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 9 - Hãng không công bố | Số nhân:: 12 | Số luồng:: 24 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 2 TB SSD M.2 NVMe PCIe Gen 4 | Kích thước màn hình:: 16" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 500 nits (Khi bật HDR) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354.9 mm - Rộng 246.9 mm - Dày 17.3 mm - 1.85 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15ahp11-r7-250-83q7001hvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-proart-p1-h7606wp-r9-ai-hx-370-sr335w</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 15:58:24</t>
+          <t>2026-09-15 13:40:11</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002NVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus TUF Gaming A15 FA506NCG - HN390W (R7 155, 16GB, 512GB, RTX 3050 4GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>22990000</v>
+        <v>27490000</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>29990000</v>
+        <v>37490000</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>-23%</t>
+          <t>-27%</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 155 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.0 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 4 GB | RAM:: 16 GB | Loại RAM:: DDR5 2 khe (1 khe 16 GB + 1 khe trống) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 62.5% sRGB 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 Gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: HD webcam | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Built-in array microphone | Tản nhiệt:: 2 quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 256 mm - Dày 24.5 mm - 2.30 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002nvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-tuf-gaming-a15-fa506ncg-r7-155-hn390w</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 15:58:38</t>
+          <t>2026-09-15 13:40:24</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002PVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Vivobook 14 X1404MA - EB028W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>19190000</v>
+        <v>23990000</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>25990000</v>
+        <v>31990000</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe RAM) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Hãng không công bố | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 21.39 mm - Rộng 32.49 mm - Dày 1.79 mm - 1.4 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002pvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1404ma-core-5-320-eb028w</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 15:58:52</t>
+          <t>2026-09-15 13:40:37</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00A8VN (Core 3 304, 8GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Vivobook 14 X1407CA - LY203W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>17490000</v>
+        <v>24490000</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>23990000</v>
+        <v>33490000</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
@@ -3979,629 +3991,1176 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core™ 3 - 304 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz (P-core), Turbo tối đa 4.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 2242 PCIe 4.0x4 NVMe | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 × USB-C (USB 5 Gbps), hỗ trợ USB PD 45–65W và DisplayPort 1.2 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Optimized with Dolby Audio 2W x 2 High Definition (HD) Audio Stereo speakers | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 240 mm - Rộng 343 mm - Dày 17 - 18 - 1.59 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 19.9 mm - 1.46 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-3-304-83rr00a8vn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1407ca-ultra-5-225h-ly203w</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 15:59:05</t>
+          <t>2026-09-15 13:40:49</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00AAVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ385W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>22990000</v>
+        <v>23990000</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>29990000</v>
+        <v>31990000</v>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>-23%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00aavn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-5-320-bq385w</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 15:59:18</t>
+          <t>2026-09-15 13:41:02</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Ideapad Slim 3 15IWC11 - 83RR00CVVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ395W (Core 7 350, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>19190000</v>
+        <v>27990000</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>25990000</v>
+        <v>35490000</v>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 7 Wildcat Lake - 350 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 17 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00cvvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-7-350-bq395w</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 15:59:32</t>
+          <t>2026-09-15 13:41:15</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US0040VN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Vivobook 16 X1607CA - MB387W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>23690000</v>
+        <v>24590000</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>31990000</v>
+        <v>33490000</v>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-27%</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 x USB-C (USB 5Gbps), with USB PD 45-65W and DisplayPort 1.2 1x Headphone / microphone combo jack (3.5 mm) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 18 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 SO-DIMM | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 25.06 mm - Rộng 35.7 mm - Dày 1.79 ~ 1.99 - 1.88 kg | Chất liệu:: Khung nhôm - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-5-322-83us0040vn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-16-x1607ca-ultra-5-225h-mb387w</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 15:59:45</t>
+          <t>2026-09-15 13:41:28</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US003YVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Vivobook Go 14 E1404FA - EB012W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>28990000</v>
+        <v>18790000</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>36990000</v>
+        <v>22990000</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>-22%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us003yvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb012w</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 15:59:59</t>
+          <t>2026-09-15 13:41:42</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14IPH11 - 83S5004FVN (Ultra 7 355, 16GB, 512GB, WUXGA OLED, Win11)</t>
+          <t>Laptop Asus Vivobook Go 14 E1404FA - EB1832W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>34990000</v>
+        <v>18790000</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>37990000</v>
+        <v>22990000</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14iph11-ultra-7-355-83s5004fvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb1832w</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:00:14</t>
+          <t>2026-09-15 13:41:55</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkBook 14 G9 - 21V0005PVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ893W (Core 3 304, 8GB, 512GB, Full HD, Win 11)</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>33390000</v>
+        <v>17990000</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>35290000</v>
+        <v>22990000</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Wildcat Lake - 304 | Số nhân:: 5 | Số luồng:: 5 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.30 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 15 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits Chứng nhận TÜV Rheinland | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.7 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-g9-r7-250-21v0005pvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-15-x1504ma-core-3-304-bq893w</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:00:29</t>
+          <t>2026-09-15 12:20:48</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkBook 14 Gen 9 IRL - 21UY008TVN (i5 13420H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Vivobook S 16 S3607VA - RP155W (Core 5 210H, 16GB, 512GB, Full HD+ 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>31190000</v>
+        <v>26990000</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>32890000</v>
+        <v>34990000</v>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-23%</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare LED Backlit | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 259.6 mm - Dày 15.9 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-gen-9-irl-i5-13420h-21uy008tvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-s-16-s3607va-core-5-210h-rp155w</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:00:43</t>
+          <t>2026-09-15 12:21:02</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkBook 16 G9 - 21UT005MVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Vivobook S14 S3407VA - LY256W (Core 7 240H, 16GB, 512GB, WUXGA OLED, Win11)</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>30190000</v>
+        <v>26990000</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>31590000</v>
+        <v>29990000</v>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356 mm - Rộng 253.5 mm - Dày 17.5 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 17.9 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-16-g9-r7-250-21ut005mvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-s14-s3407va-core-7-240h-ly256w</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:00:57</t>
+          <t>2026-09-15 12:21:17</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad E14 - 21T90025VN (Gen 7 Core 7 240H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Zenbook 14 UM3406GA - QD075W (R7 AI 445, 16GB, 512GB, WUXGA OLED, Win11)</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>34190000</v>
+        <v>34590000</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>35590000</v>
+        <v>39990000</v>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: P-core 2.5/ 5.2 GHz, E-core 1.8/ 4.0 GHz | Card màn hình:: Card tích hợp - Integrated Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare 300 nits | Cổng giao tiếp:: 1x USB-A (USB 10Gbps / USB 3.2 Gen 2), Always On 1x Headphone / microphone combo jack (3.5 mm) 1x USB-C® (Thunderbolt™ 4 / USB4® 40 Gbps), with USB PD 15-65W and DisplayPort™ 2.1 1x HDMI® 2.1, up to 4K/6 0Hz 1x Ethernet (RJ-45) 1x USB-A (USB 5 Gbps / USB 3.2 Gen 1) | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: FHD 1080p + IR Hybrid with Privacy Shutter | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Stereo speakers, 2W x2, Dolby Atmos®, audio by HARMAN 2x, Array | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ Discrete TPM 2.0 Enabled | Thông tin Pin:: 3-cell, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 04/2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 10.1/15.25 (front/rear), 19.7 (maximum) mm - 1.34 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.0 GHz | NPU:: AMD XDNA | Card màn hình:: Card tích hợp | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 70% Less harmful blue light 400 nits 600 nits (Khi bật HDR) | Cổng giao tiếp:: 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 75 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.01 mm - Rộng 31.24 mm - Dày 1.49 mm - 1.2 kg | Chất liệu:: Nhôm nguyên khối</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-core-7-240h-21t90025vn</t>
+          <t>https://www.thegioididong.com/laptop/asus-zenbook-14-um3406ga-r7-ai-445-qd075w</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:01:12</t>
+          <t>2026-09-15 12:21:31</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad E14 - 21SX002YVN (Gen 7 Ultra 255H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Dell 14 DC14250 - DC14250-C3U085W11SLU-2Y (Core 3 100U, 8GB, 512GB, Full HD+, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>39190000</v>
+        <v>21490000</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>40590000</v>
+        <v>22590000</v>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.10 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140T | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 1x USB-A (USB 10Gbps / USB 3.2 Gen 2), Always On 1x HDMI® 2.1, up to 4K/60 Hz 1x Headphone / microphone combo jack (3.5 mm) 1x USB-C® (Thunderbolt™ 4 / USB4® 40 Gbps), with USB PD 15-65W and DisplayPort™ 2.1 1x Ethernet (RJ-45) 1x USB-A (USB 5 Gbps / USB 3.2 Gen 1) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD 1080p + IR Hybrid with Privacy Shutter | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Stereo speakers, 2W x2, Dolby Atmos®, audio by HARMAN 2x, Array | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 04/2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 10.1/15.25 (front/rear), 19.7 (maximum) mm - 1.34 kg | Chất liệu:: Vỏ kim loại - Nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 3 - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-255h-21sx002yvn</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-3-100u-dc14250-c3u085w11slu-2y</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:01:26</t>
+          <t>2026-09-15 12:21:45</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX005NVN (Ultra 5 225U, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Dell 14 DC14250 - DC4C5375W1-2Y (Core 5 120U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>36490000</v>
+        <v>28990000</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>38390000</v>
+        <v>32090000</v>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4 với USB Power Delivery và DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226 mm - Dày 18 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-225u-21sx005nvn</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-5-120u-dc4c5375w1-2y</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:01:39</t>
+          <t>2026-09-15 12:21:58</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad X9 14 Gen 1 - 21QA006JVN (Ultra 7 258V, 32GB, 512GB, WUXGA OLED, Win11Pro)</t>
+          <t>Laptop Dell 14 DC14250 - 71100515 (Core 7 150U, 16GB, 512GB, Full HD+ 120Hz, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>53790000</v>
+        <v>31990000</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>55190000</v>
+        <v>35490000</v>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.80 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Chống chói Anti Glare Dolby Vision 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm HDMI 2.1 2 x USB-C (hỗ trợ Thunderbolt 4/USB 4, USB Power Delivery và DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.8 mm - Rộng 212.3 mm - Dày 17.18 mm - 1.21 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 320 mm - Rộng 215.97 mm - Dày 18.02 mm - 1.83 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-x9-14-gen-1-ultra-7-258v-21qa006jvn</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-71100515</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:01:54</t>
+          <t>2026-09-15 12:22:12</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo V14 G5 - 83HD0035VN (Core7 240H, 16G, 512GB, Full HD, Win11)</t>
+          <t>Laptop Dell 14 DC14250 - DC14250-C7U161W11SLU-2Y (Core 7 150U, 16GB, 1TB, Full HD+ ,OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>31290000</v>
+        <v>34990000</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>32690000</v>
+        <v>37990000</v>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) LAN (RJ45) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Ion, 47 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324.2 mm - Rộng 215.2 mm - Dày 17.9 mm - 1.37 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 PCIe Gen 4 x 4 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (M.2 2230)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-v14-g5-core7-240h-83hd0035vn</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-dc14250-c7u161w11slu-2y</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:02:08</t>
+          <t>2026-09-15 12:22:26</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002LVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Dell 15 DC15250 - 71100520 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>38490000</v>
+        <v>21490000</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>44990000</v>
+        <v>22590000</v>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort 1.4, Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Bluetooth 5.0 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-5-322-83tc002lvn</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-71100520</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:22:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Laptop Dell 15 DC15250 - CPH993 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>21490000</v>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>22590000</v>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: Đang cập nhật | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 70% Less harmful blue light 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 16.96 mm đến 18.99 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-cph993</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:22:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Laptop Dell 15 DC15250 - DC5C3259W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>21490000</v>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>22590000</v>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3259w1-2y</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:23:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Laptop Dell 15 DC15250 - DC5C3851W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>21490000</v>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>22590000</v>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x Headphone/ Microphone combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 2 x USB 2.0 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 235 mm - Rộng 358.5 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3851w1-2y</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:23:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Laptop Dell 15 DC15255 - DC5R5973W1-2Y (R5 7530U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>23990000</v>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>25690000</v>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 7530U | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/microphone combo 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r5-7530u-dc5r5973w1-2y</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:23:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Laptop Dell 15 DC15255 - X9YM42 (R7 7730U, 16GB, 1TB, Full HD 120Hz, OfficeH24+36, Win11)</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>29890000</v>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>30590000</v>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 8 x 2.0 GHz | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Bluetooth 5.0 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.635 kg | Chất liệu:: Vỏ nhựa</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r7-7730u-x9ym42</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:23:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Laptop Dell 16 DC16250 - 71100513 (Core 5 120U, 16GB, 1TB, Full HD+, OfficeH24+365B, Win11)</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr"/>
+      <c r="D103" s="2" t="inlineStr"/>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits eDP Wide View Angle | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2W x 2 Realtek ALC3254 Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 05/2025 | Kích thước:: Dài 357.3 mm - Rộng 250.6 mm - Dày 18.23 mm - 2 kg | Chất liệu:: Vỏ nhựa</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-5-120u-71100513</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:23:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Laptop Dell Pro 15 Essential PV15250 - PV15250-100U-8512W-2Y (Core 3 100U, 8GB, 512GB, Full HD, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>22490000</v>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>23990000</v>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Rộng 358.5 mm - Dày 17.5 mm | Chất liệu:: Khung và mặt lưng nhựa</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/dell-pro-15-essential-pv15250-core-3-100u-pv15250-100u-8512w-2y</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:24:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Laptop HP 15 fd2183TU - DP2C0PA (Ultra 7 255U, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>31590000</v>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>32990000</v>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 255U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: Hãng không công bố | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB Type-C with Thunderbolt 5 (hỗ trợ USB 4, DisplayPort 2.1 và Power Delivery 3.0) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: HP True Vision 720p HD camera, tích hợp màn che và micro kép | Đèn bàn phím:: Không có đèn | Bảo mật:: fTPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hard Disk Utilities | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 35.98 cm - Rộng 23.6 cm - Dày 1.86 cm - 1.614 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/hp-15-fd2183tu-ultra-7-255u-dp2c0pa</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:24:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Laptop HP Gaming HyperX Omen 15 ga0092TX - D72D8PA (i5 14450HX, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>45590000</v>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>46990000</v>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 421 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.37 kg | Chất liệu:: Vỏ nhựa</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/hp-gaming-hyperx-omen-15-ga0092tx-i5-14450hx-d72d8pa</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:02:23</t>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:24:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Laptop HP HyperX Omen 15 ga0091TX - D72D7PA (i5 14450HX, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>48590000</v>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>49990000</v>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3840 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 614 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.363 kg | Chất liệu:: Vỏ nhựa</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/hp-hyperx-omen-15-ga0091tx-i5-14450h-d72d7pa</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:24:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Laptop HP OmniBook 5 14 hh0072TU - D72CQPA (Ultra 7 355, 16GB, 512GB, WUXGA, Cảm ứng, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>40690000</v>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 2 x Thunderbolt 4 (hỗ trợ truyền dữ liệu,Power Delivery,DisplayPort,HP Sleep and Charge) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 59.16 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 217.5 mm - Dày 13.6 mm - 1.296 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-5-14-hh0072tu-ultra-7-355-d72cqpa</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:25:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Laptop HP OmniBook 5 14 hh0073TU - D72CRPA (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>38990000</v>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>39690000</v>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 2 x Thunderbolt 4 (hỗ trợ truyền dữ liệu,Power Delivery,DisplayPort,HP Sleep and Charge) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 59.16 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 217.5 mm - Dày 13.6 mm - 1.296 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-5-14-hh0073tu-ultra-7-355-d72crpa</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:25:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Laptop HP OmniBook 5 14 hh0074TU - D72CSPA (Ultra 5 322, 16GB, 512GB, WUXGA, Cảm ứng, OfficeH24+365, Win11)</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>36990000</v>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>37690000</v>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.90 GHz (Lên đến 4.40 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 1600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 2 x Thunderbolt 4 (hỗ trợ truyền dữ liệu,Power Delivery,DisplayPort,HP Sleep and Charge) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 59.16 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 217.5 mm - Dày 13.6 mm - 1.337 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-5-14-hh0074tu-ultra-5-322-d72cspa</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:25:36</t>
         </is>
       </c>
     </row>

--- a/laptop_tgdd_all.xlsx
+++ b/laptop_tgdd_all.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I110"/>
+  <dimension ref="A1:I111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -492,143 +492,143 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-977M - NX.W26SV.001 (Ultra 9 185H, 16GB, 512GB, Full HD+, Win11)</t>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ893W (Core 3 304, 8GB, 512GB, Full HD, Win 11)</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>29990000</v>
+        <v>17990000</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>31990000</v>
+        <v>22990000</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 9 Meteor Lake - 185H | Số luồng:: 22 | Tốc độ CPU:: 2.30 GHz (Lên đến 5.10 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (1 khe onboard) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB Type-C (65W) 1 x USB Type-C LAN (RJ45) HDMI 2.1 USB Type-C | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Stereo speakers | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 10 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.6 mm - Rộng 227.7 mm - Dày 17.9 mm - 1.49 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 3 Wildcat Lake - 304 | Số nhân:: 5 | Số luồng:: 5 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.30 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 15 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits Chứng nhận TÜV Rheinland | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.7 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-go-14-ai-ag14-i71m-977m-ultra-9-185h-nx-w26sv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-15-x1504ma-core-3-304-bq893w</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:15:00</t>
+          <t>2026-09-16 12:47:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR - NX.X0PSV.002 (Ryzen 5 3500U, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Asus Vivobook S 16 S3607VA - RP155W (Core 5 210H, 16GB, 512GB, Full HD+ 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>17990000</v>
+        <v>26990000</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>20990000</v>
+        <v>34990000</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-23%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 3500U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz | Card màn hình:: Card tích hợp - AMD Radeon Vega Mobile Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 2400 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: IPS LED-backlit TFT LCD Wide viewing angle 250 nits | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A HDMI 1 x SuperSpeed USB Type-C (hỗ trợ DisplayPort 1.4) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP FHD 1080p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: 2 loa 2 microphones | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Phím Copilot | Thông tin Pin:: 2-cell Li-ion, 45.6 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 210.2 mm - Rộng 322.6 mm - Dày 19.8 mm - 1.3 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare LED Backlit | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 259.6 mm - Dày 15.9 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-nx-x0psv-002</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-s-16-s3607va-core-5-210h-rp155w</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:15:14</t>
+          <t>2026-09-16 12:47:56</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN - NX.DDASV.001 (Core 3 N350, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Asus Vivobook S14 S3407VA - LY256W (Core 7 240H, 16GB, 512GB, WUXGA OLED, Win11)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>16990000</v>
+        <v>26990000</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>18990000</v>
+        <v>29990000</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - N350 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 3.90 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB 3.2 HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.0 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.8 mm - Rộng 235.6 mm - Dày 19.7 mm - 1.53 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 17.9 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-36p-30tn-core-3-n350-nx-ddasv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-s14-s3407va-core-7-240h-ly256w</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:15:28</t>
+          <t>2026-09-16 12:48:09</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 - NX.X0RSV.001 (Ryzen 5 3500U, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Asus Zenbook 14 UM3406GA - QD075W (R7 AI 445, 16GB, 512GB, WUXGA OLED, Win11)</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>17990000</v>
+        <v>34590000</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>20990000</v>
+        <v>39990000</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -637,256 +637,256 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 3500U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz | Card màn hình:: Card tích hợp - AMD Radeon Vega Mobile Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 2400 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: IPS Màn hình Wide View Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A HDMI 1 x SuperSpeed USB Type-C (hỗ trợ DisplayPort 1.4) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP FHD 1080p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: 2 loa 2 microphones | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Phím Copilot | Thông tin Pin:: 2-cell Li-ion, 45.6 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 229.3 mm - Rộng 357.4 mm - Dày 19.85 mm - 1.5 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.0 GHz | NPU:: AMD XDNA | Card màn hình:: Card tích hợp | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 70% Less harmful blue light 400 nits 600 nits (Khi bật HDR) | Cổng giao tiếp:: 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 75 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.01 mm - Rộng 31.24 mm - Dày 1.49 mm - 1.2 kg | Chất liệu:: Nhôm nguyên khối</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-nx-x0rsv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-zenbook-14-um3406ga-r7-ai-445-qd075w</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:15:42</t>
+          <t>2026-09-16 12:48:22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-44P-R4UH - NX.DJVSV.002 (R7 7730U, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Dell 14 DC14250 - DC14250-C3U085W11SLU-2Y (Core 3 100U, 8GB, 512GB, Full HD+, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>21990000</v>
+        <v>21490000</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>23990000</v>
+        <v>22590000</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB Type - C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 230.2 mm - Dày 18.6 mm - 1.49 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-44p-r4uh-r7-7730u-nx-djvsv-002</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-3-100u-dc14250-c3u085w11slu-2y</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:15:55</t>
+          <t>2026-09-16 12:48:36</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC - NX.DG3SV.002.16G (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Dell 14 DC14250 - DC4C5375W1-2Y (Core 5 120U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>21990000</v>
+        <v>28990000</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>24990000</v>
+        <v>32090000</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 357.6 mm - Rộng 228.5 mm - Dày 18.7 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226 mm - Dày 18 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-53p-56ec-core-5-120u-nx-dg3sv-002-16g</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-5-120u-dc4c5375w1-2y</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:16:09</t>
+          <t>2026-09-16 12:48:50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AL16-71P-582Q - NX.DRSSV.001 (Ultra 5 125H, 16GB, 512GB, Full HD+ 120Hz, Win11)</t>
+          <t>Laptop Dell 14 DC14250 - 71100515 (Core 7 150U, 16GB, 512GB, Full HD+ 120Hz, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>24990000</v>
+        <v>31990000</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>26990000</v>
+        <v>35490000</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 125H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357 mm - Rộng 245.5 mm - Dày 18.9 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 320 mm - Rộng 215.97 mm - Dày 18.02 mm - 1.83 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-16-al16-71p-582q-ultra-5-125h-nx-drssv-001</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-71100515</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:16:22</t>
+          <t>2026-09-16 12:49:04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Aspire 7 A715-59G-59RD - NH.DXUSV.001 (Core 5 210H, 16GB, 512GB, RTX 3050 4GB, Fulll HD 144Hz, Win11)</t>
+          <t>Laptop Dell 14 DC14250 - DC14250-C7U161W11SLU-2Y (Core 7 150U, 16GB, 1TB, Full HD+ ,OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>26990000</v>
+        <v>34990000</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>31990000</v>
+        <v>37990000</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 4 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35W - 80W | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 4 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle 350 nits Acer ComfyView | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C (hỗ trợ DisplayPort 1.4) LAN (RJ45) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn LED - 15 chế độ màu | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 359.5 mm - Rộng 238 mm - Dày 22.7 mm - 1.99 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 7 - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 PCIe Gen 4 x 4 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (M.2 2230)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-aspire-7-a715-59g-59rd-core-5-210h-nh-dxusv-001</t>
+          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-dc14250-c7u161w11slu-2y</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:16:35</t>
+          <t>2026-09-16 12:49:18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel AN16S-61-R9CN - NH.QXGSV.001 (Ryzen AI 7 350, 16GB, 512GB, RTX 5070 8GB, 2K+ 180Hz, Win11)</t>
+          <t>Laptop Dell 15 DC15250 - 71100520 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>57990000</v>
+        <v>21490000</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>64990000</v>
+        <v>22590000</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.0 GHz (Lên đến 5.2 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits 3ms | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: NVIDIA Optimus | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort 1.4, Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Bluetooth 5.0 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-an16s-61-r9cn-ryzen-ai-7-350-nh-qxgsv-001</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-71100520</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:16:49</t>
+          <t>2026-09-16 12:49:32</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-556L - NH.QZ9SV.006 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
+          <t>Laptop Dell 15 DC15250 - CPH993 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>38990000</v>
+        <v>21490000</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>40990000</v>
+        <v>22590000</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -895,729 +895,717 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 60W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 16:9 aspect ratio Ultra-slim design Mercury free, environment friendly Thời gian phản hồi: 3 ms LED-backlit TFT LCD Wide viewing angle 300 nits Acer ComfyView | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Ethernet (LAN) Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: 720p at 30 fps HD camera | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High SNR DAC 2.1 Vrms Hỗ trợ tai nghe đến 600 Ω Compatible with Cortana with Voice 2 microphones Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Tính năng khác:: NitroSense Key Copilot Key | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 239.89 mm - Rộng 362.3 mm - Dày 115.7/23.5 - 2.1 kg | Chất liệu:: Nhựa nguyên khối</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: Đang cập nhật | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 70% Less harmful blue light 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 16.96 mm đến 18.99 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-556l-core-5-210h-nh-qz9sv-006</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-cph993</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:17:02</t>
+          <t>2026-09-16 12:49:46</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-73Z8 - NH.QUASV.001 (Core 7 240H, 16GB, 512GB, RTX 4050 6GB, Full HD  180Hz, Win11)</t>
+          <t>Laptop Dell 15 DC15250 - DC5C3259W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>35990000</v>
+        <v>21490000</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>39990000</v>
+        <v>22590000</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: IPS | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1x Ethernet 3 x USB 3.2 Gen 1 Type-A 1 x USB Type-C (65W) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: 720p at 30 fps HD camera Camera with Dual Microphone | Đèn bàn phím:: Đơn sắc - Màu cam | Công nghệ âm thanh:: Windows Spatial Sound High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-73z8-core-7-240h-nh-quasv-001</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3259w1-2y</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:17:16</t>
+          <t>2026-09-16 12:49:59</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-78MD - NH.QZ9SV.007 (Core 7 240H, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
+          <t>Laptop Dell 15 DC15250 - DC5C3851W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>40990000</v>
+        <v>21490000</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>43990000</v>
+        <v>22590000</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms 300 nits Acer ComfyView | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2 microphones Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Nhựa nguyên khối</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x Headphone/ Microphone combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 2 x USB 2.0 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 235 mm - Rộng 358.5 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-78md-core-7-240h-nh-qz9sv-007</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3851w1-2y</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:17:30</t>
+          <t>2026-09-16 12:50:13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-61-R0B8 - NH.QXQSV.001 (Ryzen AI 5 340, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
+          <t>Laptop Dell 15 DC15255 - DC5R5973W1-2Y (R5 7530U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>42990000</v>
+        <v>23990000</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>47990000</v>
+        <v>25690000</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.40 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 7530U | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/microphone combo 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-61-r0b8-ryzen-ai-5-340-nh-qxqsv-001</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r5-7530u-dc5r5973w1-2y</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:17:43</t>
+          <t>2026-09-16 12:50:26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-71-58WQ - NH.QXBSV.001 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, 2K+ 180Hz, Win11)</t>
+          <t>Laptop Dell 15 DC15255 - X9YM42 (R7 7730U, 16GB, 1TB, Full HD 120Hz, OfficeH24+36, Win11)</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>44990000</v>
+        <v>29890000</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46990000</v>
+        <v>30590000</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 8 x 2.0 GHz | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Bluetooth 5.0 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.635 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-71-58wq-core-5-210h-nh-qxbsv-001</t>
+          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r7-7730u-x9ym42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:17:57</t>
+          <t>2026-09-16 12:50:39</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Predator Helios Neo 16S PHN16S-I51-97T9 - NH.U3SSV.006 (Ultra 9 386H, 16GB, 512GB, RTX 5070 8GB, 2K+ 165Hz, Win11)</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>75990000</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>77990000</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
-        </is>
-      </c>
+          <t>Laptop Dell 16 DC16250 - 71100513 (Core 5 120U, 16GB, 1TB, Full HD+, OfficeH24+365B, Win11)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 9 Panther Lake - 386H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 50 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: LED-backlit TFT LCD 500 nits Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 18.9 mm - 2.2 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits eDP Wide View Angle | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2W x 2 Realtek ALC3254 Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 05/2025 | Kích thước:: Dài 357.3 mm - Rộng 250.6 mm - Dày 18.23 mm - 2 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16s-phn16s-i51-97t9-ultra-9-386h</t>
+          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-5-120u-71100513</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:18:11</t>
+          <t>2026-09-16 12:50:53</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Nitro ProPanel AN16S-61-R7ZJ - NH.QXFSV.002 (R7 AI 350, 16GB, 512GB, RTX 5060 8GB, 2K, Win11)</t>
+          <t>Laptop Dell Pro 15 Essential PV15250 - PV15250-100U-8512W-2Y (Core 3 100U, 8GB, 512GB, Full HD, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>49990000</v>
+        <v>22490000</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>51990000</v>
+        <v>23990000</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Nhôm &amp; Nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Rộng 358.5 mm - Dày 17.5 mm | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-an16s-61-r7zj-r7-ai-350-nhqxfsv002</t>
+          <t>https://www.thegioididong.com/laptop/dell-pro-15-essential-pv15250-core-3-100u-pv15250-100u-8512w-2y</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:18:25</t>
+          <t>2026-09-16 12:51:07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Nitro ProPanel ANV15-52-50RB - NH.QUASV.002 (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, Full HD 180Hz, Win11)</t>
+          <t>Laptop HP 15 fd2183TU - DP2C0PA (Ultra 7 255U, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>33490000</v>
+        <v>31590000</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>37990000</v>
+        <v>32990000</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 60W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 300 nits Acer ComfyView 3ms | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2 microphones Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Tính năng khác:: Copilot Key | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 255U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: Hãng không công bố | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB Type-C with Thunderbolt 5 (hỗ trợ USB 4, DisplayPort 2.1 và Power Delivery 3.0) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: HP True Vision 720p HD camera, tích hợp màn che và micro kép | Đèn bàn phím:: Không có đèn | Bảo mật:: fTPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hard Disk Utilities | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 35.98 cm - Rộng 23.6 cm - Dày 1.86 cm - 1.614 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv15-52-50rb-core-5-210h-nh-quasv-002</t>
+          <t>https://www.thegioididong.com/laptop/hp-15-fd2183tu-ultra-7-255u-dp2c0pa</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:18:39</t>
+          <t>2026-09-16 12:51:20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Nitro ProPanel ANV16-72-782F - NH.QUPSV.001 (Core 7 240H, 16GB, 512GB, RTX 5050 8GB, Full HD+ 180 Hz, Win11)</t>
+          <t>Laptop HP Gaming HyperX Omen 15 ga0092TX - D72D8PA (i5 14450HX, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>43990000</v>
+        <v>45590000</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>45990000</v>
+        <v>46990000</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 80 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 360 mm - Rộng 274.5 mm - Dày 24.5 mm - 2.4 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 421 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.37 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv16-72-782f-core-7-240h-nhqupsv001</t>
+          <t>https://www.thegioididong.com/laptop/hp-gaming-hyperx-omen-15-ga0092tx-i5-14450hx-d72d8pa</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:18:52</t>
+          <t>2026-09-16 12:51:33</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Nitro ProPanel ANV16S-61-R7KQ - NH.QXPSV.001 (R5 AI 340, 16GB, 512GB, RTX 5060 8GB, Full HD 180Hz, Win11)</t>
+          <t>Laptop HP HyperX Omen 15 ga0091TX - D72D7PA (i5 14450HX, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46990000</v>
+        <v>48590000</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>48990000</v>
+        <v>49990000</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 400 nits | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB Type C 3.2 Gen 2 (Hỗ trợ Power Delivery và DisplayPort™ 2.1) LAN (RJ45) HDMI 2.1 3 x USB A | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD 1080p Camera IR | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Hi-Res certification Spatial Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3840 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 614 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.363 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv16s-61-r7kq-r5-ai-340-nhqxpsv001</t>
+          <t>https://www.thegioididong.com/laptop/hp-hyperx-omen-15-ga0091tx-i5-14450h-d72d7pa</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:19:06</t>
+          <t>2026-09-16 12:51:47</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Air 14 SFA14-I31-34NF - NX.W49SV.001 (Core 3 304, 12GB, 512GB, WUXGA 120Hz, Win11)</t>
+          <t>Laptop HP OmniBook 5 14 hh0072TU - D72CQPA (Ultra 7 355, 16GB, 512GB, WUXGA, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>21990000</v>
+        <v>39990000</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>23990000</v>
+        <v>40690000</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - 304 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 12 GB | Loại RAM:: LPDDR5 (1 khe onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Wide viewing angle 350 nits LED Backlight Acer ComfyView | Cổng giao tiếp:: 1 x USB 3.2 2 x USB Type-C (hỗ trợ USB, Power Delivery, DisplayPort và Thunderbolt 4) | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.3 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.99 mm - Rộng 222.65 mm - Dày 12.99 mm - 1.19 kg | Chất liệu:: Khung và mặt lưng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 2 x Thunderbolt 4 (hỗ trợ truyền dữ liệu,Power Delivery,DisplayPort,HP Sleep and Charge) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 59.16 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 217.5 mm - Dày 13.6 mm - 1.296 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-swift-air-14-sfa14-i31-34nf-core-3-304-nx-w49sv-001</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-5-14-hh0072tu-ultra-7-355-d72cqpa</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:19:20</t>
+          <t>2026-09-16 12:52:02</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Air 14 SFA14-I31-52BV - NX.W49SV.002 (Core 5 320, 12GB, 512GB, Full HD 120Hz, Win11)</t>
+          <t>Laptop HP OmniBook 5 14 hh0073TU - D72CRPA (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>24990000</v>
+        <v>38990000</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>26990000</v>
+        <v>39690000</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Đang cập nhật | RAM:: 12 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 350 nits | Cổng giao tiếp:: 1 x USB 3.2 2 x USB Type-C (hỗ trợ USB, Power Delivery, DisplayPort và Thunderbolt 4) | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.3 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 222.65 mm - Rộng 222.65 mm - Dày 12.99 mm - 1.19 kg | Chất liệu:: Khung và mặt lưng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 2 x Thunderbolt 4 (hỗ trợ truyền dữ liệu,Power Delivery,DisplayPort,HP Sleep and Charge) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 59.16 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 217.5 mm - Dày 13.6 mm - 1.296 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-swift-air-14-sfa14-i31-52bv-core-5-320-nx-w49sv-002</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-5-14-hh0073tu-ultra-7-355-d72crpa</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:19:34</t>
+          <t>2026-09-16 12:52:15</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go AI SFG14-75-5264 - NX.JNBSV.001 (Ultra 5 226V, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop HP OmniBook 5 14 hh0074TU - D72CSPA (Ultra 5 322, 16GB, 512GB, WUXGA, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>29990000</v>
+        <v>36990000</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>31990000</v>
+        <v>37690000</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Lunar Lake - 226V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 3.50 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 40 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 130V | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: OLED | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe ACER CineCrystal 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 2 x USB4 Type-C (hỗ trợ truyền dữ liệu, DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 65Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 227.4 mm - Rộng 312.4 mm - Dày 15.95 mm - 1.24 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.90 GHz (Lên đến 4.40 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 1600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 2 x Thunderbolt 4 (hỗ trợ truyền dữ liệu,Power Delivery,DisplayPort,HP Sleep and Charge) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 59.16 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 217.5 mm - Dày 13.6 mm - 1.337 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-swift-go-ai-sfg14-75-5264-ultra-5-226v-nxjnbsv001</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-5-14-hh0074tu-ultra-5-322-d72cspa</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:19:47</t>
+          <t>2026-09-16 12:52:29</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook 5 14 hh0075TU - D72CTPA (Ultra 5 322, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Swift Go AI SFG14-75-765M - NX.JNBSV.004 (Ultra 7 258V, 32GB, 512GB, Full HD+, Win11)</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>35990000</v>
+        <v>39990000</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>36690000</v>
+        <v>41990000</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.90 GHz (Lên đến 4.40 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 2 x Thunderbolt 4 (hỗ trợ truyền dữ liệu,Power Delivery,DisplayPort,HP Sleep and Charge) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 59.16 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 217.5 mm - Dày 13.6 mm - 1.337 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số luồng:: 8 | Tốc độ CPU:: 2.2 GHz | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: Lên đến 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Wide viewing angle ACER CineCrystal 400 nits | Cổng giao tiếp:: 1 x USB 3.2 Gen 1 (hỗ trợ Power-off USB charging) HDMI 2.1 Micro SD 2 x USB Type-C (hỗ trợ DisplayPort, Thunderbolt 4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD card reader | Webcam:: HP True Vision 1080p FHD camera ToF Sensor Camera with Dual Microphone Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Công nghệ âm thanh:: Hi-Res Audio Spatial Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: Li-ion, 65 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 227.4 mm - Rộng 312.4 mm - Dày 9.7/15.95 (H) - 1.24 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-5-14-hh0075tu-ultra-5-322-d72ctpa</t>
+          <t>https://www.thegioididong.com/laptop/acer-swift-go-ai-sfg14-75-765m-ultra-7-258v-nx-jnbsv-004</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:11:37</t>
+          <t>2026-09-16 12:53:20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook 7 14 fr0033TU - C1MN2PA (Ultra 5 225U, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP - U716S8W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>27490000</v>
+        <v>32990000</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>28990000</v>
+        <v>34990000</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 3.80 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Công suất đồ hoạ - TGP:: 15 - 25W | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 2600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Thunderbolt 4 with USB Type - C (hỗ trợ truyền dữ liệu, Power Delivery 3.1, DisplayPort 2.1,  HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB 3.2 gen 2 Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Poly Studio Dual speakers HP Audio Boost DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 4-cell, 64 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.65 mm - Rộng 31.4 mm - Dày 1.49 mm - 1.41 kg | Chất liệu:: Khung và mặt lưng kim loại, nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 430 mm - Rộng 316 mm - Dày 19.9 mm - 2.61 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-7-14-fr0033tu-ultra-5-225u-c1mn2pa</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-p3-p3406ccap-ultra-7-255h-u716s8w</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:11:51</t>
+          <t>2026-09-16 12:53:35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook Ultra 14 kd0036TU - D72C6PA (Ultra 9 386H, 32GB, 1TB, 3K OLED 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA - NZ1368W (Ultra 5 226V, 16GB, 512GB, WQXGA 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>65190000</v>
+        <v>30090000</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>65890000</v>
+        <v>31990000</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 9 Panther Lake - 386H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: up to 120 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light 500 nits Corning Gorilla Glass 3 | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery 3.1, DisplayPort 2.1) 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.1 mm - Rộng 215.6 mm - Dày 10.7 mm - 1.282 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Lunar Lake - 226V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 40 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 130V | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Anti-Glare Màn hình Wide View 400 nits | Cổng giao tiếp:: 2 x Thunderbolt 4 1 x 3.5mm combo audio jack HDMI 2 x USB 3.2 gen 2 Type-A | Kết nối không dây:: Hãng không công bố | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in array microphone Dolby Atmos | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 223 mm - Dày 12.8 ~ 16.4 mm - 1.2 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-ultra-14-kd0036tu-ultra-9-386h-d72c6pa</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-p5-p5405csa-ultra-5-226v-nz1368w</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:12:04</t>
+          <t>2026-09-16 12:53:49</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook Ultra 14 kd0039TU - D72C7PA (Ultra 7 356H, 32GB, 1TB, 3K OLED 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA - NZ1371W (Ultra 7 258V, 32GB, 512GB, WQXGA 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>59190000</v>
+        <v>37490000</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>59890000</v>
+        <v>39490000</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 356H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz (Lên đến 4.7 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: up to 120 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 500 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery 3.1, DisplayPort 2.1) 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.1 mm - Rộng 215.6 mm - Dày 10.7 mm - 1.288 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Intel Arc 140V | Số nhân GPU:: Hãng không công bố | RAM:: 32 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Anti-Glare Màn hình Wide View 400 nits | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 Type-A 1 x Thunderbolt 4 (hỗ trợ DisplayPort) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Smart Amp Technology Built-in array microphone Dolby Atmos | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 223 mm - Dày 12.8 ~ 16.4 mm - 1.2 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-ultra-14-kd0039tu-ultra-7-356h-d72c7pa</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-p5-p5405csa-ultra-7-258v-nz1371w</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:12:17</t>
+          <t>2026-09-16 12:54:03</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook X Flip 14 fk0082AU - BZ7N8PA (R7 AI 350, 32GB, 1TB, 2K, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Asus ExpertBook Ultra B9 B9406CAA - X7642TW (Ultra X7 358H, 64GB, 2TB, WQXGA+ OLED 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>39890000</v>
+        <v>97990000</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>40890000</v>
+        <v>100000000</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
@@ -1626,791 +1614,791 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: 2K (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Corning Gorilla Glass 3 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB Type-C (hỗ trợ truyền dữ liệu, DisplayPort 2.1, Power delivery 3.1, HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E MT7922 Bluetooth 5.3 | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ | Thông tin Pin:: 3-cell Li-Po, 59 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 218.5 mm - Dày 14.6 mm - 1.39 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra X7 Panther Lake | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 2 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 1 x USB Type-C (hỗ trợ cổng Thunderbolt 4) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Có | Công nghệ âm thanh:: Built-in speaker Built-in array microphone Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 28.8 mm - Rộng 12.7 mm - Dày 38.9 mm - 1.131 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-x-flip-14-fk0082au-r7-ai-350-bz7n8pa</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-b9-b9406caa-ultra-x7-358h-x7642tw</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:12:31</t>
+          <t>2026-09-16 12:54:17</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP ProBook 4 G1a 14 - D9CP7AT (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus ExpertBook Ultra B9 B9406CAA - X7321TW (Ultra X7 358H, 32GB, 1TB, WQXGA+ OLED 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>30590000</v>
+        <v>65990000</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>31990000</v>
+        <v>68000000</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB Type-C (hỗ trợ cổng Thunderbolt 4) LAN (RJ45) 2 x USB 3.2 Gen 2 Type-C (hỗ trợ Power Delivery 3.0, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) | Webcam:: Camera HP FHD, tích hợp màn che và micro kép | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: fTPM 2.0 TPM Embedded Security Smart Cover Secure Platform Management (SPM) Secure Boot Configuration POST Power-On Password Microsoft Pluton Processor BIOS Sure Start AMD PSP 11.0 Device Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hard Drive Utilities | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 31.86 cm - Rộng 22.43 cm - Dày 1.70 cm - 1.465 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra X7 Panther Lake - 358H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare 600 nits Pantone Validated | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x Thunderbolt 4 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Built-in speaker Built-in array microphone Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.9 mm - Dày 16.4 mm - 1.1 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-probook-4-g1a-14-r7-250-d9cp7at</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-b9-b9406caa-x7321tw-ultra-x7-358h-32gb-1tb-wqxga-oled-120hz-win11</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:12:45</t>
+          <t>2026-09-16 12:54:31</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP Probook 4 G1ah 16 - D9CP8AT (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0045W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>30590000</v>
+        <v>30990000</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>31990000</v>
+        <v>33990000</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (2280) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI 2 x USB 3.2 Gen 2 Type-C (hỗ trợ Power Delivery 3.0, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) | Webcam:: Camera HP FHD, tích hợp màn che và micro kép | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM Embedded Security Smart Cover Secure Platform Management (SPM) Secure Boot Configuration POST Power-On Password Microsoft Pluton Processor fTPM 2.0 BIOS Sure Start AMD PSP 11.0 Device Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hard Drive Utilities | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 35.94 cm - Rộng 25.1 cm - Dày 1.7 cm - 1.783 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 1 x USB Type-C with Thunderbolt 5 (hỗ trợ USB 4, DisplayPort 2.1 và Power Delivery 3.0) | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-probook-4-g1ah-16-r7-250-d9cp8at</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-5-225h-sf0045w</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:12:59</t>
+          <t>2026-09-16 12:54:44</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP ProBook 4 G2i 16 - DK2X9AT (Ultra 5 325, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0241W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>35190000</v>
+        <v>35990000</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>36590000</v>
+        <v>37990000</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 325 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell, 68.03 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.4 mm - Rộng 251 mm - Dày 17.5 mm - 1.848 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display Màn hình Wide View | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-probook-4-g2i-16-ultra-5-325-dk2x9at</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-7-255-sf0241w</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:13:13</t>
+          <t>2026-09-16 12:54:57</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP ProBook 4 G2i 16 - DK2Y5AT (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0047W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>39190000</v>
+        <v>35990000</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>40590000</v>
+        <v>37990000</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell, 68.03 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.4 mm - Rộng 251 mm - Dày 17.5 mm - 1.846 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display Màn hình Wide View | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-probook-4-g2i-16-ultra-7-355-dk2y5at</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-7-255h-sf0047w</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:13:26</t>
+          <t>2026-09-16 12:55:11</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Gaming Legion 5 15AHP11 - 83Q7001HVN (R7 250, 16GB, 512GB, RTX 5050 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
+          <t>Laptop Asus Gaming ROG Strix G16 G614PM - TS147W (R9 8940HX, 16GB, 512GB, RTX 5060 8GB, WQXGA 300Hz, Win11)</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>52990000</v>
+        <v>54990000</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>56990000</v>
+        <v>57990000</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Boost Clock 2662MHz, TGP 115W, 440 AI TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: 2.5K | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: DisplayHDR True Black 1000 | Cổng giao tiếp:: 1x Ethernet 2 x USB Type-C (USB4 40Gbps) hỗ trợ USB PD 65 - 100W và DisplayPort 1.4 1 x Headphone/ Microphone combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) 2×2 Bluetooth 6.0 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 244.5 mm - Rộng 344 mm - Dày 19~20 - 1.87 kg | Chất liệu:: Mặt trên: nhôm + Mặt dưới: nhựa PC-ABS</t>
+          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115W - 140W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.288 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15ahp11-r7-250-83q7001hvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pm-r9-8940hx-ts147w</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:13:39</t>
+          <t>2026-09-16 12:55:25</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002NVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Gaming ROG Strix G16 G614PR - TS103W (R9 8940HX, 16GB, 512GB, RTX 5070Ti 12GB, WQXGA 300Hz, Win11)</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>22990000</v>
+        <v>70590000</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>29990000</v>
+        <v>71990000</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-23%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070Ti, 12 GB | Số nhân GPU:: 5888 CUDA Cores | Công suất đồ hoạ - TGP:: 140 W | Hiệu năng xử lý AI (TOPS):: Lên đến 992 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.34 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002nvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pr-r9-8940hx-ts103w</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:13:53</t>
+          <t>2026-09-16 12:55:38</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002PVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Gaming V16 V3607VJ Core 5 - TK189W (Core 5 210H, 16GB, 512GB, RTX 3050 6GB, WUXGA 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>19190000</v>
+        <v>25990000</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>25990000</v>
+        <v>36990000</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-30%</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 6 GB | Công suất đồ hoạ - TGP:: 65 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% Adobe | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x 3.5mm combo audio jack HDMI 2.1 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: 1080p with Privacy Shutter | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in microphone | Tản nhiệt:: 2 quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 63 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 251 mm - Dày 22 mm - 1.95 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002pvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-v16-v3607vj-core-5-core-5-210h-tk189w</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:14:06</t>
+          <t>2026-09-16 12:55:52</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00A8VN (Core 3 304, 8GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Gaming V16 V3607VU - TK416W (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, WUXGA 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>17490000</v>
+        <v>32990000</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>23990000</v>
+        <v>41990000</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-27%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core™ 3 - 304 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz (P-core), Turbo tối đa 4.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 2242 PCIe 4.0x4 NVMe | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 × USB-C (USB 5 Gbps), hỗ trợ USB PD 45–65W và DisplayPort 1.2 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Optimized with Dolby Audio 2W x 2 High Definition (HD) Audio Stereo speakers | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 240 mm - Rộng 343 mm - Dày 17 - 18 - 1.59 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 65 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 2 khe (1 khe 16 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x 3.5mm combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.3 | Webcam:: 1080p FHD camera | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: Mô-đun bảo mật TPM (Firmware TPM) Mật khẩu thiết lập BIOS | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in microphone | Tản nhiệt:: 2 quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 63 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 250.7 mm - Dày 18 mm - 1.95 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-3-304-83rr00a8vn</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-v16-v3607vu-core-5-210h-tk416w</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:14:19</t>
+          <t>2026-09-16 12:56:06</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00AAVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus ProArt P1 H7606WP - SR335W (R9 AI HX 370, 64GB, 2TB, RTX 5070 8GB, 3K 120Hz, Cảm ứng, Win11)</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>22990000</v>
+        <v>114890000</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>29990000</v>
+        <v>124990000</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-23%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 9 - Hãng không công bố | Số nhân:: 12 | Số luồng:: 24 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 2 TB SSD M.2 NVMe PCIe Gen 4 | Kích thước màn hình:: 16" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 500 nits (Khi bật HDR) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354.9 mm - Rộng 246.9 mm - Dày 17.3 mm - 1.85 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00aavn</t>
+          <t>https://www.thegioididong.com/laptop/asus-proart-p1-h7606wp-r9-ai-hx-370-sr335w</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:14:32</t>
+          <t>2026-09-16 12:56:19</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Ideapad Slim 3 15IWC11 - 83RR00CVVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus TUF Gaming A15 FA506NCG - HN390W (R7 155, 16GB, 512GB, RTX 3050 4GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>19190000</v>
+        <v>27490000</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>25990000</v>
+        <v>37490000</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-27%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 155 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.0 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 4 GB | RAM:: 16 GB | Loại RAM:: DDR5 2 khe (1 khe 16 GB + 1 khe trống) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 62.5% sRGB 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 Gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: HD webcam | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Built-in array microphone | Tản nhiệt:: 2 quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 256 mm - Dày 24.5 mm - 2.30 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00cvvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-tuf-gaming-a15-fa506ncg-r7-155-hn390w</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:14:46</t>
+          <t>2026-09-16 12:56:33</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US0040VN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Vivobook 14 X1404MA - EB028W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>23690000</v>
+        <v>23990000</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>31990000</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 x USB-C (USB 5Gbps), with USB PD 45-65W and DisplayPort 1.2 1x Headphone / microphone combo jack (3.5 mm) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 18 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe RAM) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Hãng không công bố | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 21.39 mm - Rộng 32.49 mm - Dày 1.79 mm - 1.4 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-5-322-83us0040vn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1404ma-core-5-320-eb028w</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:14:59</t>
+          <t>2026-09-16 12:56:46</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US003YVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Vivobook 14 X1407CA - LY203W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>28990000</v>
+        <v>24090000</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>36990000</v>
+        <v>33490000</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>-22%</t>
+          <t>-28%</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 19.9 mm - 1.46 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us003yvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1407ca-ultra-5-225h-ly203w</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:15:14</t>
+          <t>2026-09-16 12:56:58</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14IPH11 - 83S5004FVN (Ultra 7 355, 16GB, 512GB, WUXGA OLED, Win11)</t>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ385W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>34990000</v>
+        <v>23990000</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>37990000</v>
+        <v>31990000</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14iph11-ultra-7-355-83s5004fvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-5-320-bq385w</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:15:27</t>
+          <t>2026-09-16 12:57:11</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkBook 14 G9 - 21V0005PVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Vivobook 15 X1504MA - BQ395W (Core 7 350, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>33390000</v>
+        <v>27990000</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>35290000</v>
+        <v>35490000</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Wildcat Lake - 350 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 17 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-g9-r7-250-21v0005pvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-7-350-bq395w</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:15:40</t>
+          <t>2026-09-16 12:57:24</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkBook 14 Gen 9 IRL - 21UY008TVN (i5 13420H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Vivobook 16 X1607CA - MB387W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>31190000</v>
+        <v>24590000</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>32890000</v>
+        <v>33490000</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-27%</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 SO-DIMM | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 25.06 mm - Rộng 35.7 mm - Dày 1.79 ~ 1.99 - 1.88 kg | Chất liệu:: Khung nhôm - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-gen-9-irl-i5-13420h-21uy008tvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-16-x1607ca-ultra-5-225h-mb387w</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:15:53</t>
+          <t>2026-09-16 12:57:39</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkBook 16 G9 - 21UT005MVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Vivobook Go 14 E1404FA - EB012W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>30190000</v>
+        <v>18790000</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>31590000</v>
+        <v>22990000</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356 mm - Rộng 253.5 mm - Dày 17.5 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-16-g9-r7-250-21ut005mvn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb012w</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:16:07</t>
+          <t>2026-09-16 12:57:52</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad E14 - 21T90025VN (Gen 7 Core 7 240H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Asus Vivobook Go 14 E1404FA - EB1832W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>34190000</v>
+        <v>18790000</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>35590000</v>
+        <v>22990000</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: P-core 2.5/ 5.2 GHz, E-core 1.8/ 4.0 GHz | Card màn hình:: Card tích hợp - Integrated Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare 300 nits | Cổng giao tiếp:: 1x USB-A (USB 10Gbps / USB 3.2 Gen 2), Always On 1x Headphone / microphone combo jack (3.5 mm) 1x USB-C® (Thunderbolt™ 4 / USB4® 40 Gbps), with USB PD 15-65W and DisplayPort™ 2.1 1x HDMI® 2.1, up to 4K/6 0Hz 1x Ethernet (RJ-45) 1x USB-A (USB 5 Gbps / USB 3.2 Gen 1) | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: FHD 1080p + IR Hybrid with Privacy Shutter | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Stereo speakers, 2W x2, Dolby Atmos®, audio by HARMAN 2x, Array | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ Discrete TPM 2.0 Enabled | Thông tin Pin:: 3-cell, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 04/2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 10.1/15.25 (front/rear), 19.7 (maximum) mm - 1.34 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-core-7-240h-21t90025vn</t>
+          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb1832w</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:16:22</t>
+          <t>2026-09-16 12:58:05</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad E14 - 21SX002YVN (Gen 7 Ultra 255H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Lenovo ThinkPad E14 - 21T90025VN (Gen 7 Core 7 240H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>39190000</v>
+        <v>34190000</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>40590000</v>
+        <v>35590000</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.10 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140T | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 1x USB-A (USB 10Gbps / USB 3.2 Gen 2), Always On 1x HDMI® 2.1, up to 4K/60 Hz 1x Headphone / microphone combo jack (3.5 mm) 1x USB-C® (Thunderbolt™ 4 / USB4® 40 Gbps), with USB PD 15-65W and DisplayPort™ 2.1 1x Ethernet (RJ-45) 1x USB-A (USB 5 Gbps / USB 3.2 Gen 1) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD 1080p + IR Hybrid with Privacy Shutter | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Stereo speakers, 2W x2, Dolby Atmos®, audio by HARMAN 2x, Array | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 04/2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 10.1/15.25 (front/rear), 19.7 (maximum) mm - 1.34 kg | Chất liệu:: Vỏ kim loại - Nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 7 - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: P-core 2.5/ 5.2 GHz, E-core 1.8/ 4.0 GHz | Card màn hình:: Card tích hợp - Integrated Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare 300 nits | Cổng giao tiếp:: 1x USB-A (USB 10Gbps / USB 3.2 Gen 2), Always On 1x Headphone / microphone combo jack (3.5 mm) 1x USB-C® (Thunderbolt™ 4 / USB4® 40 Gbps), with USB PD 15-65W and DisplayPort™ 2.1 1x HDMI® 2.1, up to 4K/6 0Hz 1x Ethernet (RJ-45) 1x USB-A (USB 5 Gbps / USB 3.2 Gen 1) | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: FHD 1080p + IR Hybrid with Privacy Shutter | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Stereo speakers, 2W x2, Dolby Atmos®, audio by HARMAN 2x, Array | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ Discrete TPM 2.0 Enabled | Thông tin Pin:: 3-cell, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 04/2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 10.1/15.25 (front/rear), 19.7 (maximum) mm - 1.34 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-255h-21sx002yvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-core-7-240h-21t90025vn</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2420,83 +2408,83 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:03:50</t>
+          <t>2026-09-16 15:38:50</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX005NVN (Ultra 5 225U, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Lenovo ThinkPad E14 - 21SX002YVN (Gen 7 Ultra 255H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>36490000</v>
+        <v>39190000</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>38390000</v>
+        <v>40590000</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4 với USB Power Delivery và DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.10 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140T | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 1x USB-A (USB 10Gbps / USB 3.2 Gen 2), Always On 1x HDMI® 2.1, up to 4K/60 Hz 1x Headphone / microphone combo jack (3.5 mm) 1x USB-C® (Thunderbolt™ 4 / USB4® 40 Gbps), with USB PD 15-65W and DisplayPort™ 2.1 1x Ethernet (RJ-45) 1x USB-A (USB 5 Gbps / USB 3.2 Gen 1) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD 1080p + IR Hybrid with Privacy Shutter | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Stereo speakers, 2W x2, Dolby Atmos®, audio by HARMAN 2x, Array | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 04/2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 10.1/15.25 (front/rear), 19.7 (maximum) mm - 1.34 kg | Chất liệu:: Vỏ kim loại - Nhôm</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-225u-21sx005nvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-255h-21sx002yvn</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:04:03</t>
+          <t>2026-09-16 15:39:04</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad X9 14 Gen 1 - 21QA006JVN (Ultra 7 258V, 32GB, 512GB, WUXGA OLED, Win11Pro)</t>
+          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX005NVN (Ultra 5 225U, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>53790000</v>
+        <v>36490000</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>55190000</v>
+        <v>38390000</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.80 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Chống chói Anti Glare Dolby Vision 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm HDMI 2.1 2 x USB-C (hỗ trợ Thunderbolt 4/USB 4, USB Power Delivery và DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.8 mm - Rộng 212.3 mm - Dày 17.18 mm - 1.21 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4 với USB Power Delivery và DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-x9-14-gen-1-ultra-7-258v-21qa006jvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-225u-21sx005nvn</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2506,40 +2494,40 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:04:17</t>
+          <t>2026-09-16 15:39:18</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo V14 G5 - 83HD0035VN (Core7 240H, 16G, 512GB, Full HD, Win11)</t>
+          <t>Laptop Lenovo ThinkPad X9 14 Gen 1 - 21QA006JVN (Ultra 7 258V, 32GB, 512GB, WUXGA OLED, Win11Pro)</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>31290000</v>
+        <v>53790000</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>32690000</v>
+        <v>55190000</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) LAN (RJ45) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Ion, 47 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324.2 mm - Rộng 215.2 mm - Dày 17.9 mm - 1.37 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.80 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Chống chói Anti Glare Dolby Vision 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm HDMI 2.1 2 x USB-C (hỗ trợ Thunderbolt 4/USB 4, USB Power Delivery và DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.8 mm - Rộng 212.3 mm - Dày 17.18 mm - 1.21 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-v14-g5-core7-240h-83hd0035vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-x9-14-gen-1-ultra-7-258v-21qa006jvn</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2549,40 +2537,40 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:04:31</t>
+          <t>2026-09-16 15:39:32</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002LVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo V14 G5 - 83HD0035VN (Core7 240H, 16G, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>38490000</v>
+        <v>31290000</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>44990000</v>
+        <v>32690000</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) LAN (RJ45) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Ion, 47 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324.2 mm - Rộng 215.2 mm - Dày 17.9 mm - 1.37 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-5-322-83tc002lvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-v14-g5-core7-240h-83hd0035vn</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2592,21 +2580,21 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:04:45</t>
+          <t>2026-09-16 15:39:45</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002MVN (Ultra 7 355, 32GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002LVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>55990000</v>
+        <v>38490000</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>64990000</v>
+        <v>44990000</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
@@ -2620,12 +2608,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.95 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-7-355-83tc002mvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-5-322-83tc002lvn</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2635,25 +2623,25 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:04:58</t>
+          <t>2026-09-16 15:39:59</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 - 83QM0075VN (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002MVN (Ultra 7 355, 32GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>40990000</v>
+        <v>55990000</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>46990000</v>
+        <v>64990000</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2663,29 +2651,29 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe 600nits (peak) Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 70 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 04/2026 | Kích thước:: Dài 221 mm - Rộng 312 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.95 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-14iph11-ultra-7-355-83qm0075vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-7-355-83tc002mvn</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:05:13</t>
+          <t>2026-09-16 15:40:13</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 - 83QM0076VN (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 - 83QM0075VN (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
@@ -2706,12 +2694,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.00 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Khoảng 13 TOPS (NPU); tổng nền tảng AI của Intel đạt khoảng 99 TOPS (CPU + GPU + NPU) | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: 4 Xe-Cores | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7467 MT/s | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB PCIe 4.0 NVMe SSD | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: OLED Chuẩn DisplayHDR True Black 600 Low Blue Light Eyesafe Dolby Vision | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 2 x Thunderbolt 4 USB-C HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Chốt khóa webcam FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hệ thống quạt kép (Dual Fan) | Tính năng khác:: TPM 2.0 | Thông tin Pin:: 70 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 221 mm - Rộng 312 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Vỏ hợp kim Nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe 600nits (peak) Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 70 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 04/2026 | Kích thước:: Dài 221 mm - Rộng 312 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-14iph11-ultra-7-355-83qm0076vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-14iph11-ultra-7-355-83qm0075vn</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2721,25 +2709,25 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:05:27</t>
+          <t>2026-09-16 15:40:30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK0015VN (Ultra 7 355, 32GB, 1TB, WQXGA+ 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 - 83QM0076VN (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>62990000</v>
+        <v>40990000</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>72990000</v>
+        <v>46990000</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2749,12 +2737,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe 4.0x4 NVMe (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: 500 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.6 mm - Rộng 213.8 mm - Dày 13.9 mm - 0.975 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.00 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Khoảng 13 TOPS (NPU); tổng nền tảng AI của Intel đạt khoảng 99 TOPS (CPU + GPU + NPU) | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: 4 Xe-Cores | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7467 MT/s | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB PCIe 4.0 NVMe SSD | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: OLED Chuẩn DisplayHDR True Black 600 Low Blue Light Eyesafe Dolby Vision | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 2 x Thunderbolt 4 USB-C HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Chốt khóa webcam FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hệ thống quạt kép (Dual Fan) | Tính năng khác:: TPM 2.0 | Thông tin Pin:: 70 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 221 mm - Rộng 312 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Vỏ hợp kim Nhôm</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-7-355-83qk0015vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-14iph11-ultra-7-355-83qm0076vn</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2764,25 +2752,25 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:05:40</t>
+          <t>2026-09-16 15:40:43</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK006GVN (Ultra 7 355, 32GB, 1TB, WQXGA+ 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK0015VN (Ultra 7 355, 32GB, 1TB, WQXGA+ 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>64990000</v>
+        <v>62990000</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>66990000</v>
+        <v>72990000</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2792,12 +2780,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe 4.0x4 NVMe (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Eyesafe DisplayHDR True Black 1000 500 nits Corning Gorilla Glass 3 Dolby Vision PureSight Pro Flicker Free 1100 nits (peak) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.6 mm - Rộng 213.8 mm - Dày 13.9 mm - 0.975 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe 4.0x4 NVMe (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: 500 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.6 mm - Rộng 213.8 mm - Dày 13.9 mm - 0.975 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-7-355-83qk006gvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-7-355-83qk0015vn</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2807,25 +2795,25 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:05:54</t>
+          <t>2026-09-16 15:40:58</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK009PVN (Ultra X9 378H, 32GB, 1TB, WQXGA+ 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK006GVN (Ultra 7 355, 32GB, 1TB, WQXGA+ 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>68990000</v>
+        <v>64990000</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>79990000</v>
+        <v>66990000</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2835,12 +2823,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra X9 - 378H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.00 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 32 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 9600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe® 4.0x4 NVMe® (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Eyesafe 500 nits typical DisplayHDR True Black 1000 Corning Gorilla Glass 3 500 nits Glossy Dolby Vision PureSight Pro Flicker Free 1100 nits (peak) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 18/05/2026 | Kích thước:: Dài 213.8 mm - Rộng 312.6 mm - Dày 13.9 mm - 0.975 kg</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe 4.0x4 NVMe (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Eyesafe DisplayHDR True Black 1000 500 nits Corning Gorilla Glass 3 Dolby Vision PureSight Pro Flicker Free 1100 nits (peak) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.6 mm - Rộng 213.8 mm - Dày 13.9 mm - 0.975 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-x9-378h-83qk009pvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-7-355-83qk006gvn</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2850,68 +2838,68 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:06:07</t>
+          <t>2026-09-16 15:41:11</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 Black Edition A13VEO - 2610VN (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK009PVN (Ultra X9 378H, 32GB, 1TB, WQXGA+ 120Hz, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>27890000</v>
+        <v>68990000</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>31990000</v>
+        <v>79990000</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell, 53.5Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 250.3 mm - Dày 22.9 mm - 1,.98 | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra X9 - 378H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.00 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 32 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 9600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe® 4.0x4 NVMe® (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Eyesafe 500 nits typical DisplayHDR True Black 1000 Corning Gorilla Glass 3 500 nits Glossy Dolby Vision PureSight Pro Flicker Free 1100 nits (peak) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 18/05/2026 | Kích thước:: Dài 213.8 mm - Rộng 312.6 mm - Dày 13.9 mm - 0.975 kg</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-black-edition-a13veo-i5-13420h-2610vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-x9-378h-83qk009pvn</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:06:21</t>
+          <t>2026-09-16 15:41:26</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 Black Edition A13VEO - 2608VN (i7 13620H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop MSI Cyborg 15 Black Edition A13VEO - 2610VN (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>29890000</v>
+        <v>27890000</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>33990000</v>
+        <v>31990000</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2921,12 +2909,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 1.8 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell, 53.5Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 250.3 mm - Dày 22.9 mm - 1,.98 | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell, 53.5Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 250.3 mm - Dày 22.9 mm - 1,.98 | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-black-edition-a13veo-i7-13620h-2608vn</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-black-edition-a13veo-i5-13420h-2610vn</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2936,25 +2924,25 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:06:34</t>
+          <t>2026-09-16 15:41:39</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 C13WEO - 418VN (i5 13420H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop MSI Cyborg 15 Black Edition A13VEO - 2608VN (i7 13620H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>30990000</v>
+        <v>29890000</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>34990000</v>
+        <v>33990000</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2964,12 +2952,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 70 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 1.982 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 1.8 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell, 53.5Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 250.3 mm - Dày 22.9 mm - 1,.98 | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-c13weo-i5-13420h-418vn</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-black-edition-a13veo-i7-13620h-2608vn</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2979,64 +2967,64 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:06:48</t>
+          <t>2026-09-16 15:41:53</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 Max C13WE - 422VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop MSI Cyborg 15 C13WEO - 418VN (i5 13420H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>41590000</v>
+        <v>30990000</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>42990000</v>
+        <v>34990000</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x SuperSpeed USB Type-A LAN (RJ45) HDMI 2.1 2 x USB 3.2 1 x USB Type-C 3.2 (hỗ trợ Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: 3 ống đồng Cooler Boost 2 quạt | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 2 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 70 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 1.982 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-max-c13we-422vn-i7-13620h</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-c13weo-i5-13420h-418vn</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:07:02</t>
+          <t>2026-09-16 15:42:06</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 Max C13WF - 421VN (i7 13620H, 16GB, 512GB, RTX 5060 8GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop MSI Cyborg 15 Max C13WE - 422VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>43590000</v>
+        <v>41590000</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>44990000</v>
+        <v>42990000</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
@@ -3050,12 +3038,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x SuperSpeed USB Type-A LAN (RJ45) HDMI 2.1 2 x USB 3.2 1 x USB Type-C 3.2 (hỗ trợ Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: 3 ống đồng Cooler Boost 2 quạt | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 2 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x SuperSpeed USB Type-A LAN (RJ45) HDMI 2.1 2 x USB 3.2 1 x USB Type-C 3.2 (hỗ trợ Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: 3 ống đồng Cooler Boost 2 quạt | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 2 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-max-c13wf-421vn-i7-13620h</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-max-c13we-422vn-i7-13620h</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3065,107 +3053,107 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:07:15</t>
+          <t>2026-09-16 15:42:19</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Gaming Cyborg 15 C13WEO-417VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop MSI Cyborg 15 Max C13WF - 421VN (i7 13620H, 16GB, 512GB, RTX 5060 8GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>34590000</v>
+        <v>43590000</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>36990000</v>
+        <v>44990000</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - Intel UHD Graphics (tích hợp) + NVIDIA GeForce RTX 5050 GPU, 8GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB Type-A 1 x Headphone/ Microphone combo audio jack 1 x USB Type C (chỉ hỗ trợ Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: DTS Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.98 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x SuperSpeed USB Type-A LAN (RJ45) HDMI 2.1 2 x USB 3.2 1 x USB Type-C 3.2 (hỗ trợ Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: 3 ống đồng Cooler Boost 2 quạt | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 2 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-c13weo-417vn-i7-13620h</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-max-c13wf-421vn-i7-13620h</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:07:29</t>
+          <t>2026-09-16 15:42:32</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14S G3MG-003VN (Core 5 320, 16GB, 1TB, Full HD+ 120Hz, Win11)</t>
+          <t>Laptop MSI Gaming Cyborg 15 C13WEO-417VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>27990000</v>
+        <v>34590000</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>31490000</v>
+        <v>36990000</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: SSD 1TB, chuẩn M.2 2280 NVMe PCIe Gen4, tối đa hỗ trợ 2TB | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 50% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 2 x USB 3.2 gen 1 Type-A LAN (RJ45) HDMI 2.1 2 x USB Type-C 3.2 Gen 2 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD card reader | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: DTS | Tản nhiệt:: 2 ống đồng 1 x Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.39 mm - Rộng 31.59 mm - Dày 1.11 ~ 1.79 - 1.45 kg | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - Intel UHD Graphics (tích hợp) + NVIDIA GeForce RTX 5050 GPU, 8GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB Type-A 1 x Headphone/ Microphone combo audio jack 1 x USB Type C (chỉ hỗ trợ Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: DTS Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.98 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-modern-14s-g3mg-003vn-core-5-320</t>
+          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-c13weo-417vn-i7-13620h</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:07:43</t>
+          <t>2026-09-16 15:42:46</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1264VN (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop MSI Modern 14S G3MG-003VN (Core 5 320, 16GB, 1TB, Full HD+ 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>19990000</v>
+        <v>27990000</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>22390000</v>
+        <v>31490000</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
@@ -3174,41 +3162,41 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core thế hệ 12 - 120U | Số nhân:: Hãng không công bố | Số luồng:: 12 | Tốc độ CPU:: 1.45 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (2280) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: Hãng không công bố | Cổng giao tiếp:: 3 x USB 3.2 Gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell, 46.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.7 kg | Chất liệu:: Plastic (nhựa dẻo)</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: SSD 1TB, chuẩn M.2 2280 NVMe PCIe Gen4, tối đa hỗ trợ 2TB | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 50% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 2 x USB 3.2 gen 1 Type-A LAN (RJ45) HDMI 2.1 2 x USB Type-C 3.2 Gen 2 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD card reader | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: DTS | Tản nhiệt:: 2 ống đồng 1 x Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.39 mm - Rộng 31.59 mm - Dày 1.11 ~ 1.79 - 1.45 kg | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-modern-15-f1mg-1264vn-core-5-120u</t>
+          <t>https://www.thegioididong.com/laptop/msi-modern-14s-g3mg-003vn-core-5-320</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:07:58</t>
+          <t>2026-09-16 15:43:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Laptop SingPC M16-i382 (i3 1215U, 8GB, 256GB, WUXGA, Win11 Pro)</t>
+          <t>Laptop MSI Modern 15 F1MG-1264VN (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>13490000</v>
+        <v>19990000</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>15190000</v>
+        <v>22390000</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
@@ -3217,60 +3205,60 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i3 Alder Lake - 1215U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.2GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 256 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core thế hệ 12 - 120U | Số nhân:: Hãng không công bố | Số luồng:: 12 | Tốc độ CPU:: 1.45 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (2280) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: Hãng không công bố | Cổng giao tiếp:: 3 x USB 3.2 Gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell, 46.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.7 kg | Chất liệu:: Plastic (nhựa dẻo)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/singpc-m16-i382-i3-1215u</t>
+          <t>https://www.thegioididong.com/laptop/msi-modern-15-f1mg-1264vn-core-5-120u</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:08:11</t>
+          <t>2026-09-16 15:43:16</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Laptop SingPC M16-i595 (i5 1235U, 16GB, 512GB, WUXGA, Win11 Pro)</t>
+          <t>Laptop SingPC M16-i382 (i3 1215U, 8GB, 256GB, WUXGA, Win11 Pro)</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>17390000</v>
+        <v>13490000</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>19990000</v>
+        <v>15190000</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Alder Lake - 1235U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 72% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i3 Alder Lake - 1215U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.2GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 256 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/singpc-m16-i595-i5-1235u</t>
+          <t>https://www.thegioididong.com/laptop/singpc-m16-i382-i3-1215u</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3280,64 +3268,64 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:08:25</t>
+          <t>2026-09-16 15:43:29</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go AI SFG14-75-765M - NX.JNBSV.004 (Ultra 7 258V, 32GB, 512GB, Full HD+, Win11)</t>
+          <t>Laptop SingPC M16-i595 (i5 1235U, 16GB, 512GB, WUXGA, Win11 Pro)</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>39990000</v>
+        <v>17390000</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>41990000</v>
+        <v>19990000</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số luồng:: 8 | Tốc độ CPU:: 2.2 GHz | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: Lên đến 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Wide viewing angle ACER CineCrystal 400 nits | Cổng giao tiếp:: 1 x USB 3.2 Gen 1 (hỗ trợ Power-off USB charging) HDMI 2.1 Micro SD 2 x USB Type-C (hỗ trợ DisplayPort, Thunderbolt 4) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD card reader | Webcam:: HP True Vision 1080p FHD camera ToF Sensor Camera with Dual Microphone Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Công nghệ âm thanh:: Hi-Res Audio Spatial Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: Li-ion, 65 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 227.4 mm - Rộng 312.4 mm - Dày 9.7/15.95 (H) - 1.24 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i5 Alder Lake - 1235U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 72% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-swift-go-ai-sfg14-75-765m-ultra-7-258v-nx-jnbsv-004</t>
+          <t>https://www.thegioididong.com/laptop/singpc-m16-i595-i5-1235u</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:37:19</t>
+          <t>2026-09-16 15:43:42</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP - U716S8W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-977M - NX.W26SV.001 (Ultra 9 185H, 16GB, 512GB, Full HD+, Win11)</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>32990000</v>
+        <v>29990000</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>34990000</v>
+        <v>31990000</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
@@ -3346,447 +3334,447 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 430 mm - Rộng 316 mm - Dày 19.9 mm - 2.61 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 9 Meteor Lake - 185H | Số luồng:: 22 | Tốc độ CPU:: 2.30 GHz (Lên đến 5.10 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (1 khe onboard) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB Type-C (65W) 1 x USB Type-C LAN (RJ45) HDMI 2.1 USB Type-C | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Stereo speakers | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 10 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.6 mm - Rộng 227.7 mm - Dày 17.9 mm - 1.49 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-p3-p3406ccap-ultra-7-255h-u716s8w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-go-14-ai-ag14-i71m-977m-ultra-9-185h-nx-w26sv-001</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:37:32</t>
+          <t>2026-09-16 11:49:12</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA - NZ1368W (Ultra 5 226V, 16GB, 512GB, WQXGA 144Hz, Win11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR - NX.X0PSV.002 (Ryzen 5 3500U, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>30090000</v>
+        <v>17990000</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>31990000</v>
+        <v>20990000</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Lunar Lake - 226V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 40 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 130V | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Anti-Glare Màn hình Wide View 400 nits | Cổng giao tiếp:: 2 x Thunderbolt 4 1 x 3.5mm combo audio jack HDMI 2 x USB 3.2 gen 2 Type-A | Kết nối không dây:: Hãng không công bố | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in array microphone Dolby Atmos | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 223 mm - Dày 12.8 ~ 16.4 mm - 1.2 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 3500U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz | Card màn hình:: Card tích hợp - AMD Radeon Vega Mobile Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 2400 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: IPS LED-backlit TFT LCD Wide viewing angle 250 nits | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A HDMI 1 x SuperSpeed USB Type-C (hỗ trợ DisplayPort 1.4) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP FHD 1080p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: 2 loa 2 microphones | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Phím Copilot | Thông tin Pin:: 2-cell Li-ion, 45.6 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 210.2 mm - Rộng 322.6 mm - Dày 19.8 mm - 1.3 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-p5-p5405csa-ultra-5-226v-nz1368w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-nx-x0psv-002</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:37:45</t>
+          <t>2026-09-16 11:49:26</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA - NZ1371W (Ultra 7 258V, 32GB, 512GB, WQXGA 144Hz, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN - NX.DDASV.001 (Core 3 N350, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>37490000</v>
+        <v>16990000</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>39490000</v>
+        <v>18990000</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Intel Arc 140V | Số nhân GPU:: Hãng không công bố | RAM:: 32 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Anti-Glare Màn hình Wide View 400 nits | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 Type-A 1 x Thunderbolt 4 (hỗ trợ DisplayPort) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Smart Amp Technology Built-in array microphone Dolby Atmos | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 223 mm - Dày 12.8 ~ 16.4 mm - 1.2 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - N350 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 3.90 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB 3.2 HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.0 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.8 mm - Rộng 235.6 mm - Dày 19.7 mm - 1.53 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-p5-p5405csa-ultra-7-258v-nz1371w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-36p-30tn-core-3-n350-nx-ddasv-001</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:37:58</t>
+          <t>2026-09-16 11:49:39</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook Ultra B9 B9406CAA - X7642TW (Ultra X7 358H, 64GB, 2TB, WQXGA+ OLED 120Hz, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 - NX.X0RSV.001 (Ryzen 5 3500U, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>97990000</v>
+        <v>17990000</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>100000000</v>
+        <v>20990000</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra X7 Panther Lake | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 2 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 1 x USB Type-C (hỗ trợ cổng Thunderbolt 4) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Có | Công nghệ âm thanh:: Built-in speaker Built-in array microphone Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 28.8 mm - Rộng 12.7 mm - Dày 38.9 mm - 1.131 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 3500U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz | Card màn hình:: Card tích hợp - AMD Radeon Vega Mobile Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 2400 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: IPS Màn hình Wide View Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A HDMI 1 x SuperSpeed USB Type-C (hỗ trợ DisplayPort 1.4) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP FHD 1080p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: 2 loa 2 microphones | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Phím Copilot | Thông tin Pin:: 2-cell Li-ion, 45.6 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 229.3 mm - Rộng 357.4 mm - Dày 19.85 mm - 1.5 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-b9-b9406caa-ultra-x7-358h-x7642tw</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-nx-x0rsv-001</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:38:11</t>
+          <t>2026-09-16 11:49:53</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook Ultra B9 B9406CAA - X7321TW (Ultra X7 358H, 32GB, 1TB, WQXGA+ OLED 120Hz, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-44P-R4UH - NX.DJVSV.002 (R7 7730U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>65990000</v>
+        <v>21990000</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>68000000</v>
+        <v>23990000</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra X7 Panther Lake - 358H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare 600 nits Pantone Validated | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x Thunderbolt 4 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Built-in speaker Built-in array microphone Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.9 mm - Dày 16.4 mm - 1.1 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB Type - C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 230.2 mm - Dày 18.6 mm - 1.49 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-b9-b9406caa-x7321tw-ultra-x7-358h-32gb-1tb-wqxga-oled-120hz-win11</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-44p-r4uh-r7-7730u-nx-djvsv-002</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:38:25</t>
+          <t>2026-09-16 11:50:06</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0045W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC - NX.DG3SV.002.16G (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>30990000</v>
+        <v>21990000</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>33990000</v>
+        <v>24990000</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 1 x USB Type-C with Thunderbolt 5 (hỗ trợ USB 4, DisplayPort 2.1 và Power Delivery 3.0) | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 357.6 mm - Rộng 228.5 mm - Dày 18.7 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-5-225h-sf0045w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-53p-56ec-core-5-120u-nx-dg3sv-002-16g</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:38:38</t>
+          <t>2026-09-16 11:50:19</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0241W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Acer Aspire Lite 16 AL16-71P-582Q - NX.DRSSV.001 (Ultra 5 125H, 16GB, 512GB, Full HD+ 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>35990000</v>
+        <v>24990000</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>37990000</v>
+        <v>26990000</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display Màn hình Wide View | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 125H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357 mm - Rộng 245.5 mm - Dày 18.9 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-7-255-sf0241w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-16-al16-71p-582q-ultra-5-125h-nx-drssv-001</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:38:51</t>
+          <t>2026-09-16 11:50:33</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0047W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Acer Gaming Aspire 7 A715-59G-59RD - NH.DXUSV.001 (Core 5 210H, 16GB, 512GB, RTX 3050 4GB, Fulll HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>35990000</v>
+        <v>26990000</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>37990000</v>
+        <v>31990000</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display Màn hình Wide View | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 4 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35W - 80W | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 4 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle 350 nits Acer ComfyView | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C (hỗ trợ DisplayPort 1.4) LAN (RJ45) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn LED - 15 chế độ màu | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 359.5 mm - Rộng 238 mm - Dày 22.7 mm - 1.99 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-7-255h-sf0047w</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-aspire-7-a715-59g-59rd-core-5-210h-nh-dxusv-001</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:39:04</t>
+          <t>2026-09-16 11:50:46</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming ROG Strix G16 G614PM - TS147W (R9 8940HX, 16GB, 512GB, RTX 5060 8GB, WQXGA 300Hz, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel AN16S-61-R9CN - NH.QXGSV.001 (Ryzen AI 7 350, 16GB, 512GB, RTX 5070 8GB, 2K+ 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>54990000</v>
+        <v>57990000</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>57990000</v>
+        <v>64990000</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115W - 140W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.288 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.0 GHz (Lên đến 5.2 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits 3ms | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: NVIDIA Optimus | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pm-r9-8940hx-ts147w</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-an16s-61-r9cn-ryzen-ai-7-350-nh-qxgsv-001</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:39:17</t>
+          <t>2026-09-16 11:51:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming ROG Strix G16 G614PR - TS103W (R9 8940HX, 16GB, 512GB, RTX 5070Ti 12GB, WQXGA 300Hz, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-556L - NH.QZ9SV.006 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>70590000</v>
+        <v>38990000</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>71990000</v>
+        <v>40990000</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070Ti, 12 GB | Số nhân GPU:: 5888 CUDA Cores | Công suất đồ hoạ - TGP:: 140 W | Hiệu năng xử lý AI (TOPS):: Lên đến 992 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.34 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 60W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 16:9 aspect ratio Ultra-slim design Mercury free, environment friendly Thời gian phản hồi: 3 ms LED-backlit TFT LCD Wide viewing angle 300 nits Acer ComfyView | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Ethernet (LAN) Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: 720p at 30 fps HD camera | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High SNR DAC 2.1 Vrms Hỗ trợ tai nghe đến 600 Ω Compatible with Cortana with Voice 2 microphones Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Tính năng khác:: NitroSense Key Copilot Key | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 239.89 mm - Rộng 362.3 mm - Dày 115.7/23.5 - 2.1 kg | Chất liệu:: Nhựa nguyên khối</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pr-r9-8940hx-ts103w</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-556l-core-5-210h-nh-qz9sv-006</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:39:31</t>
+          <t>2026-09-16 11:51:14</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming V16 V3607VJ Core 5 - TK189W (Core 5 210H, 16GB, 512GB, RTX 3050 6GB, WUXGA 144Hz, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-73Z8 - NH.QUASV.001 (Core 7 240H, 16GB, 512GB, RTX 4050 6GB, Full HD  180Hz, Win11)</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>25990000</v>
+        <v>35990000</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>36990000</v>
+        <v>39990000</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 6 GB | Công suất đồ hoạ - TGP:: 65 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% Adobe | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x 3.5mm combo audio jack HDMI 2.1 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: 1080p with Privacy Shutter | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in microphone | Tản nhiệt:: 2 quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 63 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 251 mm - Dày 22 mm - 1.95 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: IPS | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1x Ethernet 3 x USB 3.2 Gen 1 Type-A 1 x USB Type-C (65W) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: 720p at 30 fps HD camera Camera with Dual Microphone | Đèn bàn phím:: Đơn sắc - Màu cam | Công nghệ âm thanh:: Windows Spatial Sound High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-v16-v3607vj-core-5-core-5-210h-tk189w</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-73z8-core-7-240h-nh-quasv-001</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3796,1060 +3784,1072 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:39:45</t>
+          <t>2026-09-16 11:51:28</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming V16 V3607VU - TK416W (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, WUXGA 144Hz, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-78MD - NH.QZ9SV.007 (Core 7 240H, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>32990000</v>
+        <v>40990000</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>41990000</v>
+        <v>43990000</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 65 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 2 khe (1 khe 16 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x 3.5mm combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.3 | Webcam:: 1080p FHD camera | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: Mô-đun bảo mật TPM (Firmware TPM) Mật khẩu thiết lập BIOS | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in microphone | Tản nhiệt:: 2 quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 63 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 250.7 mm - Dày 18 mm - 1.95 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms 300 nits Acer ComfyView | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2 microphones Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Nhựa nguyên khối</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-v16-v3607vu-core-5-210h-tk416w</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-78md-core-7-240h-nh-qz9sv-007</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:39:58</t>
+          <t>2026-09-16 11:51:41</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ProArt P1 H7606WP - SR335W (R9 AI HX 370, 64GB, 2TB, RTX 5070 8GB, 3K 120Hz, Cảm ứng, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-61-R0B8 - NH.QXQSV.001 (Ryzen AI 5 340, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>114890000</v>
+        <v>42990000</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>124990000</v>
+        <v>47990000</v>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 9 - Hãng không công bố | Số nhân:: 12 | Số luồng:: 24 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 2 TB SSD M.2 NVMe PCIe Gen 4 | Kích thước màn hình:: 16" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 500 nits (Khi bật HDR) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354.9 mm - Rộng 246.9 mm - Dày 17.3 mm - 1.85 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.40 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-proart-p1-h7606wp-r9-ai-hx-370-sr335w</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-61-r0b8-ryzen-ai-5-340-nh-qxqsv-001</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:40:11</t>
+          <t>2026-09-16 11:51:55</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus TUF Gaming A15 FA506NCG - HN390W (R7 155, 16GB, 512GB, RTX 3050 4GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-71-58WQ - NH.QXBSV.001 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, 2K+ 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>27490000</v>
+        <v>44990000</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>37490000</v>
+        <v>46990000</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>-27%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 155 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.0 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 4 GB | RAM:: 16 GB | Loại RAM:: DDR5 2 khe (1 khe 16 GB + 1 khe trống) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 62.5% sRGB 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 Gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: HD webcam | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Built-in array microphone | Tản nhiệt:: 2 quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 256 mm - Dày 24.5 mm - 2.30 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-tuf-gaming-a15-fa506ncg-r7-155-hn390w</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-71-58wq-core-5-210h-nh-qxbsv-001</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:40:24</t>
+          <t>2026-09-16 11:52:08</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1404MA - EB028W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Acer Gaming Predator Helios Neo 16S PHN16S-I51-97T9 - NH.U3SSV.006 (Ultra 9 386H, 16GB, 512GB, RTX 5070 8GB, 2K+ 165Hz, Win11)</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>23990000</v>
+        <v>75990000</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>31990000</v>
+        <v>77990000</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe RAM) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Hãng không công bố | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 21.39 mm - Rộng 32.49 mm - Dày 1.79 mm - 1.4 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 9 Panther Lake - 386H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 50 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: LED-backlit TFT LCD 500 nits Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 18.9 mm - 2.2 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1404ma-core-5-320-eb028w</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16s-phn16s-i51-97t9-ultra-9-386h</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:40:37</t>
+          <t>2026-09-16 11:52:22</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1407CA - LY203W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Acer Nitro ProPanel AN16S-61-R7ZJ - NH.QXFSV.002 (R7 AI 350, 16GB, 512GB, RTX 5060 8GB, 2K, Win11)</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>24490000</v>
+        <v>49990000</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>33490000</v>
+        <v>51990000</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>-27%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 19.9 mm - 1.46 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Nhôm &amp; Nhựa</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1407ca-ultra-5-225h-ly203w</t>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-an16s-61-r7zj-r7-ai-350-nhqxfsv002</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:40:49</t>
+          <t>2026-09-16 11:52:36</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ385W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Acer Nitro ProPanel ANV15-52-50RB - NH.QUASV.002 (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>23990000</v>
+        <v>33490000</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>31990000</v>
+        <v>37990000</v>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 60W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 300 nits Acer ComfyView 3ms | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2 microphones Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Tính năng khác:: Copilot Key | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-5-320-bq385w</t>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv15-52-50rb-core-5-210h-nh-quasv-002</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:41:02</t>
+          <t>2026-09-16 11:52:50</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ395W (Core 7 350, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Acer Nitro ProPanel ANV16-72-782F - NH.QUPSV.001 (Core 7 240H, 16GB, 512GB, RTX 5050 8GB, Full HD+ 180 Hz, Win11)</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>27990000</v>
+        <v>43990000</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>35490000</v>
+        <v>45990000</v>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Wildcat Lake - 350 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 17 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 80 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 360 mm - Rộng 274.5 mm - Dày 24.5 mm - 2.4 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-7-350-bq395w</t>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv16-72-782f-core-7-240h-nhqupsv001</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:41:15</t>
+          <t>2026-09-16 11:53:03</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 16 X1607CA - MB387W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Acer Nitro ProPanel ANV16S-61-R7KQ - NH.QXPSV.001 (R5 AI 340, 16GB, 512GB, RTX 5060 8GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>24590000</v>
+        <v>46990000</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>33490000</v>
+        <v>48990000</v>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>-27%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 SO-DIMM | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 25.06 mm - Rộng 35.7 mm - Dày 1.79 ~ 1.99 - 1.88 kg | Chất liệu:: Khung nhôm - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 400 nits | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB Type C 3.2 Gen 2 (Hỗ trợ Power Delivery và DisplayPort™ 2.1) LAN (RJ45) HDMI 2.1 3 x USB A | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD 1080p Camera IR | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Hi-Res certification Spatial Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-16-x1607ca-ultra-5-225h-mb387w</t>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv16s-61-r7kq-r5-ai-340-nhqxpsv001</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:41:28</t>
+          <t>2026-09-16 11:53:17</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook Go 14 E1404FA - EB012W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Acer Swift Air 14 SFA14-I31-34NF - NX.W49SV.001 (Core 3 304, 12GB, 512GB, WUXGA 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>18790000</v>
+        <v>21990000</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>22990000</v>
+        <v>23990000</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - 304 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 12 GB | Loại RAM:: LPDDR5 (1 khe onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Wide viewing angle 350 nits LED Backlight Acer ComfyView | Cổng giao tiếp:: 1 x USB 3.2 2 x USB Type-C (hỗ trợ USB, Power Delivery, DisplayPort và Thunderbolt 4) | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.3 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.99 mm - Rộng 222.65 mm - Dày 12.99 mm - 1.19 kg | Chất liệu:: Khung và mặt lưng kim loại</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb012w</t>
+          <t>https://www.thegioididong.com/laptop/acer-swift-air-14-sfa14-i31-34nf-core-3-304-nx-w49sv-001</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:41:42</t>
+          <t>2026-09-16 11:53:31</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook Go 14 E1404FA - EB1832W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Acer Swift Air 14 SFA14-I31-52BV - NX.W49SV.002 (Core 5 320, 12GB, 512GB, Full HD 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>18790000</v>
+        <v>24990000</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>22990000</v>
+        <v>26990000</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Đang cập nhật | RAM:: 12 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 350 nits | Cổng giao tiếp:: 1 x USB 3.2 2 x USB Type-C (hỗ trợ USB, Power Delivery, DisplayPort và Thunderbolt 4) | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.3 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 222.65 mm - Rộng 222.65 mm - Dày 12.99 mm - 1.19 kg | Chất liệu:: Khung và mặt lưng kim loại</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb1832w</t>
+          <t>https://www.thegioididong.com/laptop/acer-swift-air-14-sfa14-i31-52bv-core-5-320-nx-w49sv-002</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:41:55</t>
+          <t>2026-09-16 11:53:45</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ893W (Core 3 304, 8GB, 512GB, Full HD, Win 11)</t>
+          <t>Laptop Acer Swift Go AI SFG14-75-5264 - NX.JNBSV.001 (Ultra 5 226V, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>17990000</v>
+        <v>29990000</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>22990000</v>
+        <v>31990000</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>-22%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Wildcat Lake - 304 | Số nhân:: 5 | Số luồng:: 5 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.30 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 15 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits Chứng nhận TÜV Rheinland | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.7 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Lunar Lake - 226V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 3.50 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 40 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 130V | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: OLED | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe ACER CineCrystal 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 2 x USB4 Type-C (hỗ trợ truyền dữ liệu, DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 65Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 227.4 mm - Rộng 312.4 mm - Dày 15.95 mm - 1.24 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-15-x1504ma-core-3-304-bq893w</t>
+          <t>https://www.thegioididong.com/laptop/acer-swift-go-ai-sfg14-75-5264-ultra-5-226v-nxjnbsv001</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:20:48</t>
+          <t>2026-09-16 11:53:58</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook S 16 S3607VA - RP155W (Core 5 210H, 16GB, 512GB, Full HD+ 144Hz, Win11)</t>
+          <t>Laptop HP OmniBook 5 14 hh0075TU - D72CTPA (Ultra 5 322, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>26990000</v>
+        <v>35990000</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>34990000</v>
+        <v>36690000</v>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>-23%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare LED Backlit | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 259.6 mm - Dày 15.9 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.90 GHz (Lên đến 4.40 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 2 x Thunderbolt 4 (hỗ trợ truyền dữ liệu,Power Delivery,DisplayPort,HP Sleep and Charge) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 59.16 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 217.5 mm - Dày 13.6 mm - 1.337 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-s-16-s3607va-core-5-210h-rp155w</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-5-14-hh0075tu-ultra-5-322-d72ctpa</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:21:02</t>
+          <t>2026-09-16 12:16:47</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook S14 S3407VA - LY256W (Core 7 240H, 16GB, 512GB, WUXGA OLED, Win11)</t>
+          <t>Laptop HP OmniBook 7 14 fr0033TU - C1MN2PA (Ultra 5 225U, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>26990000</v>
+        <v>27490000</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>29990000</v>
+        <v>28990000</v>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 17.9 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 3.80 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Công suất đồ hoạ - TGP:: 15 - 25W | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 2600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Thunderbolt 4 with USB Type - C (hỗ trợ truyền dữ liệu, Power Delivery 3.1, DisplayPort 2.1,  HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB 3.2 gen 2 Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Poly Studio Dual speakers HP Audio Boost DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 4-cell, 64 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.65 mm - Rộng 31.4 mm - Dày 1.49 mm - 1.41 kg | Chất liệu:: Khung và mặt lưng kim loại, nhựa</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-s14-s3407va-core-7-240h-ly256w</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-7-14-fr0033tu-ultra-5-225u-c1mn2pa</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:21:17</t>
+          <t>2026-09-16 12:17:01</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Zenbook 14 UM3406GA - QD075W (R7 AI 445, 16GB, 512GB, WUXGA OLED, Win11)</t>
+          <t>Laptop HP OmniBook Ultra 14 kd0036TU - D72C6PA (Ultra 9 386H, 32GB, 1TB, 3K OLED 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>34590000</v>
+        <v>65190000</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>39990000</v>
+        <v>65890000</v>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.0 GHz | NPU:: AMD XDNA | Card màn hình:: Card tích hợp | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 70% Less harmful blue light 400 nits 600 nits (Khi bật HDR) | Cổng giao tiếp:: 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 75 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.01 mm - Rộng 31.24 mm - Dày 1.49 mm - 1.2 kg | Chất liệu:: Nhôm nguyên khối</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 9 Panther Lake - 386H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: up to 120 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light 500 nits Corning Gorilla Glass 3 | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery 3.1, DisplayPort 2.1) 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.1 mm - Rộng 215.6 mm - Dày 10.7 mm - 1.282 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-zenbook-14-um3406ga-r7-ai-445-qd075w</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-ultra-14-kd0036tu-ultra-9-386h-d72c6pa</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:21:31</t>
+          <t>2026-09-16 12:17:15</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC14250-C3U085W11SLU-2Y (Core 3 100U, 8GB, 512GB, Full HD+, OfficeH24+365, Win11)</t>
+          <t>Laptop HP OmniBook Ultra 14 kd0039TU - D72C7PA (Ultra 7 356H, 32GB, 1TB, 3K OLED 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>21490000</v>
+        <v>59190000</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>22590000</v>
+        <v>59890000</v>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 356H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz (Lên đến 4.7 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: up to 120 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 500 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery 3.1, DisplayPort 2.1) 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.1 mm - Rộng 215.6 mm - Dày 10.7 mm - 1.288 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-3-100u-dc14250-c3u085w11slu-2y</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-ultra-14-kd0039tu-ultra-7-356h-d72c7pa</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:21:45</t>
+          <t>2026-09-16 12:17:29</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC4C5375W1-2Y (Core 5 120U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+          <t>Laptop HP OmniBook X Flip 14 fk0082AU - BZ7N8PA (R7 AI 350, 32GB, 1TB, 2K, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>28990000</v>
+        <v>39890000</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>32090000</v>
+        <v>40890000</v>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226 mm - Dày 18 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: 2K (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Corning Gorilla Glass 3 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB Type-C (hỗ trợ truyền dữ liệu, DisplayPort 2.1, Power delivery 3.1, HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E MT7922 Bluetooth 5.3 | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ | Thông tin Pin:: 3-cell Li-Po, 59 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 218.5 mm - Dày 14.6 mm - 1.39 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-5-120u-dc4c5375w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-x-flip-14-fk0082au-r7-ai-350-bz7n8pa</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:21:58</t>
+          <t>2026-09-16 12:17:43</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - 71100515 (Core 7 150U, 16GB, 512GB, Full HD+ 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop HP OmniBook X Flip 14 kb0048TU - D72BYPA (Ultra 7 355, 32GB, 512GB, WUXGA, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>31990000</v>
+        <v>49190000</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>35490000</v>
+        <v>49890000</v>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 320 mm - Rộng 215.97 mm - Dày 18.02 mm - 1.83 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 95% DCI-P3 | Công nghệ màn hình:: 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x Headphone/ Microphone combo audio jack HDMI 2 x USB 3.2 gen 2 Type-A 2 x Thunderbolt 4 (hỗ trợ truyền dữ liệu,Power Delivery,DisplayPort,HP Sleep and Charge) | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Poly Studio DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ | Thông tin Pin:: 3-cell Li-Po, 59.16 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 218.5 mm - Dày 14.4 mm - 1.398 kg | Chất liệu:: Nhôm &amp; Nhựa</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-71100515</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-x-flip-14-kb0048tu-ultra-7-355-d72bypa</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:22:12</t>
+          <t>2026-09-16 12:17:57</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC14250-C7U161W11SLU-2Y (Core 7 150U, 16GB, 1TB, Full HD+ ,OfficeH24+365, Win11)</t>
+          <t>Laptop HP ProBook 4 G1a 14 - D9CP7AT (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>34990000</v>
+        <v>30590000</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>37990000</v>
+        <v>31990000</v>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 PCIe Gen 4 x 4 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (M.2 2230)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB Type-C (hỗ trợ cổng Thunderbolt 4) LAN (RJ45) 2 x USB 3.2 Gen 2 Type-C (hỗ trợ Power Delivery 3.0, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) | Webcam:: Camera HP FHD, tích hợp màn che và micro kép | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: fTPM 2.0 TPM Embedded Security Smart Cover Secure Platform Management (SPM) Secure Boot Configuration POST Power-On Password Microsoft Pluton Processor BIOS Sure Start AMD PSP 11.0 Device Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hard Drive Utilities | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 31.86 cm - Rộng 22.43 cm - Dày 1.70 cm - 1.465 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-dc14250-c7u161w11slu-2y</t>
+          <t>https://www.thegioididong.com/laptop/hp-probook-4-g1a-14-r7-250-d9cp7at</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:22:26</t>
+          <t>2026-09-16 12:18:10</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - 71100520 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop HP Probook 4 G1ah 16 - D9CP8AT (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>21490000</v>
+        <v>30590000</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>22590000</v>
+        <v>31990000</v>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort 1.4, Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Bluetooth 5.0 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (2280) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI 2 x USB 3.2 Gen 2 Type-C (hỗ trợ Power Delivery 3.0, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) | Webcam:: Camera HP FHD, tích hợp màn che và micro kép | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM Embedded Security Smart Cover Secure Platform Management (SPM) Secure Boot Configuration POST Power-On Password Microsoft Pluton Processor fTPM 2.0 BIOS Sure Start AMD PSP 11.0 Device Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hard Drive Utilities | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 35.94 cm - Rộng 25.1 cm - Dày 1.7 cm - 1.783 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-71100520</t>
+          <t>https://www.thegioididong.com/laptop/hp-probook-4-g1ah-16-r7-250-d9cp8at</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:22:39</t>
+          <t>2026-09-16 12:18:24</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - CPH993 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop HP ProBook 4 G2i 16 - DK2X9AT (Ultra 5 325, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>21490000</v>
+        <v>35190000</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>22590000</v>
+        <v>36590000</v>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: Đang cập nhật | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 70% Less harmful blue light 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 16.96 mm đến 18.99 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 325 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell, 68.03 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.4 mm - Rộng 251 mm - Dày 17.5 mm - 1.848 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-cph993</t>
+          <t>https://www.thegioididong.com/laptop/hp-probook-4-g2i-16-ultra-5-325-dk2x9at</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:22:53</t>
+          <t>2026-09-16 12:18:38</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC5C3259W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+          <t>Laptop HP ProBook 4 G2i 16 - DK2Y5AT (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>21490000</v>
+        <v>39190000</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>22590000</v>
+        <v>40590000</v>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell, 68.03 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.4 mm - Rộng 251 mm - Dày 17.5 mm - 1.846 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3259w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/hp-probook-4-g2i-16-ultra-7-355-dk2y5at</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:23:06</t>
+          <t>2026-09-16 12:18:52</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC5C3851W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo Gaming Legion 5 15AHP11 - 83Q7001HVN (R7 250, 16GB, 512GB, RTX 5050 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>21490000</v>
+        <v>52990000</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>22590000</v>
+        <v>56990000</v>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x Headphone/ Microphone combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 2 x USB 2.0 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 235 mm - Rộng 358.5 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Boost Clock 2662MHz, TGP 115W, 440 AI TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: 2.5K | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: DisplayHDR True Black 1000 | Cổng giao tiếp:: 1x Ethernet 2 x USB Type-C (USB4 40Gbps) hỗ trợ USB PD 65 - 100W và DisplayPort 1.4 1 x Headphone/ Microphone combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) 2×2 Bluetooth 6.0 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 244.5 mm - Rộng 344 mm - Dày 19~20 - 1.87 kg | Chất liệu:: Mặt trên: nhôm + Mặt dưới: nhựa PC-ABS</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3851w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15ahp11-r7-250-83q7001hvn</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:23:19</t>
+          <t>2026-09-16 12:19:05</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15255 - DC5R5973W1-2Y (R5 7530U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002NVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>23990000</v>
+        <v>22990000</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>25690000</v>
+        <v>29990000</v>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-23%</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 7530U | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/microphone combo 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r5-7530u-dc5r5973w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002nvn</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:23:32</t>
+          <t>2026-09-16 12:19:19</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15255 - X9YM42 (R7 7730U, 16GB, 1TB, Full HD 120Hz, OfficeH24+36, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002PVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>29890000</v>
+        <v>18990000</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>30590000</v>
+        <v>25990000</v>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-27%</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 8 x 2.0 GHz | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Bluetooth 5.0 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.635 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r7-7730u-x9ym42</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002pvn</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:23:46</t>
+          <t>2026-09-16 12:19:32</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 16 DC16250 - 71100513 (Core 5 120U, 16GB, 1TB, Full HD+, OfficeH24+365B, Win11)</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr"/>
-      <c r="C103" s="2" t="inlineStr"/>
-      <c r="D103" s="2" t="inlineStr"/>
-      <c r="E103" s="2" t="inlineStr"/>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00A8VN (Core 3 304, 8GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>17490000</v>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>23990000</v>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>-27%</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits eDP Wide View Angle | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2W x 2 Realtek ALC3254 Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 05/2025 | Kích thước:: Dài 357.3 mm - Rộng 250.6 mm - Dày 18.23 mm - 2 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core™ 3 - 304 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz (P-core), Turbo tối đa 4.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 2242 PCIe 4.0x4 NVMe | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 × USB-C (USB 5 Gbps), hỗ trợ USB PD 45–65W và DisplayPort 1.2 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Optimized with Dolby Audio 2W x 2 High Definition (HD) Audio Stereo speakers | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 240 mm - Rộng 343 mm - Dày 17 - 18 - 1.59 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-5-120u-71100513</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-3-304-83rr00a8vn</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -4859,169 +4859,169 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:23:59</t>
+          <t>2026-09-16 12:19:46</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell Pro 15 Essential PV15250 - PV15250-100U-8512W-2Y (Core 3 100U, 8GB, 512GB, Full HD, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00AAVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>22490000</v>
+        <v>22990000</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>23990000</v>
+        <v>29990000</v>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-23%</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Rộng 358.5 mm - Dày 17.5 mm | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-pro-15-essential-pv15250-core-3-100u-pv15250-100u-8512w-2y</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00aavn</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:24:13</t>
+          <t>2026-09-16 12:19:59</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 15 fd2183TU - DP2C0PA (Ultra 7 255U, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Lenovo Ideapad Slim 3 15IWC11 - 83RR00CVVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>31590000</v>
+        <v>19190000</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>32990000</v>
+        <v>25990000</v>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 255U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: Hãng không công bố | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB Type-C with Thunderbolt 5 (hỗ trợ USB 4, DisplayPort 2.1 và Power Delivery 3.0) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: HP True Vision 720p HD camera, tích hợp màn che và micro kép | Đèn bàn phím:: Không có đèn | Bảo mật:: fTPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hard Disk Utilities | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 35.98 cm - Rộng 23.6 cm - Dày 1.86 cm - 1.614 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-15-fd2183tu-ultra-7-255u-dp2c0pa</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00cvvn</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:24:25</t>
+          <t>2026-09-16 12:20:13</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP Gaming HyperX Omen 15 ga0092TX - D72D8PA (i5 14450HX, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US0040VN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>45590000</v>
+        <v>23690000</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>46990000</v>
+        <v>31990000</v>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 421 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.37 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 x USB-C (USB 5Gbps), with USB PD 45-65W and DisplayPort 1.2 1x Headphone / microphone combo jack (3.5 mm) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 18 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-gaming-hyperx-omen-15-ga0092tx-i5-14450hx-d72d8pa</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-5-322-83us0040vn</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:24:39</t>
+          <t>2026-09-16 12:20:26</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP HyperX Omen 15 ga0091TX - D72D7PA (i5 14450HX, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US003YVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>48590000</v>
+        <v>28990000</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>49990000</v>
+        <v>36990000</v>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3840 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 614 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.363 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-hyperx-omen-15-ga0091tx-i5-14450h-d72d7pa</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us003yvn</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5031,136 +5031,179 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:24:53</t>
+          <t>2026-09-16 12:20:40</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook 5 14 hh0072TU - D72CQPA (Ultra 7 355, 16GB, 512GB, WUXGA, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14IPH11 - 83S5004FVN (Ultra 7 355, 16GB, 512GB, WUXGA OLED, Win11)</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>39990000</v>
+        <v>34990000</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>40690000</v>
+        <v>37990000</v>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 2 x Thunderbolt 4 (hỗ trợ truyền dữ liệu,Power Delivery,DisplayPort,HP Sleep and Charge) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 59.16 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 217.5 mm - Dày 13.6 mm - 1.296 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-5-14-hh0072tu-ultra-7-355-d72cqpa</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14iph11-ultra-7-355-83s5004fvn</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:25:07</t>
+          <t>2026-09-16 12:20:53</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook 5 14 hh0073TU - D72CRPA (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo ThinkBook 14 G9 - 21V0005PVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>38990000</v>
+        <v>33390000</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>39690000</v>
+        <v>35290000</v>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 2 x Thunderbolt 4 (hỗ trợ truyền dữ liệu,Power Delivery,DisplayPort,HP Sleep and Charge) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 59.16 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 217.5 mm - Dày 13.6 mm - 1.296 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-5-14-hh0073tu-ultra-7-355-d72crpa</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-g9-r7-250-21v0005pvn</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:25:22</t>
+          <t>2026-09-16 12:21:06</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook 5 14 hh0074TU - D72CSPA (Ultra 5 322, 16GB, 512GB, WUXGA, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo ThinkBook 14 Gen 9 IRL - 21UY008TVN (i5 13420H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>36990000</v>
+        <v>28690000</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>37690000</v>
+        <v>32890000</v>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.90 GHz (Lên đến 4.40 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 1600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 2 x Thunderbolt 4 (hỗ trợ truyền dữ liệu,Power Delivery,DisplayPort,HP Sleep and Charge) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 59.16 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 217.5 mm - Dày 13.6 mm - 1.337 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-5-14-hh0074tu-ultra-5-322-d72cspa</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-gen-9-irl-i5-13420h-21uy008tvn</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 12:25:36</t>
+          <t>2026-09-16 12:21:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Laptop Lenovo ThinkBook 16 G9 - 21UT005MVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>30190000</v>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>31590000</v>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356 mm - Rộng 253.5 mm - Dày 17.5 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-16-g9-r7-250-21ut005mvn</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:21:34</t>
         </is>
       </c>
     </row>

--- a/laptop_tgdd_all.xlsx
+++ b/laptop_tgdd_all.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I111"/>
+  <dimension ref="A1:I112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -492,143 +492,143 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ893W (Core 3 304, 8GB, 512GB, Full HD, Win 11)</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-977M - NX.W26SV.001 (Ultra 9 185H, 16GB, 512GB, Full HD+, Win11)</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>17990000</v>
+        <v>29990000</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>22990000</v>
+        <v>31990000</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>-22%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Wildcat Lake - 304 | Số nhân:: 5 | Số luồng:: 5 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.30 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 15 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits Chứng nhận TÜV Rheinland | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.7 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 9 Meteor Lake - 185H | Số luồng:: 22 | Tốc độ CPU:: 2.30 GHz (Lên đến 5.10 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (1 khe onboard) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB Type-C (65W) 1 x USB Type-C LAN (RJ45) HDMI 2.1 USB Type-C | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Stereo speakers | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 10 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.6 mm - Rộng 227.7 mm - Dày 17.9 mm - 1.49 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-15-x1504ma-core-3-304-bq893w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-go-14-ai-ag14-i71m-977m-ultra-9-185h-nx-w26sv-001</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:47:42</t>
+          <t>2026-09-17 13:24:02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook S 16 S3607VA - RP155W (Core 5 210H, 16GB, 512GB, Full HD+ 144Hz, Win11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR - NX.X0PSV.002 (Ryzen 5 3500U, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>26990000</v>
+        <v>17990000</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>34990000</v>
+        <v>20990000</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>-23%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB onboard + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Hãng không công bố | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare LED Backlit | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (2 x 2) | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 259.6 mm - Dày 15.9 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 3500U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz | Card màn hình:: Card tích hợp - AMD Radeon Vega Mobile Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 2400 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: IPS LED-backlit TFT LCD Wide viewing angle 250 nits | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A HDMI 1 x SuperSpeed USB Type-C (hỗ trợ DisplayPort 1.4) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP FHD 1080p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: 2 loa 2 microphones | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Phím Copilot | Thông tin Pin:: 2-cell Li-ion, 45.6 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 210.2 mm - Rộng 322.6 mm - Dày 19.8 mm - 1.3 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-s-16-s3607va-core-5-210h-rp155w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-nx-x0psv-002</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:47:56</t>
+          <t>2026-09-17 13:24:16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook S14 S3407VA - LY256W (Core 7 240H, 16GB, 512GB, WUXGA OLED, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN - NX.DDASV.001 (Core 3 N350, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>26990000</v>
+        <v>16990000</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>29990000</v>
+        <v>18990000</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 17.9 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - N350 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 3.90 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB 3.2 HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.0 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.8 mm - Rộng 235.6 mm - Dày 19.7 mm - 1.53 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-s14-s3407va-core-7-240h-ly256w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-36p-30tn-core-3-n350-nx-ddasv-001</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:48:09</t>
+          <t>2026-09-17 13:24:30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Zenbook 14 UM3406GA - QD075W (R7 AI 445, 16GB, 512GB, WUXGA OLED, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 - NX.X0RSV.001 (Ryzen 5 3500U, 8GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>34590000</v>
+        <v>17990000</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>39990000</v>
+        <v>20990000</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -637,256 +637,256 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 445 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.0 GHz | NPU:: AMD XDNA | Card màn hình:: Card tích hợp | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 70% Less harmful blue light 400 nits 600 nits (Khi bật HDR) | Cổng giao tiếp:: 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 75 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.01 mm - Rộng 31.24 mm - Dày 1.49 mm - 1.2 kg | Chất liệu:: Nhôm nguyên khối</t>
+          <t>Công nghệ CPU:: AMD Ryzen 5 - 3500U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz | Card màn hình:: Card tích hợp - AMD Radeon Vega Mobile Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 2400 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: IPS Màn hình Wide View Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A HDMI 1 x SuperSpeed USB Type-C (hỗ trợ DisplayPort 1.4) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP FHD 1080p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: 2 loa 2 microphones | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Phím Copilot | Thông tin Pin:: 2-cell Li-ion, 45.6 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 229.3 mm - Rộng 357.4 mm - Dày 19.85 mm - 1.5 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-zenbook-14-um3406ga-r7-ai-445-qd075w</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-nx-x0rsv-001</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:48:22</t>
+          <t>2026-09-17 13:24:43</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC14250-C3U085W11SLU-2Y (Core 3 100U, 8GB, 512GB, Full HD+, OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-44P-R4UH - NX.DJVSV.002 (R7 7730U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>21490000</v>
+        <v>21990000</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>22590000</v>
+        <v>23990000</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB Type - C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 230.2 mm - Dày 18.6 mm - 1.49 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-3-100u-dc14250-c3u085w11slu-2y</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-44p-r4uh-r7-7730u-nx-djvsv-002</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:48:36</t>
+          <t>2026-09-17 13:24:57</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC4C5375W1-2Y (Core 5 120U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC - NX.DG3SV.002.16G (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>28990000</v>
+        <v>21990000</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>32090000</v>
+        <v>24990000</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz (Lên đến 5.00 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: Đang cập nhật | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 314 mm - Rộng 226 mm - Dày 18 mm - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 357.6 mm - Rộng 228.5 mm - Dày 18.7 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-5-120u-dc4c5375w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-53p-56ec-core-5-120u-nx-dg3sv-002-16g</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:48:50</t>
+          <t>2026-09-17 13:25:11</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - 71100515 (Core 7 150U, 16GB, 512GB, Full HD+ 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Aspire Lite 16 AL16-71P-582Q - NX.DRSSV.001 (Ultra 5 125H, 16GB, 512GB, Full HD+ 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>31990000</v>
+        <v>24990000</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>35490000</v>
+        <v>26990000</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 320 mm - Rộng 215.97 mm - Dày 18.02 mm - 1.83 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 125H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357 mm - Rộng 245.5 mm - Dày 18.9 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-71100515</t>
+          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-16-al16-71p-582q-ultra-5-125h-nx-drssv-001</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:49:04</t>
+          <t>2026-09-17 13:25:25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 14 DC14250 - DC14250-C7U161W11SLU-2Y (Core 7 150U, 16GB, 1TB, Full HD+ ,OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Gaming Aspire 7 A715-59G-59RD - NH.DXUSV.001 (Core 5 210H, 16GB, 512GB, RTX 3050 4GB, Fulll HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>34990000</v>
+        <v>26990000</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>37990000</v>
+        <v>31990000</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 - 150U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: E-core: 0.9 GHz - 3.3 GHz, P-core: 1.2 GHz - 4.7 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MT/s | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 PCIe Gen 4 x 4 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (M.2 2230)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Display with ComfortView Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell, 54 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 22.615 mm - Rộng 31.4 mm - Dày 1.669 ~ 1.807 - 1.69 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 4 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35W - 80W | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 4 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle 350 nits Acer ComfyView | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C (hỗ trợ DisplayPort 1.4) LAN (RJ45) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn LED - 15 chế độ màu | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 359.5 mm - Rộng 238 mm - Dày 22.7 mm - 1.99 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-14-dc14250-core-7-150u-dc14250-c7u161w11slu-2y</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-aspire-7-a715-59g-59rd-core-5-210h-nh-dxusv-001</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:49:18</t>
+          <t>2026-09-17 13:25:39</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - 71100520 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel AN16S-61-R9CN - NH.QXGSV.001 (Ryzen AI 7 350, 16GB, 512GB, RTX 5070 8GB, 2K+ 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>21490000</v>
+        <v>57990000</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>22590000</v>
+        <v>64990000</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 PCIe (có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort 1.4, Power Delivery) 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Bluetooth 5.0 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.9 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.0 GHz (Lên đến 5.2 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits 3ms | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: NVIDIA Optimus | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-71100520</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-an16s-61-r9cn-ryzen-ai-7-350-nh-qxgsv-001</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:49:32</t>
+          <t>2026-09-17 13:25:52</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - CPH993 (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-556L - NH.QZ9SV.006 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>21490000</v>
+        <v>38990000</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>22590000</v>
+        <v>40990000</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -895,531 +895,543 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: Đang cập nhật | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 70% Less harmful blue light 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.56 mm - Dày 16.96 mm đến 18.99 mm - 1.637 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 60W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 16:9 aspect ratio Ultra-slim design Mercury free, environment friendly Thời gian phản hồi: 3 ms LED-backlit TFT LCD Wide viewing angle 300 nits Acer ComfyView | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Ethernet (LAN) Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: 720p at 30 fps HD camera | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High SNR DAC 2.1 Vrms Hỗ trợ tai nghe đến 600 Ω Compatible with Cortana with Voice 2 microphones Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Tính năng khác:: NitroSense Key Copilot Key | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 239.89 mm - Rộng 362.3 mm - Dày 115.7/23.5 - 2.1 kg | Chất liệu:: Nhựa nguyên khối</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-cph993</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-556l-core-5-210h-nh-qz9sv-006</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:49:46</t>
+          <t>2026-09-17 13:26:06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC5C3259W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-73Z8 - NH.QUASV.001 (Core 7 240H, 16GB, 512GB, RTX 4050 6GB, Full HD  180Hz, Win11)</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>21490000</v>
+        <v>35990000</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>22590000</v>
+        <v>39990000</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB-A (hỗ trợ USB 2.0) 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: IPS | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1x Ethernet 3 x USB 3.2 Gen 1 Type-A 1 x USB Type-C (65W) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: 720p at 30 fps HD camera Camera with Dual Microphone | Đèn bàn phím:: Đơn sắc - Màu cam | Công nghệ âm thanh:: Windows Spatial Sound High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3259w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-73z8-core-7-240h-nh-quasv-001</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:49:59</t>
+          <t>2026-09-17 13:26:20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - DC5C3851W1-2Y (Core 3 100U, 8GB, 512GB, Full HD 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV15-52-78MD - NH.QZ9SV.007 (Core 7 240H, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>21490000</v>
+        <v>40990000</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>22590000</v>
+        <v>43990000</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x Headphone/ Microphone combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 2 x USB 2.0 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 235 mm - Rộng 358.5 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms 300 nits Acer ComfyView | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2 microphones Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Nhựa nguyên khối</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15250-core-3-100u-dc5c3851w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv15-52-78md-core-7-240h-nh-qz9sv-007</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:50:13</t>
+          <t>2026-09-17 13:26:34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15255 - DC5R5973W1-2Y (R5 7530U, 16GB, 512GB, Full HD 120Hz, OfficeHS24+365, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-61-R0B8 - NH.QXQSV.001 (Ryzen AI 5 340, 16GB, 512GB, RTX 5050 8GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>23990000</v>
+        <v>42990000</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>25690000</v>
+        <v>47990000</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 7530U | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/microphone combo 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 358.5 mm - Rộng 235 mm - Dày 17.5 mm - 1.65 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.40 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r5-7530u-dc5r5973w1-2y</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-61-r0b8-ryzen-ai-5-340-nh-qxqsv-001</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:50:26</t>
+          <t>2026-09-17 13:26:47</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15255 - X9YM42 (R7 7730U, 16GB, 1TB, Full HD 120Hz, OfficeH24+36, Win11)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel ANV16S-71-58WQ - NH.QXBSV.001 (Core 5 210H, 16GB, 512GB, RTX 5050 8GB, 2K+ 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>29890000</v>
+        <v>44990000</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>30590000</v>
+        <v>46990000</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 8 x 2.0 GHz | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: WVA | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB 3.2 Gen 1 Type-C | Kết nối không dây:: Bluetooth 5.0 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 358.5 mm - Rộng 235.5 mm - Dày 18.9 mm - 1.635 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-15-dc15255-r7-7730u-x9ym42</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-anv16s-71-58wq-core-5-210h-nh-qxbsv-001</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:50:39</t>
+          <t>2026-09-17 13:27:02</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 16 DC16250 - 71100513 (Core 5 120U, 16GB, 1TB, Full HD+, OfficeH24+365B, Win11)</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
+          <t>Laptop Acer Gaming Predator Helios Neo 16S PHN16S-I51-97T9 - NH.U3SSV.006 (Ultra 9 386H, 16GB, 512GB, RTX 5070 8GB, 2K+ 165Hz, Win11)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>75990000</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>77990000</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.40 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits eDP Wide View Angle | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) 1 x Headphone/microphone combo HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2W x 2 Realtek ALC3254 Realtek ALC3204 | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 41 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 05/2025 | Kích thước:: Dài 357.3 mm - Rộng 250.6 mm - Dày 18.23 mm - 2 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 9 Panther Lake - 386H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 50 W - 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) OLED | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: LED-backlit TFT LCD 500 nits Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 92 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 18.9 mm - 2.2 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-16-dc16250-core-5-120u-71100513</t>
+          <t>https://www.thegioididong.com/laptop/acer-gaming-predator-helios-neo-16s-phn16s-i51-97t9-ultra-9-386h</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:50:53</t>
+          <t>2026-09-17 13:27:16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell Pro 15 Essential PV15250 - PV15250-100U-8512W-2Y (Core 3 100U, 8GB, 512GB, Full HD, OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Nitro ProPanel AN16S-61-R7ZJ - NH.QXFSV.002 (R7 AI 350, 16GB, 512GB, RTX 5060 8GB, 2K, Win11)</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>22490000</v>
+        <v>49990000</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>23990000</v>
+        <v>51990000</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Raptor Lake - 100U | Số luồng:: 8 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.70 GHz khi tải nặng) | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 4400 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: WVA | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD RGB | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Realtek ALC3254 | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3 cell, 41 Wh | Hệ điều hành:: Windows 11 Home + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2025 | Kích thước:: Rộng 358.5 mm - Dày 17.5 mm | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Nhôm &amp; Nhựa</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/dell-pro-15-essential-pv15250-core-3-100u-pv15250-100u-8512w-2y</t>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-an16s-61-r7zj-r7-ai-350-nhqxfsv002</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:51:07</t>
+          <t>2026-09-17 13:27:30</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 15 fd2183TU - DP2C0PA (Ultra 7 255U, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Acer Nitro ProPanel ANV15-52-50RB - NH.QUASV.002 (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>31590000</v>
+        <v>33490000</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>32990000</v>
+        <v>37990000</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 255U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: Hãng không công bố | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB Type-C with Thunderbolt 5 (hỗ trợ USB 4, DisplayPort 2.1 và Power Delivery 3.0) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: HP True Vision 720p HD camera, tích hợp màn che và micro kép | Đèn bàn phím:: Không có đèn | Bảo mật:: fTPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hard Disk Utilities | Thông tin Pin:: 3-cell Li-Po, 41.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 35.98 cm - Rộng 23.6 cm - Dày 1.86 cm - 1.614 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 60W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 300 nits Acer ComfyView 3ms | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: 2 microphones Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Tính năng khác:: Copilot Key | Thông tin Pin:: 4-cell Li-ion, 57 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 362.3 mm - Rộng 239.89 mm - Dày 23.5 mm - 2.1 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-15-fd2183tu-ultra-7-255u-dp2c0pa</t>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv15-52-50rb-core-5-210h-nh-quasv-002</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:51:20</t>
+          <t>2026-09-17 13:27:44</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP Gaming HyperX Omen 15 ga0092TX - D72D8PA (i5 14450HX, 16GB, 512GB, RTX 5050 8GB, WUXGA 165Hz, Win11)</t>
+          <t>Laptop Acer Nitro ProPanel ANV16-72-782F - NH.QUPSV.001 (Core 7 240H, 16GB, 512GB, RTX 5050 8GB, Full HD+ 180 Hz, Win11)</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45590000</v>
+        <v>43990000</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46990000</v>
+        <v>45990000</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 421 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.37 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 1.80 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 80 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 4 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Thời gian phản hồi: 3 ms Acer ComfyView 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ ThunderBolt 4 và DisplayPort) 3 x USB 3.2 LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Đèn nền - Màu hổ phách | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 360 mm - Rộng 274.5 mm - Dày 24.5 mm - 2.4 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-gaming-hyperx-omen-15-ga0092tx-i5-14450hx-d72d8pa</t>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv16-72-782f-core-7-240h-nhqupsv001</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:51:33</t>
+          <t>2026-09-17 13:27:58</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP HyperX Omen 15 ga0091TX - D72D7PA (i5 14450HX, 16GB, 512GB, RTX 5060 8GB, WUXGA 165Hz, Win11)</t>
+          <t>Laptop Acer Nitro ProPanel ANV16S-61-R7KQ - NH.QXPSV.001 (R5 AI 340, 16GB, 512GB, RTX 5060 8GB, Full HD 180Hz, Win11)</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>48590000</v>
+        <v>46990000</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>49990000</v>
+        <v>48990000</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 14450HX | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3840 CUDA Cores | Công suất đồ hoạ - TGP:: 75 W - 100 W | Hiệu năng xử lý AI (TOPS):: Lên đến 614 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 1 TB (2280)) 512 GB SSD PCIe M.2 (2280) (Có thể tháo rời, lắp thanh khác tối đa 1 TB (2280)) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 165 Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power delivery, HP Sleep and Charge) HDMI 2 x USB 3.2 gen 2 Type-A LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: OMEN Tempest Cooling | Thông tin Pin:: 4-cell Li-Po, 70.07 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 343 mm - Rộng 253 mm - Dày 23.6 mm - 2.363 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 5 - 340 | Số luồng:: 12 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 400 nits | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB Type C 3.2 Gen 2 (Hỗ trợ Power Delivery và DisplayPort™ 2.1) LAN (RJ45) HDMI 2.1 3 x USB A | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD 1080p Camera IR | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Công nghệ âm thanh:: Hi-Res certification Spatial Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357.7 mm - Rộng 264 mm - Dày 19.95 mm - 2.1 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-hyperx-omen-15-ga0091tx-i5-14450h-d72d7pa</t>
+          <t>https://www.thegioididong.com/laptop/acer-nitro-propanel-anv16s-61-r7kq-r5-ai-340-nhqxpsv001</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:51:47</t>
+          <t>2026-09-17 13:28:13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook 5 14 hh0072TU - D72CQPA (Ultra 7 355, 16GB, 512GB, WUXGA, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Swift Air 14 SFA14-I31-34NF - NX.W49SV.001 (Core 3 304, 12GB, 512GB, WUXGA 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>39990000</v>
+        <v>21990000</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>40690000</v>
+        <v>23990000</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 2 x Thunderbolt 4 (hỗ trợ truyền dữ liệu,Power Delivery,DisplayPort,HP Sleep and Charge) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 59.16 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 217.5 mm - Dày 13.6 mm - 1.296 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - 304 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 12 GB | Loại RAM:: LPDDR5 (1 khe onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Wide viewing angle 350 nits LED Backlight Acer ComfyView | Cổng giao tiếp:: 1 x USB 3.2 2 x USB Type-C (hỗ trợ USB, Power Delivery, DisplayPort và Thunderbolt 4) | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.3 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.99 mm - Rộng 222.65 mm - Dày 12.99 mm - 1.19 kg | Chất liệu:: Khung và mặt lưng kim loại</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-5-14-hh0072tu-ultra-7-355-d72cqpa</t>
+          <t>https://www.thegioididong.com/laptop/acer-swift-air-14-sfa14-i31-34nf-core-3-304-nx-w49sv-001</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:52:02</t>
+          <t>2026-09-17 13:28:27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook 5 14 hh0073TU - D72CRPA (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Swift Air 14 SFA14-I31-52BV - NX.W49SV.002 (Core 5 320, 12GB, 512GB, Full HD 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>38990000</v>
+        <v>24990000</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>39690000</v>
+        <v>26990000</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 2 x Thunderbolt 4 (hỗ trợ truyền dữ liệu,Power Delivery,DisplayPort,HP Sleep and Charge) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 59.16 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 217.5 mm - Dày 13.6 mm - 1.296 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Đang cập nhật | RAM:: 12 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 350 nits | Cổng giao tiếp:: 1 x USB 3.2 2 x USB Type-C (hỗ trợ USB, Power Delivery, DisplayPort và Thunderbolt 4) | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.3 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Hi-Res Audio High SNR DAC with 2.1 Vrms out capability Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 222.65 mm - Rộng 222.65 mm - Dày 12.99 mm - 1.19 kg | Chất liệu:: Khung và mặt lưng kim loại</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-5-14-hh0073tu-ultra-7-355-d72crpa</t>
+          <t>https://www.thegioididong.com/laptop/acer-swift-air-14-sfa14-i31-52bv-core-5-320-nx-w49sv-002</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:52:15</t>
+          <t>2026-09-17 13:28:40</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP OmniBook 5 14 hh0074TU - D72CSPA (Ultra 5 322, 16GB, 512GB, WUXGA, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Acer Swift Go AI SFG14-75-5264 - NX.JNBSV.001 (Ultra 5 226V, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>36990000</v>
+        <v>29990000</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>37690000</v>
+        <v>31990000</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.90 GHz (Lên đến 4.40 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 1600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 1 x Headphone/ Microphone combo audio jack HDMI 2 x Thunderbolt 4 (hỗ trợ truyền dữ liệu,Power Delivery,DisplayPort,HP Sleep and Charge) | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek High Definition Audio DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Po, 59.16 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 217.5 mm - Dày 13.6 mm - 1.337 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Lunar Lake - 226V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 3.50 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 40 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 130V | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD | Tấm nền:: OLED | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe ACER CineCrystal 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB 3.2 2 x USB4 Type-C (hỗ trợ truyền dữ liệu, DisplayPort, Power Delivery) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: 2 quạt | Thông tin Pin:: 4-cell, 65Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 227.4 mm - Rộng 312.4 mm - Dày 15.95 mm - 1.24 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/hp-omnibook-5-14-hh0074tu-ultra-5-322-d72cspa</t>
+          <t>https://www.thegioididong.com/laptop/acer-swift-go-ai-sfg14-75-5264-ultra-5-226v-nxjnbsv001</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:52:29</t>
+          <t>2026-09-17 13:28:55</t>
         </is>
       </c>
     </row>
@@ -1462,1096 +1474,1096 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:53:20</t>
+          <t>2026-09-17 13:29:08</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP - U716S8W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Lenovo ThinkPad X9 14 Gen 1 - 21QA006JVN (Ultra 7 258V, 32GB, 512GB, WUXGA OLED, Win11Pro)</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>32990000</v>
+        <v>53790000</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>34990000</v>
+        <v>55190000</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 430 mm - Rộng 316 mm - Dày 19.9 mm - 2.61 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.80 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Chống chói Anti Glare Dolby Vision 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm HDMI 2.1 2 x USB-C (hỗ trợ Thunderbolt 4/USB 4, USB Power Delivery và DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.8 mm - Rộng 212.3 mm - Dày 17.18 mm - 1.21 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-p3-p3406ccap-ultra-7-255h-u716s8w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-x9-14-gen-1-ultra-7-258v-21qa006jvn</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:53:35</t>
+          <t>2026-09-17 15:36:22</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA - NZ1368W (Ultra 5 226V, 16GB, 512GB, WQXGA 144Hz, Win11)</t>
+          <t>Laptop Lenovo V14 G5 - 83HD0035VN (Core7 240H, 16G, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>30090000</v>
+        <v>31290000</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>31990000</v>
+        <v>32690000</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Lunar Lake - 226V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 40 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 130V | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Anti-Glare Màn hình Wide View 400 nits | Cổng giao tiếp:: 2 x Thunderbolt 4 1 x 3.5mm combo audio jack HDMI 2 x USB 3.2 gen 2 Type-A | Kết nối không dây:: Hãng không công bố | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in array microphone Dolby Atmos | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 223 mm - Dày 12.8 ~ 16.4 mm - 1.2 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) LAN (RJ45) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Ion, 47 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324.2 mm - Rộng 215.2 mm - Dày 17.9 mm - 1.37 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-p5-p5405csa-ultra-5-226v-nz1368w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-v14-g5-core7-240h-83hd0035vn</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:53:49</t>
+          <t>2026-09-17 15:36:37</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA - NZ1371W (Ultra 7 258V, 32GB, 512GB, WQXGA 144Hz, Win11)</t>
+          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002LVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>37490000</v>
+        <v>38490000</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>39490000</v>
+        <v>44990000</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Intel Arc 140V | Số nhân GPU:: Hãng không công bố | RAM:: 32 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Anti-Glare Màn hình Wide View 400 nits | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 Type-A 1 x Thunderbolt 4 (hỗ trợ DisplayPort) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Smart Amp Technology Built-in array microphone Dolby Atmos | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 223 mm - Dày 12.8 ~ 16.4 mm - 1.2 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-p5-p5405csa-ultra-7-258v-nz1371w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-5-322-83tc002lvn</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:54:03</t>
+          <t>2026-09-17 15:36:50</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook Ultra B9 B9406CAA - X7642TW (Ultra X7 358H, 64GB, 2TB, WQXGA+ OLED 120Hz, Win11)</t>
+          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002MVN (Ultra 7 355, 32GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>97990000</v>
+        <v>55990000</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>100000000</v>
+        <v>64990000</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra X7 Panther Lake | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 2 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 1 x USB Type-C (hỗ trợ cổng Thunderbolt 4) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Có | Công nghệ âm thanh:: Built-in speaker Built-in array microphone Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 28.8 mm - Rộng 12.7 mm - Dày 38.9 mm - 1.131 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.95 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-b9-b9406caa-ultra-x7-358h-x7642tw</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-7-355-83tc002mvn</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:54:17</t>
+          <t>2026-09-17 15:37:04</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook Ultra B9 B9406CAA - X7321TW (Ultra X7 358H, 32GB, 1TB, WQXGA+ OLED 120Hz, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 - 83QM0075VN (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>65990000</v>
+        <v>40990000</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>68000000</v>
+        <v>46990000</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra X7 Panther Lake - 358H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare 600 nits Pantone Validated | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x Thunderbolt 4 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Built-in speaker Built-in array microphone Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.9 mm - Dày 16.4 mm - 1.1 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe 600nits (peak) Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 70 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 04/2026 | Kích thước:: Dài 221 mm - Rộng 312 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-b9-b9406caa-x7321tw-ultra-x7-358h-32gb-1tb-wqxga-oled-120hz-win11</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-14iph11-ultra-7-355-83qm0075vn</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:54:31</t>
+          <t>2026-09-17 15:37:19</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0045W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 - 83QM0076VN (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>30990000</v>
+        <v>40990000</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>33990000</v>
+        <v>46990000</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 1 x USB Type-C with Thunderbolt 5 (hỗ trợ USB 4, DisplayPort 2.1 và Power Delivery 3.0) | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.00 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Khoảng 13 TOPS (NPU); tổng nền tảng AI của Intel đạt khoảng 99 TOPS (CPU + GPU + NPU) | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: 4 Xe-Cores | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7467 MT/s | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB PCIe 4.0 NVMe SSD | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: OLED Chuẩn DisplayHDR True Black 600 Low Blue Light Eyesafe Dolby Vision | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 2 x Thunderbolt 4 USB-C HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Chốt khóa webcam FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hệ thống quạt kép (Dual Fan) | Tính năng khác:: TPM 2.0 | Thông tin Pin:: 70 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 221 mm - Rộng 312 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Vỏ hợp kim Nhôm</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-5-225h-sf0045w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-14iph11-ultra-7-355-83qm0076vn</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:54:44</t>
+          <t>2026-09-17 15:37:33</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0241W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK0015VN (Ultra 7 355, 32GB, 1TB, WQXGA+ 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>35990000</v>
+        <v>62990000</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>37990000</v>
+        <v>72990000</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display Màn hình Wide View | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe 4.0x4 NVMe (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: 500 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.6 mm - Rộng 213.8 mm - Dày 13.9 mm - 0.975 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-7-255-sf0241w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-7-355-83qk0015vn</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:54:57</t>
+          <t>2026-09-17 15:37:48</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0047W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK006GVN (Ultra 7 355, 32GB, 1TB, WQXGA+ 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>35990000</v>
+        <v>64990000</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>37990000</v>
+        <v>66990000</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display Màn hình Wide View | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe 4.0x4 NVMe (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Eyesafe DisplayHDR True Black 1000 500 nits Corning Gorilla Glass 3 Dolby Vision PureSight Pro Flicker Free 1100 nits (peak) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.6 mm - Rộng 213.8 mm - Dày 13.9 mm - 0.975 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-7-255h-sf0047w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-7-355-83qk006gvn</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:55:11</t>
+          <t>2026-09-17 15:38:03</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming ROG Strix G16 G614PM - TS147W (R9 8940HX, 16GB, 512GB, RTX 5060 8GB, WQXGA 300Hz, Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK009PVN (Ultra X9 378H, 32GB, 1TB, WQXGA+ 120Hz, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>54990000</v>
+        <v>68990000</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>57990000</v>
+        <v>79990000</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115W - 140W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.288 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra X9 - 378H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.00 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 32 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 9600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe® 4.0x4 NVMe® (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Eyesafe 500 nits typical DisplayHDR True Black 1000 Corning Gorilla Glass 3 500 nits Glossy Dolby Vision PureSight Pro Flicker Free 1100 nits (peak) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 18/05/2026 | Kích thước:: Dài 213.8 mm - Rộng 312.6 mm - Dày 13.9 mm - 0.975 kg</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pm-r9-8940hx-ts147w</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-x9-378h-83qk009pvn</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:55:25</t>
+          <t>2026-09-17 15:38:17</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming ROG Strix G16 G614PR - TS103W (R9 8940HX, 16GB, 512GB, RTX 5070Ti 12GB, WQXGA 300Hz, Win11)</t>
+          <t>Laptop MSI Cyborg 15 Black Edition A13VEO - 2610VN (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>70590000</v>
+        <v>28590000</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>71990000</v>
+        <v>31990000</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070Ti, 12 GB | Số nhân GPU:: 5888 CUDA Cores | Công suất đồ hoạ - TGP:: 140 W | Hiệu năng xử lý AI (TOPS):: Lên đến 992 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.34 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell, 53.5Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 250.3 mm - Dày 22.9 mm - 1,.98 | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pr-r9-8940hx-ts103w</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-black-edition-a13veo-i5-13420h-2610vn</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:55:38</t>
+          <t>2026-09-17 15:38:32</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming V16 V3607VJ Core 5 - TK189W (Core 5 210H, 16GB, 512GB, RTX 3050 6GB, WUXGA 144Hz, Win11)</t>
+          <t>Laptop MSI Cyborg 15 Black Edition A13VEO - 2608VN (i7 13620H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>25990000</v>
+        <v>30590000</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>36990000</v>
+        <v>33990000</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 6 GB | Công suất đồ hoạ - TGP:: 65 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% Adobe | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x 3.5mm combo audio jack HDMI 2.1 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: 1080p with Privacy Shutter | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in microphone | Tản nhiệt:: 2 quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 63 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 251 mm - Dày 22 mm - 1.95 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 1.8 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell, 53.5Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 250.3 mm - Dày 22.9 mm - 1,.98 | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-v16-v3607vj-core-5-core-5-210h-tk189w</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-black-edition-a13veo-i7-13620h-2608vn</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:55:52</t>
+          <t>2026-09-17 15:38:45</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Gaming V16 V3607VU - TK416W (Core 5 210H, 16GB, 512GB, RTX 4050 6GB, WUXGA 144Hz, Win11)</t>
+          <t>Laptop MSI Cyborg 15 C13WEO - 418VN (i5 13420H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>32990000</v>
+        <v>31590000</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>41990000</v>
+        <v>34990000</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 65 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 2 khe (1 khe 16 GB + 1 khe trống) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x 3.5mm combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (2 x 2) Bluetooth 5.3 | Webcam:: 1080p FHD camera | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: Mô-đun bảo mật TPM (Firmware TPM) Mật khẩu thiết lập BIOS | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in microphone | Tản nhiệt:: 2 quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 63 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357 mm - Rộng 250.7 mm - Dày 18 mm - 1.95 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 70 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 1.982 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-gaming-v16-v3607vu-core-5-210h-tk416w</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-c13weo-i5-13420h-418vn</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:56:06</t>
+          <t>2026-09-17 15:38:59</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ProArt P1 H7606WP - SR335W (R9 AI HX 370, 64GB, 2TB, RTX 5070 8GB, 3K 120Hz, Cảm ứng, Win11)</t>
+          <t>Laptop MSI Cyborg 15 Max C13WE - 422VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>114890000</v>
+        <v>41590000</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>124990000</v>
+        <v>42990000</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 9 - Hãng không công bố | Số nhân:: 12 | Số luồng:: 24 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 2 TB SSD M.2 NVMe PCIe Gen 4 | Kích thước màn hình:: 16" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 500 nits (Khi bật HDR) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB 3.2 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C HDMI 2.1 1 x USB 4.0 Gen 3 Type-C (Hỗ trợ DisplayPort và Power Delivery) | Kết nối không dây:: Hãng không công bố | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD (hỗ trợ Windows Hello) | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Smart Amp Technology Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354.9 mm - Rộng 246.9 mm - Dày 17.3 mm - 1.85 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x SuperSpeed USB Type-A LAN (RJ45) HDMI 2.1 2 x USB 3.2 1 x USB Type-C 3.2 (hỗ trợ Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: 3 ống đồng Cooler Boost 2 quạt | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 2 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-proart-p1-h7606wp-r9-ai-hx-370-sr335w</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-max-c13we-422vn-i7-13620h</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:56:19</t>
+          <t>2026-09-17 15:39:13</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus TUF Gaming A15 FA506NCG - HN390W (R7 155, 16GB, 512GB, RTX 3050 4GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop MSI Cyborg 15 Max C13WF - 421VN (i7 13620H, 16GB, 512GB, RTX 5060 8GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>27490000</v>
+        <v>43590000</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>37490000</v>
+        <v>44990000</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-27%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 155 | Số nhân:: 6 | Số luồng:: 12 | Tốc độ CPU:: 3.0 GHz (Lên đến 4.70 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 4 GB | RAM:: 16 GB | Loại RAM:: DDR5 2 khe (1 khe 16 GB + 1 khe trống) | Tốc độ Bus RAM:: 4800 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 62.5% sRGB 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: Jack tai nghe 3.5 mm 3 x USB 3.2 Gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: HD webcam | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Built-in array microphone | Tản nhiệt:: 2 quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 256 mm - Dày 24.5 mm - 2.30 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x SuperSpeed USB Type-A LAN (RJ45) HDMI 2.1 2 x USB 3.2 1 x USB Type-C 3.2 (hỗ trợ Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: 3 ống đồng Cooler Boost 2 quạt | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 2 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-tuf-gaming-a15-fa506ncg-r7-155-hn390w</t>
+          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-max-c13wf-421vn-i7-13620h</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:56:33</t>
+          <t>2026-09-17 15:39:27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1404MA - EB028W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop MSI Gaming Cyborg 15 C13WEO-417VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>23990000</v>
+        <v>34590000</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>31990000</v>
+        <v>36990000</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe RAM) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Hãng không công bố | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 21.39 mm - Rộng 32.49 mm - Dày 1.79 mm - 1.4 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - Intel UHD Graphics (tích hợp) + NVIDIA GeForce RTX 5050 GPU, 8GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB Type-A 1 x Headphone/ Microphone combo audio jack 1 x USB Type C (chỉ hỗ trợ Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: DTS Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.98 kg | Chất liệu:: Vỏ nhựa</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1404ma-core-5-320-eb028w</t>
+          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-c13weo-417vn-i7-13620h</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:56:46</t>
+          <t>2026-09-17 15:39:41</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1407CA - LY203W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop MSI Modern 14S G3MG-003VN (Core 5 320, 16GB, 1TB, Full HD+ 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>24090000</v>
+        <v>27990000</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>33490000</v>
+        <v>31490000</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>-28%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort, Power Delivery) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 315.2 mm - Rộng 223.4 mm - Dày 19.9 mm - 1.46 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: SSD 1TB, chuẩn M.2 2280 NVMe PCIe Gen4, tối đa hỗ trợ 2TB | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 50% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 2 x USB 3.2 gen 1 Type-A LAN (RJ45) HDMI 2.1 2 x USB Type-C 3.2 Gen 2 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD card reader | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: DTS | Tản nhiệt:: 2 ống đồng 1 x Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.39 mm - Rộng 31.59 mm - Dày 1.11 ~ 1.79 - 1.45 kg | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-14-x1407ca-ultra-5-225h-ly203w</t>
+          <t>https://www.thegioididong.com/laptop/msi-modern-14s-g3mg-003vn-core-5-320</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:56:58</t>
+          <t>2026-09-17 15:39:55</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ385W (Core 5 320, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop MSI Modern 15 F1MG-1264VN (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>23990000</v>
+        <v>19190000</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>31990000</v>
+        <v>22390000</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core thế hệ 12 - 120U | Số nhân:: Hãng không công bố | Số luồng:: 12 | Tốc độ CPU:: 1.45 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (2280) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: Hãng không công bố | Cổng giao tiếp:: 3 x USB 3.2 Gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell, 46.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.7 kg | Chất liệu:: Plastic (nhựa dẻo)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-5-320-bq385w</t>
+          <t>https://www.thegioididong.com/laptop/msi-modern-15-f1mg-1264vn-core-5-120u</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:57:11</t>
+          <t>2026-09-17 15:40:09</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 15 X1504MA - BQ395W (Core 7 350, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop SingPC M16-i382 (i3 1215U, 8GB, 256GB, WUXGA, Win11 Pro)</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>27990000</v>
+        <v>13490000</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>35490000</v>
+        <v>15190000</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Wildcat Lake - 350 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 17 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (mỗi khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.7 mm - Rộng 232.5 mm - Dày 17.9 mm - 1.52 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i3 Alder Lake - 1215U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.2GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 256 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-15-x1504ma-core-7-350-bq395w</t>
+          <t>https://www.thegioididong.com/laptop/singpc-m16-i382-i3-1215u</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:57:24</t>
+          <t>2026-09-17 15:40:22</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 16 X1607CA - MB387W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop SingPC M16-i595 (i5 1235U, 16GB, 512GB, WUXGA, Win11 Pro)</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>24590000</v>
+        <v>17390000</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>33490000</v>
+        <v>19990000</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>-27%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 SO-DIMM | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 2 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: SonicMaster Built-in speaker Built-in array microphone | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 25.06 mm - Rộng 35.7 mm - Dày 1.79 ~ 1.99 - 1.88 kg | Chất liệu:: Khung nhôm - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Alder Lake - 1235U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 72% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-16-x1607ca-ultra-5-225h-mb387w</t>
+          <t>https://www.thegioididong.com/laptop/singpc-m16-i595-i5-1235u</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:57:39</t>
+          <t>2026-09-17 15:40:35</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook Go 14 E1404FA - EB012W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop HP OmniBook Ultra 14 kd0036TU - D72C6PA (Ultra 9 386H, 32GB, 1TB, 3K OLED 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>18790000</v>
+        <v>65190000</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>22990000</v>
+        <v>65890000</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 9 Panther Lake - 386H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: up to 120 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light 500 nits Corning Gorilla Glass 3 | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery 3.1, DisplayPort 2.1) 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.1 mm - Rộng 215.6 mm - Dày 10.7 mm - 1.282 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb012w</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-ultra-14-kd0036tu-ultra-9-386h-d72c6pa</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:57:52</t>
+          <t>2026-09-17 12:57:46</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook Go 14 E1404FA - EB1832W (R5 40, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop HP OmniBook Ultra 14 kd0039TU - D72C7PA (Ultra 7 356H, 32GB, 1TB, 3K OLED 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>18790000</v>
+        <v>59190000</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>22990000</v>
+        <v>59890000</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 40 | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.80 GHz (Lên đến 4.30 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5500 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 3.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare LED Backlit 250 nits | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: SonicMaster | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 325.5 mm - Rộng 213.9 mm - Dày 17.9 mm - 1.38 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 356H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz (Lên đến 4.7 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: 3K (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: up to 120 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: 500 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery 3.1, DisplayPort 2.1) 1 x Headphone/ Microphone combo audio jack | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.1 mm - Rộng 215.6 mm - Dày 10.7 mm - 1.288 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/asus-vivobook-go-14-e1404fa-r5-40-eb1832w</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-ultra-14-kd0039tu-ultra-7-356h-d72c7pa</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 12:58:05</t>
+          <t>2026-09-17 12:58:01</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad E14 - 21T90025VN (Gen 7 Core 7 240H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop HP OmniBook X Flip 14 fk0082AU - BZ7N8PA (R7 AI 350, 32GB, 1TB, 2K, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>34190000</v>
+        <v>39890000</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>35590000</v>
+        <v>40890000</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng bộ 4 ứng dụng AI trị giá đến 6 triệu đồng (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: P-core 2.5/ 5.2 GHz, E-core 1.8/ 4.0 GHz | Card màn hình:: Card tích hợp - Integrated Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare 300 nits | Cổng giao tiếp:: 1x USB-A (USB 10Gbps / USB 3.2 Gen 2), Always On 1x Headphone / microphone combo jack (3.5 mm) 1x USB-C® (Thunderbolt™ 4 / USB4® 40 Gbps), with USB PD 15-65W and DisplayPort™ 2.1 1x HDMI® 2.1, up to 4K/6 0Hz 1x Ethernet (RJ-45) 1x USB-A (USB 5 Gbps / USB 3.2 Gen 1) | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: FHD 1080p + IR Hybrid with Privacy Shutter | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Stereo speakers, 2W x2, Dolby Atmos®, audio by HARMAN 2x, Array | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ Discrete TPM 2.0 Enabled | Thông tin Pin:: 3-cell, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 04/2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 10.1/15.25 (front/rear), 19.7 (maximum) mm - 1.34 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.00 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 860M Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7500 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: 2K (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: Micro-edge Corning Gorilla Glass 3 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x USB Type-C (hỗ trợ truyền dữ liệu, DisplayPort 2.1, Power delivery 3.1, HP Sleep and Charge) Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E MT7922 Bluetooth 5.3 | Webcam:: Camera IR 5 MP | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: HP Audio Boost DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ | Thông tin Pin:: 3-cell Li-Po, 59 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 218.5 mm - Dày 14.6 mm - 1.39 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-core-7-240h-21t90025vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-x-flip-14-fk0082au-r7-ai-350-bz7n8pa</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:38:50</t>
+          <t>2026-09-17 12:58:14</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad E14 - 21SX002YVN (Gen 7 Ultra 255H, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop HP OmniBook X Flip 14 kb0048TU - D72BYPA (Ultra 7 355, 32GB, 512GB, WUXGA, Cảm ứng, OfficeH24+365, Win11)</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>39190000</v>
+        <v>49190000</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>40590000</v>
+        <v>49890000</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.10 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140T | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 1x USB-A (USB 10Gbps / USB 3.2 Gen 2), Always On 1x HDMI® 2.1, up to 4K/60 Hz 1x Headphone / microphone combo jack (3.5 mm) 1x USB-C® (Thunderbolt™ 4 / USB4® 40 Gbps), with USB PD 15-65W and DisplayPort™ 2.1 1x Ethernet (RJ-45) 1x USB-A (USB 5 Gbps / USB 3.2 Gen 1) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD 1080p + IR Hybrid with Privacy Shutter | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Stereo speakers, 2W x2, Dolby Atmos®, audio by HARMAN 2x, Array | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 04/2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 10.1/15.25 (front/rear), 19.7 (maximum) mm - 1.34 kg | Chất liệu:: Vỏ kim loại - Nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 95% DCI-P3 | Công nghệ màn hình:: 300 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x Headphone/ Microphone combo audio jack HDMI 2 x USB 3.2 gen 2 Type-A 2 x Thunderbolt 4 (hỗ trợ truyền dữ liệu,Power Delivery,DisplayPort,HP Sleep and Charge) | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Poly Studio DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ | Thông tin Pin:: 3-cell Li-Po, 59.16 Wh | Hệ điều hành:: Windows 11 Home SL + Microsoft Office Home 2024 vĩnh viễn + Microsoft 365 Basic 1 năm | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313 mm - Rộng 218.5 mm - Dày 14.4 mm - 1.398 kg | Chất liệu:: Nhôm &amp; Nhựa</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-255h-21sx002yvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-omnibook-x-flip-14-kb0048tu-ultra-7-355-d72bypa</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:39:04</t>
+          <t>2026-09-17 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX005NVN (Ultra 5 225U, 16GB, 512GB, WUXGA, Win11)</t>
+          <t>Laptop HP ProBook 4 G1a 14 - D9CP7AT (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>36490000</v>
+        <v>30590000</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>38390000</v>
+        <v>31990000</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4 với USB Power Delivery và DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI 1 x USB Type-C (hỗ trợ cổng Thunderbolt 4) LAN (RJ45) 2 x USB 3.2 Gen 2 Type-C (hỗ trợ Power Delivery 3.0, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) | Webcam:: Camera HP FHD, tích hợp màn che và micro kép | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: fTPM 2.0 TPM Embedded Security Smart Cover Secure Platform Management (SPM) Secure Boot Configuration POST Power-On Password Microsoft Pluton Processor BIOS Sure Start AMD PSP 11.0 Device Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hard Drive Utilities | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 31.86 cm - Rộng 22.43 cm - Dày 1.70 cm - 1.465 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-225u-21sx005nvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-probook-4-g1a-14-r7-250-d9cp7at</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:39:18</t>
+          <t>2026-09-17 12:58:43</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo ThinkPad X9 14 Gen 1 - 21QA006JVN (Ultra 7 258V, 32GB, 512GB, WUXGA OLED, Win11Pro)</t>
+          <t>Laptop HP Probook 4 G1ah 16 - D9CP8AT (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>53790000</v>
+        <v>30590000</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>55190000</v>
+        <v>31990000</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.80 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140V | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Chống chói Anti Glare Dolby Vision 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm HDMI 2.1 2 x USB-C (hỗ trợ Thunderbolt 4/USB 4, USB Power Delivery và DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 11 Pro | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 311.8 mm - Rộng 212.3 mm - Dày 17.18 mm - 1.21 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon Graphics | Số nhân GPU:: Hãng không công bố | Công suất đồ hoạ - TGP:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (2280) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI 2 x USB 3.2 Gen 2 Type-C (hỗ trợ Power Delivery 3.0, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) | Webcam:: Camera HP FHD, tích hợp màn che và micro kép | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM Embedded Security Smart Cover Secure Platform Management (SPM) Secure Boot Configuration POST Power-On Password Microsoft Pluton Processor fTPM 2.0 BIOS Sure Start AMD PSP 11.0 Device Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hard Drive Utilities | Thông tin Pin:: 3-cell Li-Po, 56.04 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 35.94 cm - Rộng 25.1 cm - Dày 1.7 cm - 1.783 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-x9-14-gen-1-ultra-7-258v-21qa006jvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-probook-4-g1ah-16-r7-250-d9cp8at</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:39:32</t>
+          <t>2026-09-17 12:58:57</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo V14 G5 - 83HD0035VN (Core7 240H, 16G, 512GB, Full HD, Win11)</t>
+          <t>Laptop HP ProBook 4 G2i 16 - DK2X9AT (Ultra 5 325, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>31290000</v>
+        <v>35190000</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>32690000</v>
+        <v>36590000</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
@@ -2560,389 +2572,389 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 7 Raptor Lake - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.50 GHz (Lên đến 5.20 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A HDMI 1.4b 1 x USB 3.2 Gen 1 Type-C (hỗ trợ Power Delivery, DisplayPort 1.2) LAN (RJ45) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-Ion, 47 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 324.2 mm - Rộng 215.2 mm - Dày 17.9 mm - 1.37 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 325 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell, 68.03 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.4 mm - Rộng 251 mm - Dày 17.5 mm - 1.848 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-v14-g5-core7-240h-83hd0035vn</t>
+          <t>https://www.thegioididong.com/laptop/hp-probook-4-g2i-16-ultra-5-325-dk2x9at</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:39:45</t>
+          <t>2026-09-17 12:59:11</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002LVN (Ultra 5 322, 16GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop HP ProBook 4 G2i 16 - DK2Y5AT (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>38490000</v>
+        <v>39190000</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>44990000</v>
+        <v>40590000</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Panther Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 46 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.45 mm - 1.38 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.30 GHz (Lên đến 4.70 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 62.5% sRGB | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort, Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Poly Studio Realtek High Definition Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell, 68.03 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.4 mm - Rộng 251 mm - Dày 17.5 mm - 1.846 kg | Chất liệu:: Nhựa &amp; Kim loại</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-5-322-83tc002lvn</t>
+          <t>https://www.thegioididong.com/laptop/hp-probook-4-g2i-16-ultra-7-355-dk2y5at</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:39:59</t>
+          <t>2026-09-17 12:59:25</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga 7 2in1 14IPH11 - 83TC002MVN (Ultra 7 355, 32GB, 512GB, WUXGA OLED, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo Gaming Legion 5 15AHP11 - 83Q7001HVN (R7 250, 16GB, 512GB, RTX 5050 8GB, WQXGA OLED 165Hz, OfficeH24, Win11)</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>55990000</v>
+        <v>52990000</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>64990000</v>
+        <v>56990000</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Low Blue Light Anti-fingerprint Dolby Vision 400 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x Thunderbolt 4 (hỗ trợ Power Delivery, DisplayPort 2.1) 1 x USB A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Webcam 5.0 MP + IR Camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Realtek Audio Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Màn hình gập 360 độ Độ bền chuẩn quân đội MIL STD 810H Tiêu chuẩn Nền Intel Evo | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 317 mm - Rộng 228 mm - Dày 15.95 mm - 1.4 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | NPU:: AMD XDNA | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | Card màn hình:: NVIDIA GeForce RTX 5050, 8 GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: Boost Clock 2662MHz, TGP 115W, 440 AI TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe 16 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 15.3" | Độ phân giải:: 2.5K | Tấm nền:: OLED | Tần số quét:: 165 Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: DisplayHDR True Black 1000 | Cổng giao tiếp:: 1x Ethernet 2 x USB Type-C (USB4 40Gbps) hỗ trợ USB PD 65 - 100W và DisplayPort 1.4 1 x Headphone/ Microphone combo audio jack HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) 2×2 Bluetooth 6.0 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Đèn chuyển màu RGB - 1 vùng | Công nghệ âm thanh:: Realtek ALC3287 High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 80 Wh | Hệ điều hành:: Windows 11 Home SL + Office Home 2024 | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 244.5 mm - Rộng 344 mm - Dày 19~20 - 1.87 kg | Chất liệu:: Mặt trên: nhôm + Mặt dưới: nhựa PC-ABS</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-7-2in1-14iph11-ultra-7-355-83tc002mvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-gaming-legion-5-15ahp11-r7-250-83q7001hvn</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:40:13</t>
+          <t>2026-09-17 12:59:39</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 - 83QM0075VN (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002NVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>40990000</v>
+        <v>22990000</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>46990000</v>
+        <v>29990000</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-23%</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Eyesafe 600nits (peak) Dolby Vision 400 nits X-Rite Flicker Free | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 70 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 04/2026 | Kích thước:: Dài 221 mm - Rộng 312 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Khung &amp; Mặt lưng hợp kim nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-14iph11-ultra-7-355-83qm0075vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002nvn</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:40:30</t>
+          <t>2026-09-17 12:59:53</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 - 83QM0076VN (Ultra 7 355, 16GB, 512GB, WUXGA, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 - 83RQ002PVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>40990000</v>
+        <v>18990000</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>46990000</v>
+        <v>25990000</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-27%</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.00 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Khoảng 13 TOPS (NPU); tổng nền tảng AI của Intel đạt khoảng 99 TOPS (CPU + GPU + NPU) | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: 4 Xe-Cores | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 7467 MT/s | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB PCIe 4.0 NVMe SSD | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: OLED Chuẩn DisplayHDR True Black 600 Low Blue Light Eyesafe Dolby Vision | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB-A (hỗ trợ USB 3.2 Gen 1) 2 x Thunderbolt 4 USB-C HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Chốt khóa webcam FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: Dolby Atmos | Tản nhiệt:: Hệ thống quạt kép (Dual Fan) | Tính năng khác:: TPM 2.0 | Thông tin Pin:: 70 Wh | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 221 mm - Rộng 312 mm - Dày 13.9 mm - 1.14 kg | Chất liệu:: Vỏ hợp kim Nhôm</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 PCle Gen 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 314.4 mm - Rộng 222.1 mm - Dày 16.9 - 17.9 - 1.39 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-14iph11-ultra-7-355-83qm0076vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-14iwc11-core-5-320-83rq002pvn</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:40:43</t>
+          <t>2026-09-17 13:00:06</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK0015VN (Ultra 7 355, 32GB, 1TB, WQXGA+ 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00A8VN (Core 3 304, 8GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>62990000</v>
+        <v>17490000</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>72990000</v>
+        <v>23990000</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-27%</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe 4.0x4 NVMe (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: 500 nits | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.6 mm - Rộng 213.8 mm - Dày 13.9 mm - 0.975 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
+          <t>Công nghệ CPU:: Intel Core™ 3 - 304 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz (P-core), Turbo tối đa 4.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 2242 PCIe 4.0x4 NVMe | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 × USB-C (USB 5 Gbps), hỗ trợ USB PD 45–65W và DisplayPort 1.2 1 x Headphone/ Microphone combo audio jack HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: SD Card Reader | Webcam:: HD 720p with Privacy Shutter | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Optimized with Dolby Audio 2W x 2 High Definition (HD) Audio Stereo speakers | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 240 mm - Rộng 343 mm - Dày 17 - 18 - 1.59 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-7-355-83qk0015vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-3-304-83rr00a8vn</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:40:58</t>
+          <t>2026-09-17 13:00:19</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK006GVN (Ultra 7 355, 32GB, 1TB, WQXGA+ 120Hz, Cảm ứng, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 15IWC11 - 83RR00AAVN (Core 5 320, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>64990000</v>
+        <v>22990000</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>66990000</v>
+        <v>29990000</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-23%</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Integrated Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe 4.0x4 NVMe (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Eyesafe DisplayHDR True Black 1000 500 nits Corning Gorilla Glass 3 Dolby Vision PureSight Pro Flicker Free 1100 nits (peak) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Webcam:: Camera 5.0 MP | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.6 mm - Rộng 213.8 mm - Dày 13.9 mm - 0.975 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-7-355-83qk006gvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00aavn</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:41:11</t>
+          <t>2026-09-17 13:00:32</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 - 83QK009PVN (Ultra X9 378H, 32GB, 1TB, WQXGA+ 120Hz, OfficeH24+365, Win11)</t>
+          <t>Laptop Lenovo Ideapad Slim 3 15IWC11 - 83RR00CVVN (Core 5 320, 8GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>68990000</v>
+        <v>19190000</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>79990000</v>
+        <v>25990000</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra X9 - 378H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.00 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 32 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 9600 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 2242 PCIe® 4.0x4 NVMe® (có thể tháo ra, nâng cấp tối đa 2TB/khe) | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) POLED | Tấm nền:: POLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% sRGB 100% DCI-P3 | Công nghệ màn hình:: Eyesafe 500 nits typical DisplayHDR True Black 1000 Corning Gorilla Glass 3 500 nits Glossy Dolby Vision PureSight Pro Flicker Free 1100 nits (peak) | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 3 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 2.1) | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Hãng không công bố | Webcam:: 5.0 MP with E-shutter | Đèn bàn phím:: Có | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: 2 x loa woofers 2W và 2 x loa tweeters 2W Smart Amplifier Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 75 Wh | Hệ điều hành:: Windows 11 Home + Office Home 2024 + Microsoft 365 Basic | Thời điểm ra mắt:: 18/05/2026 | Kích thước:: Dài 213.8 mm - Rộng 312.6 mm - Dày 13.9 mm - 0.975 kg</t>
+          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.6 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe trống) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) | Kích thước màn hình:: 15.3" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: HD 720p | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 50 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 343.4 mm - Rộng 239.5 mm - Dày 17.9 mm - 1.59 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/lenovo-yoga-slim-7-ultra-14iph11-ultra-x9-378h-83qk009pvn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-15iwc11-core-5-320-83rr00cvvn</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:41:26</t>
+          <t>2026-09-17 13:00:46</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 Black Edition A13VEO - 2610VN (i5 13420H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US0040VN (Ultra 5 322, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>27890000</v>
+        <v>23690000</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>31990000</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell, 53.5Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 250.3 mm - Dày 22.9 mm - 1,.98 | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 322 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: Lên đến 4.40 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD NVMe M.2 PCIe | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare Low Blue Light | Cổng giao tiếp:: 2 x USB-A (USB 5Gbps) 1 x USB-C (USB 5Gbps), with USB PD 45-65W and DisplayPort 1.2 1x Headphone / microphone combo jack (3.5 mm) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 18 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-black-edition-a13veo-i5-13420h-2610vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-5-322-83us0040vn</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:41:39</t>
+          <t>2026-09-17 13:00:59</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 Black Edition A13VEO - 2608VN (i7 13620H, 16GB, 512GB, RTX 4050 6GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16IPH11 - 83US003YVN (Ultra 7 355, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>29890000</v>
+        <v>28990000</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>33990000</v>
+        <v>36990000</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2952,40 +2964,40 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 1.8 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 4050, 6 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 45 W | Hiệu năng xử lý AI (TOPS):: Lên đến 194 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu xanh | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell, 53.5Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 250.3 mm - Dày 22.9 mm - 1,.98 | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB ) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 360 mm - Rộng 251 mm - Dày 17.9 mm - 1.73 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-black-edition-a13veo-i7-13620h-2608vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-3-16iph11-ultra-7-355-83us003yvn</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:41:53</t>
+          <t>2026-09-17 13:01:14</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 C13WEO - 418VN (i5 13420H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14IPH11 - 83S5004FVN (Ultra 7 355, 16GB, 512GB, WUXGA OLED, Win11)</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>30990000</v>
+        <v>34990000</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>34990000</v>
+        <v>37990000</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2995,270 +3007,270 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.5 GHz | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 70 W | Hiệu năng xử lý AI (TOPS):: Lên đến 440 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4.0 | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort và Power Delivery) HDMI 1 x Headphone/microphone combo LAN (RJ45) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Realtek High Definition Audio | Tản nhiệt:: Cooler Boost | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 1.982 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Panther Lake - 355 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 4.70 GHz khi tải nặng | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 49 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chuẩn DisplayHDR True Black 500 Low Blue Light 400 nits Flicker Free | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (hỗ trợ Power Delivery và DisplayPort 1.2) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.4 mm - Rộng 222 mm - Dày 16.9 mm - 1.37 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-c13weo-i5-13420h-418vn</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-ideapad-slim-5-14iph11-ultra-7-355-83s5004fvn</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:42:06</t>
+          <t>2026-09-17 13:01:29</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 Max C13WE - 422VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Lenovo ThinkBook 14 G9 - 21V0005PVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>41590000</v>
+        <v>33390000</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>42990000</v>
+        <v>35290000</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 5050, 8 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x SuperSpeed USB Type-A LAN (RJ45) HDMI 2.1 2 x USB 3.2 1 x USB Type-C 3.2 (hỗ trợ Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: 3 ống đồng Cooler Boost 2 quạt | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 2 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: AMD XDNA 2 | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Mặt lưng nhôm - Mặt dưới nhựa</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-max-c13we-422vn-i7-13620h</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-g9-r7-250-21v0005pvn</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:42:19</t>
+          <t>2026-09-17 13:01:43</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Cyborg 15 Max C13WF - 421VN (i7 13620H, 16GB, 512GB, RTX 5060 8GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Lenovo ThinkBook 14 Gen 9 IRL - 21UY008TVN (i5 13420H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>43590000</v>
+        <v>28690000</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>44990000</v>
+        <v>32890000</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 4.90 GHz khi tải nặng | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 3328 CUDA Cores | Công suất đồ hoạ - TGP:: 100 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB (2280)) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x SuperSpeed USB Type-A LAN (RJ45) HDMI 2.1 2 x USB 3.2 1 x USB Type-C 3.2 (hỗ trợ Power Delivery và DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: 3 ống đồng Cooler Boost 2 quạt | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359 mm - Rộng 249 mm - Dày 22.9 mm - 2 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core i5 Raptor Lake - 13420H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: Lên đến 4.60 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 1 x USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.5 mm - Rộng 224 mm - Dày 17.5 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-cyborg-15-max-c13wf-421vn-i7-13620h</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-14-gen-9-irl-i5-13420h-21uy008tvn</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:42:32</t>
+          <t>2026-09-17 13:01:57</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Gaming Cyborg 15 C13WEO-417VN (i7 13620H, 16GB, 512GB, RTX 5050 8GB, Full HD 144Hz, Win11)</t>
+          <t>Laptop Lenovo ThinkBook 16 G9 - 21UT005MVN (R7 250, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>34590000</v>
+        <v>30190000</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>36990000</v>
+        <v>31590000</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i7 Raptor Lake - 13620H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: 2.40 GHz (Lên đến 4.90 GHz khi tải nặng) | Card màn hình:: Card rời - Intel UHD Graphics (tích hợp) + NVIDIA GeForce RTX 5050 GPU, 8GB - GDDR7 | Số nhân GPU:: 2560 CUDA Cores | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: 512 GB SSD | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Hãng không công bố | Cổng giao tiếp:: 2 x USB Type-A 1 x Headphone/ Microphone combo audio jack 1 x USB Type C (chỉ hỗ trợ Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: DTS Audio | Tản nhiệt:: Cooler Boost | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 60 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.98 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: AMD Ryzen 7 - 250 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 3.30 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - AMD Radeon 780M Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 400 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 2 x USB Type-A 2 x USB-C (USB4 hỗ trợ DisplayPort™ 1.4a và Power Delivery) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 5.4 | Khe đọc thẻ nhớ:: SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Realtek Audio High Definition (HD) Audio Dolby Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356 mm - Rộng 253.5 mm - Dày 17.5 mm - 1.7 kg | Chất liệu:: Vỏ nhựa - Nắp lưng bằng nhôm</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-gaming-cyborg-15-c13weo-417vn-i7-13620h</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkbook-16-g9-r7-250-21ut005mvn</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:42:46</t>
+          <t>2026-09-17 13:02:10</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14S G3MG-003VN (Core 5 320, 16GB, 1TB, Full HD+ 120Hz, Win11)</t>
+          <t>Laptop Lenovo ThinkPad E14 - 21T90025VN (Gen 7 Core 7 240H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>27990000</v>
+        <v>34190000</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>31490000</v>
+        <v>35590000</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Wildcat Lake - 320 | Số nhân:: 6 | Số luồng:: 6 | Tốc độ CPU:: 1.5 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 16 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: SSD 1TB, chuẩn M.2 2280 NVMe PCIe Gen4, tối đa hỗ trợ 2TB | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 50% NTSC | Công nghệ màn hình:: Chống chói Anti Glare | Cổng giao tiếp:: 1 x Headset (Headphone and microphone combo) 2 x USB 3.2 gen 1 Type-A LAN (RJ45) HDMI 2.1 2 x USB Type-C 3.2 Gen 2 (hỗ trợ Power Delivery, DisplayPort) | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD card reader | Webcam:: HD 720p | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: DTS | Tản nhiệt:: 2 ống đồng 1 x Quạt | Tính năng khác:: Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion - 42 WHrs | Hệ điều hành:: Windows 11 Home | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 22.39 mm - Rộng 31.59 mm - Dày 1.11 ~ 1.79 - 1.45 kg | Chất liệu:: Khung kim loại - Mặt lưng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core 7 - 240H | Số nhân:: 10 | Số luồng:: 16 | Tốc độ CPU:: P-core 2.5/ 5.2 GHz, E-core 1.8/ 4.0 GHz | Card màn hình:: Card tích hợp - Integrated Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 16 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Anti-Glare 300 nits | Cổng giao tiếp:: 1x USB-A (USB 10Gbps / USB 3.2 Gen 2), Always On 1x Headphone / microphone combo jack (3.5 mm) 1x USB-C® (Thunderbolt™ 4 / USB4® 40 Gbps), with USB PD 15-65W and DisplayPort™ 2.1 1x HDMI® 2.1, up to 4K/6 0Hz 1x Ethernet (RJ-45) 1x USB-A (USB 5 Gbps / USB 3.2 Gen 1) | Kết nối không dây:: Wi-Fi 6E AX211 Bluetooth 5.3 | Webcam:: FHD 1080p + IR Hybrid with Privacy Shutter | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Stereo speakers, 2W x2, Dolby Atmos®, audio by HARMAN 2x, Array | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ Discrete TPM 2.0 Enabled | Thông tin Pin:: 3-cell, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 04/2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 10.1/15.25 (front/rear), 19.7 (maximum) mm - 1.34 kg | Chất liệu:: Vỏ kim loại</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-modern-14s-g3mg-003vn-core-5-320</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-core-7-240h-21t90025vn</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:43:00</t>
+          <t>2026-09-17 13:02:24</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1264VN (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Lenovo ThinkPad E14 - 21SX002YVN (Gen 7 Ultra 255H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>19990000</v>
+        <v>39190000</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>22390000</v>
+        <v>40590000</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core thế hệ 12 - 120U | Số nhân:: Hãng không công bố | Số luồng:: 12 | Tốc độ CPU:: 1.45 GHz | Card màn hình:: Card tích hợp | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 8 GB + 1 khe 8 GB) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD PCIe M.2 (2280) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: Hãng không công bố | Độ phủ màu:: Hãng không công bố | Cổng giao tiếp:: 3 x USB 3.2 Gen 1 Type-A 1 x USB 3.2 Gen 2 Type-C 1 x Headphone/ Microphone combo audio jack HDMI LAN (RJ45) | Kết nối không dây:: Wi-Fi 6 Bluetooth 5.3 + LE | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Hãng không công bố | Công nghệ âm thanh:: Hi-Res Audio | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Hãng không công bố | Thông tin Pin:: 3-cell, 46.8 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: 1.7 kg | Chất liệu:: Plastic (nhựa dẻo)</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: Lên đến 5.10 GHz khi tải nặng | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 140T | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 (Có thể tháo ra, lắp thanh khác tối đa 1 TB (2242) / 1 TB (2280)) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: 1x USB-A (USB 10Gbps / USB 3.2 Gen 2), Always On 1x HDMI® 2.1, up to 4K/60 Hz 1x Headphone / microphone combo jack (3.5 mm) 1x USB-C® (Thunderbolt™ 4 / USB4® 40 Gbps), with USB PD 15-65W and DisplayPort™ 2.1 1x Ethernet (RJ-45) 1x USB-A (USB 5 Gbps / USB 3.2 Gen 1) | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD 1080p + IR Hybrid with Privacy Shutter | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Stereo speakers, 2W x2, Dolby Atmos®, audio by HARMAN 2x, Array | Tản nhiệt:: Hãng không công bố | Tính năng khác:: TPM 2.0 Nút bật/tắt camera Độ bền chuẩn quân đội MIL STD 810H Bản lề mở 180 độ | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 04/2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 10.1/15.25 (front/rear), 19.7 (maximum) mm - 1.34 kg | Chất liệu:: Vỏ kim loại - Nhôm</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/msi-modern-15-f1mg-1264vn-core-5-120u</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-255h-21sx002yvn</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:43:16</t>
+          <t>2026-09-17 13:02:39</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Laptop SingPC M16-i382 (i3 1215U, 8GB, 256GB, WUXGA, Win11 Pro)</t>
+          <t>Laptop Lenovo ThinkPad E14 Gen 7 - 21SX005NVN (Ultra 5 225U, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>13490000</v>
+        <v>36490000</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>15190000</v>
+        <v>38390000</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i3 Alder Lake - 1215U | Số nhân:: 6 | Số luồng:: 8 | Tốc độ CPU:: 1.2GHz | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 256 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: Hãng không công bố | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225U | Số nhân:: 12 | Số luồng:: 14 | Tốc độ CPU:: 1.50 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 12 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 Opal 2 (Có thể tháo ra, lắp thanh khác tối đa 1 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe Gen 4 mở rộng (nâng cấp tối đa 1 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB-C (hỗ trợ Thunderbolt 4 / USB4 với USB Power Delivery và DisplayPort 2.1) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: TPM 2.0 Nhận diện khuôn mặt (FaceID) Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Audio by HARMAN Dolby Atmos | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 48 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 313 mm - Rộng 220.3 mm - Dày 19.7 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/singpc-m16-i382-i3-1215u</t>
+          <t>https://www.thegioididong.com/laptop/lenovo-thinkpad-e14-gen-7-ultra-5-225u-21sx005nvn</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3268,61 +3280,61 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:43:29</t>
+          <t>2026-09-17 13:02:53</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Laptop SingPC M16-i595 (i5 1235U, 16GB, 512GB, WUXGA, Win11 Pro)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP - U716S8W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>17390000</v>
+        <v>32990000</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>19990000</v>
+        <v>34990000</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200.000Đ (đã giảm vào giá sản phẩm) - Adapter chuyển đổi Type C 4 in 1 Xmobile DS606H | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core i5 Alder Lake - 1235U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: 1.30 GHz (Lên đến 4.40 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 PCIe/SATA (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 72% sRGB | Công nghệ màn hình:: Chống chói Anti Glare 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc - Màu trắng | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Intel Smart Sound Technology | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 50 Wh | Hệ điều hành:: Windows 11 Pro | Kích thước:: Dài 314 mm - Rộng 218 mm - Dày 15 mm - 1.1 kg | Chất liệu:: Vỏ bằng kim loại - Chiếu nghỉ tay bằng nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: 300 nits | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (hỗ trợ DisplayPort 1.4 và Power Delivery) 2 x USB 3.2 gen 1 Type-A 1 x Thunderbolt 4 with USB Type-C (hỗ trợ USB Power Delivery, DisplayPort 1.4) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.4 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Built-in speaker Built-in array microphone | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 430 mm - Rộng 316 mm - Dày 19.9 mm - 2.61 kg | Chất liệu:: Khung và mặt lưng nhựa</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/singpc-m16-i595-i5-1235u</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-p3-p3406ccap-ultra-7-255h-u716s8w</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:43:42</t>
+          <t>2026-09-17 13:30:02</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-977M - NX.W26SV.001 (Ultra 9 185H, 16GB, 512GB, Full HD+, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA - NZ1368W (Ultra 5 226V, 16GB, 512GB, WQXGA 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>29990000</v>
+        <v>30090000</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>31990000</v>
@@ -3334,1522 +3346,1510 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 9 Meteor Lake - 185H | Số luồng:: 22 | Tốc độ CPU:: 2.30 GHz (Lên đến 5.10 GHz khi tải nặng) | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (1 khe onboard) | Tốc độ Bus RAM:: 6400 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD+ | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 100% sRGB | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB Type-C (65W) 1 x USB Type-C LAN (RJ45) HDMI 2.1 USB Type-C | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD webcam | Đèn bàn phím:: Có | Bảo mật:: Công tắc khoá camera | Công nghệ âm thanh:: Stereo speakers | Tản nhiệt:: 1 x Quạt | Thông tin Pin:: 3-cell Li-ion, 55 Wh | Hệ điều hành:: Windows 10 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 313.6 mm - Rộng 227.7 mm - Dày 17.9 mm - 1.49 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Lunar Lake - 226V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 40 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics 130V | Số nhân GPU:: Hãng không công bố | RAM:: 16 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Anti-Glare Màn hình Wide View 400 nits | Cổng giao tiếp:: 2 x Thunderbolt 4 1 x 3.5mm combo audio jack HDMI 2 x USB 3.2 gen 2 Type-A | Kết nối không dây:: Hãng không công bố | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Smart Amp Technology Built-in array microphone Dolby Atmos | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 223 mm - Dày 12.8 ~ 16.4 mm - 1.2 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-go-14-ai-ag14-i71m-977m-ultra-9-185h-nx-w26sv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-p5-p5405csa-ultra-5-226v-nz1368w</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49:12</t>
+          <t>2026-09-17 13:30:17</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR - NX.X0PSV.002 (Ryzen 5 3500U, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA - NZ1371W (Ultra 7 258V, 32GB, 512GB, WQXGA 144Hz, Win11)</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>17990000</v>
+        <v>37490000</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>20990000</v>
+        <v>39490000</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 3500U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz | Card màn hình:: Card tích hợp - AMD Radeon Vega Mobile Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 2400 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: IPS LED-backlit TFT LCD Wide viewing angle 250 nits | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A HDMI 1 x SuperSpeed USB Type-C (hỗ trợ DisplayPort 1.4) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP FHD 1080p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: 2 loa 2 microphones | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Phím Copilot | Thông tin Pin:: 2-cell Li-ion, 45.6 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 210.2 mm - Rộng 322.6 mm - Dày 19.8 mm - 1.3 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Lunar Lake - 258V | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: 2.20 GHz (Lên đến 4.80 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 47 TOPS | Card màn hình:: Intel Arc 140V | Số nhân GPU:: Hãng không công bố | RAM:: 32 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: Anti-Glare Màn hình Wide View 400 nits | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 Type-A 1 x Thunderbolt 4 (hỗ trợ DisplayPort) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Đèn chuyển màu RGB | Bảo mật:: Bảo mật vân tay | Công nghệ âm thanh:: Smart Amp Technology Built-in array microphone Dolby Atmos | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 3-cell Li-ion, 42 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312 mm - Rộng 223 mm - Dày 12.8 ~ 16.4 mm - 1.2 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-nx-x0psv-002</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-p5-p5405csa-ultra-7-258v-nz1371w</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49:26</t>
+          <t>2026-09-17 13:30:31</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN - NX.DDASV.001 (Core 3 N350, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Asus ExpertBook Ultra B9 B9406CAA - X7642TW (Ultra X7 358H, 64GB, 2TB, WQXGA+ OLED 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>16990000</v>
+        <v>97990000</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>18990000</v>
+        <v>100000000</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 200,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 500,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 250.000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 3 Twin Lake - N350 | Số nhân:: 8 | Số luồng:: 8 | Tốc độ CPU:: Lên đến 3.90 GHz khi tải nặng | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB 3.2 HDMI 1.4 | Kết nối không dây:: Wi-Fi 5(802.11ac) Bluetooth 5.0 | Webcam:: HD webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 45 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 357.8 mm - Rộng 235.6 mm - Dày 19.7 mm - 1.53 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra X7 Panther Lake | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 64 GB | Loại RAM:: LPDDR5X | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 2 TB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 1 x USB Type-C (hỗ trợ cổng Thunderbolt 4) HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) | Webcam:: FHD 1080P + IR Camera for Windows Hello | Đèn bàn phím:: Có | Công nghệ âm thanh:: Built-in speaker Built-in array microphone Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 28.8 mm - Rộng 12.7 mm - Dày 38.9 mm - 1.131 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-36p-30tn-core-3-n350-nx-ddasv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-b9-b9406caa-ultra-x7-358h-x7642tw</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49:39</t>
+          <t>2026-09-17 13:30:45</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 - NX.X0RSV.001 (Ryzen 5 3500U, 8GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Asus ExpertBook Ultra B9 B9406CAA - X7321TW (Ultra X7 358H, 32GB, 1TB, WQXGA+ OLED 120Hz, Win11)</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>17990000</v>
+        <v>65990000</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>20990000</v>
+        <v>68000000</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 5 - 3500U | Số nhân:: 4 | Số luồng:: 8 | Tốc độ CPU:: 2.10 GHz | Card màn hình:: Card tích hợp - AMD Radeon Vega Mobile Graphics | RAM:: 8 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 2400 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe (nâng cấp tối đa 2TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: IPS Màn hình Wide View Acer ComfyView 250 nits | Cổng giao tiếp:: 1 x USB 2.0 2 x USB 3.2 gen 1 Type-A HDMI 1 x SuperSpeed USB Type-C (hỗ trợ DisplayPort 1.4) | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 802.11 a/b/g/n/ac/ax | Khe đọc thẻ nhớ:: Micro SD | Webcam:: 2 MP FHD 1080p | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: 2 loa 2 microphones | Tản nhiệt:: 1 x Quạt | Tính năng khác:: Phím Copilot | Thông tin Pin:: 2-cell Li-ion, 45.6 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 229.3 mm - Rộng 357.4 mm - Dày 19.85 mm - 1.5 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra X7 Panther Lake - 358H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 1.9 GHz | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 50 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 32 GB | Loại RAM:: LPDDR5X (Onboard) | Tốc độ Bus RAM:: 8533 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: 1 TB SSD M.2 NVMe PCIe 4.0 | Kích thước màn hình:: 14" | Độ phân giải:: WQXGA+ (2880 x 1800) OLED | Tấm nền:: OLED | Tần số quét:: 120Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Chống chói Anti Glare 600 nits Pantone Validated | Màn hình cảm ứng:: Cảm ứng | Cổng giao tiếp:: 2 x Thunderbolt 4 1 x 3.5mm combo audio jack 2 x USB 3.2 gen 2 Type-A HDMI 2.1 | Kết nối không dây:: Wi-Fi 7 (802.11be) Bluetooth 6.0 | Webcam:: Full HD Webcam Camera IR | Đèn bàn phím:: Đơn sắc | Bảo mật:: Nhận diện khuôn mặt (FaceID) Bảo mật vân tay | Công nghệ âm thanh:: Built-in speaker Built-in array microphone Dolby Atmos | Tản nhiệt:: Hãng không công bố | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 310.9 mm - Dày 16.4 mm - 1.1 kg | Chất liệu:: Khung và mặt lưng hợp kim Nhôm Magie</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-nx-x0rsv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-b9-b9406caa-x7321tw-ultra-x7-358h-32gb-1tb-wqxga-oled-120hz-win11</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49:53</t>
+          <t>2026-09-17 13:30:58</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-44P-R4UH - NX.DJVSV.002 (R7 7730U, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0045W (Ultra 5 225H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>21990000</v>
+        <v>30990000</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>23990000</v>
+        <v>33990000</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen 7 - 7730U | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 4.50 GHz khi tải nặng) | Card màn hình:: Card tích hợp - AMD Radeon Graphics | RAM:: 16 GB | Loại RAM:: DDR4 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD NVMe PCIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 250 nits | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 1 x USB Type - C HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 359.3 mm - Rộng 230.2 mm - Dày 18.6 mm - 1.49 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 5 Arrow Lake - 225H | Số nhân:: 14 | Số luồng:: 14 | Tốc độ CPU:: 1.70 GHz (Lên đến 4.90 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display 300 nits | Cổng giao tiếp:: 2 x USB 3.2 gen 1 Type-A 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C HDMI 1.4 1 x USB Type-C with Thunderbolt 5 (hỗ trợ USB 4, DisplayPort 2.1 và Power Delivery 3.0) | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.34 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-44p-r4uh-r7-7730u-nx-djvsv-002</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-5-225h-sf0045w</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:50:06</t>
+          <t>2026-09-17 13:31:12</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC - NX.DG3SV.002.16G (Core 5 120U, 16GB, 512GB, Full HD, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0241W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>21990000</v>
+        <v>35990000</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>24990000</v>
+        <v>37990000</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây)</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 120U | Số nhân:: 10 | Số luồng:: 12 | Tốc độ CPU:: Hãng không công bố | Card màn hình:: Card tích hợp - Intel UHD Graphics | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 60Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle Acer ComfyView | Cổng giao tiếp:: Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 1 Type - C (hỗ trợ DisplayPort) 3 x USB 3.2 Gen 1 1 x USB 3.2 Gen 1 Type-C HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: Hãng không công bố | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 357.6 mm - Rộng 228.5 mm - Dày 18.7 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display Màn hình Wide View | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-15-al15-53p-56ec-core-5-120u-nx-dg3sv-002-16g</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-7-255-sf0241w</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:50:19</t>
+          <t>2026-09-17 13:31:26</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AL16-71P-582Q - NX.DRSSV.001 (Ultra 5 125H, 16GB, 512GB, Full HD+ 120Hz, Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5406CCA - SF0047W (Ultra 7 255H, 16GB, 512GB, WUXGA, Win11)</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>24990000</v>
+        <v>35990000</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>26990000</v>
+        <v>37990000</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 400,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 500.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 700,000đ | Tặng Balo Laptop Acer (Hết quà hoàn tiền 100.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 1,500,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 500.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core Ultra 5 Meteor Lake - 125H | Số nhân:: 14 | Số luồng:: 18 | Tốc độ CPU:: 1.20 GHz (Lên đến 4.50 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Lên đến 11 TOPS | Card màn hình:: Card tích hợp - Intel Arc Graphics | RAM:: 16 GB | Loại RAM:: LPDDR5 (Onboard) | Tốc độ Bus RAM:: 7467 MHz | Hỗ trợ RAM tối đa:: Không hỗ trợ nâng cấp | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe Gen 4.0 mở rộng (nâng cấp tối đa 4 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: Full HD+ (1920 x 1200) | Tấm nền:: IPS | Tần số quét:: 120Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD 300 nits Acer ComfyView | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 2 x USB 3.2 Gen 1 Type-C (hỗ trợ DisplayPort) HDMI 1.4 | Kết nối không dây:: Wi-Fi 6 (802.11ax) Bluetooth 5.1 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: Full HD Webcam | Đèn bàn phím:: Không có đèn | Bảo mật:: TPM 2.0 Công tắc khoá camera | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 58 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 357 mm - Rộng 245.5 mm - Dày 18.9 mm - 1.6 kg | Chất liệu:: Vỏ nhựa</t>
+          <t>Công nghệ CPU:: Intel Core Ultra 7 Arrow Lake - 255H | Số nhân:: 16 | Số luồng:: 16 | Tốc độ CPU:: 2.00 GHz (Lên đến 5.10 GHz khi tải nặng) | NPU:: Intel AI Boost | Hiệu năng xử lý AI (TOPS):: Max 13 TOPS | Card màn hình:: Card tích hợp - Intel Graphics | RAM:: 16 GB | Loại RAM:: DDR5 | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe | Kích thước màn hình:: 14" | Độ phân giải:: WUXGA (1920 x 1200) - OLED | Tấm nền:: OLED | Tần số quét:: 60Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: Glossy Display Màn hình Wide View | Cổng giao tiếp:: 1 x 3.5mm combo audio jack 1 x USB 3.2 Gen 2 Type-C LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Hãng không công bố | Webcam:: Full HD Webcam | Đèn bàn phím:: Đơn sắc | Bảo mật:: TPM 2.0 Công tắc khoá camera Bảo mật vân tay | Công nghệ âm thanh:: Công nghệ Smart AMP | Tính năng khác:: Độ bền chuẩn quân đội MIL STD 810H | Thông tin Pin:: 4-cell Li-ion, 70 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 312.7 mm - Rộng 227.1 mm - Dày 17.9 mm - 1.36 kg | Chất liệu:: Vỏ nhôm</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-aspire-lite-16-al16-71p-582q-ultra-5-125h-nx-drssv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-expertbook-ultra-p5-p5406cca-ultra-7-255h-sf0047w</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:50:33</t>
+          <t>2026-09-17 13:31:41</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Aspire 7 A715-59G-59RD - NH.DXUSV.001 (Core 5 210H, 16GB, 512GB, RTX 3050 4GB, Fulll HD 144Hz, Win11)</t>
+          <t>Laptop Asus Gaming ROG Strix G16 G614PM - TS147W (R9 8940HX, 16GB, 512GB, RTX 5060 8GB, WQXGA 300Hz, Win11)</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>26990000</v>
+        <v>54990000</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>31990000</v>
+        <v>57990000</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: Intel Core 5 Raptor Lake - 210H | Số nhân:: 8 | Số luồng:: 12 | Tốc độ CPU:: 1.60 GHz (Lên đến 4.80 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 3050, 4 GB | Số nhân GPU:: 2560 CUDA Cores | Công suất đồ hoạ - TGP:: 35W - 80W | Hiệu năng xử lý AI (TOPS):: Lên đến 80 TOPS | RAM:: 16 GB | Loại RAM:: DDR4 | Tốc độ Bus RAM:: 3200 MHz | Hỗ trợ RAM tối đa:: 32 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 4 TB) | Kích thước màn hình:: 15.6" | Độ phân giải:: Full HD (1920 x 1080) | Tấm nền:: IPS | Tần số quét:: 144Hz | Độ phủ màu:: 45% NTSC | Công nghệ màn hình:: LED-backlit TFT LCD Wide viewing angle 350 nits Acer ComfyView | Cổng giao tiếp:: 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB-A (hỗ trợ USB 3.2 Gen 1) 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C (hỗ trợ DisplayPort 1.4) LAN (RJ45) HDMI 1.4 | Kết nối không dây:: Bluetooth 5.2 Wi-Fi 6 (802.11ax) | Khe đọc thẻ nhớ:: Micro SD | Webcam:: HD 720p | Đèn bàn phím:: Đơn LED - 15 chế độ màu | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: High Definition (HD) Audio | Tản nhiệt:: Hãng không công bố | Thông tin Pin:: 3-cell Li-ion, 54 Wh | Hệ điều hành:: Windows 11 Home SL | Kích thước:: Dài 359.5 mm - Rộng 238 mm - Dày 22.7 mm - 1.99 kg | Chất liệu:: Vỏ kim loại</t>
+          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5060, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115W - 140W | Hiệu năng xử lý AI (TOPS):: Lên đến 572 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.288 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-aspire-7-a715-59g-59rd-core-5-210h-nh-dxusv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pm-r9-8940hx-ts147w</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:50:46</t>
+          <t>2026-09-17 13:31:55</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel AN16S-61-R9CN - NH.QXGSV.001 (Ryzen AI 7 350, 16GB, 512GB, RTX 5070 8GB, 2K+ 180Hz, Win11)</t>
+          <t>Laptop Asus Gaming ROG Strix G16 G614PR - TS103W (R9 8940HX, 16GB, 512GB, RTX 5070Ti 12GB, WQXGA 300Hz, Win11)</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>57990000</v>
+        <v>70590000</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>64990000</v>
+        <v>71990000</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ | Balo Acer Predator Gaming (Hết quà hoàn tiền 450.000₫) | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Phiếu mua hàng máy lọc nước trị giá 300.000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
+          <t>Chọn 1 trong các khuyến mãi: - Giảm ngay 700,000đ (đã giảm vào giá sản phẩm) - Tặng Microsoft 365 Personal | Chọn 1 trong các khuyến mãi: - Giảm 700,000Đ (đã giảm vào giá sản phẩm) - Phiếu mua hàng mua Màn hình, Máy in trị giá 1,000,000đ - Phiếu mua hàng Phụ Kiện, Smartwatch, đồng hồ thời trang (trừ Apple, Beats) trị giá 900.000đ | Tặng PMH 100.000đ mua balo,túi chống sốc. | Tặng Phiếu mua hàng mua Bảo hành mở rộng Laptop 12 tháng trị giá 500,000đ | Thu cũ đổi mới: Giảm ngay 3,000,000Đ Xem chi tiết | Tặng 2 năm bảo vệ tai nạn ASUS PREMIUM CARE (Xem chi tiết) | NHẬN HOÀN NGAY ĐẾN 800.000đ khi mở thẻ tín dụng VPBANK MWG  (Xem chi tiết tại đây) | GIẢM THÊM 1.000.000₫ - Với HSSV (Từ THPT trở lên), Giáo viên, Giảng viên</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ CPU:: AMD Ryzen AI 7 - 350 | Số nhân:: 8 | Số luồng:: 16 | Tốc độ CPU:: 2.0 GHz (Lên đến 5.2 GHz khi tải nặng) | NPU:: Hãng không công bố | Hiệu năng xử lý AI (TOPS):: Lên đến 798 TOPS | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070, 8 GB | Số nhân GPU:: 4608 CUDA Cores | Công suất đồ hoạ - TGP:: 115 W | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5600 MHz | Hỗ trợ RAM tối đa:: 96 GB | Ổ cứng:: Hỗ trợ thêm 1 khe cắm SSD NVMe PCIe mở rộng (nâng cấp tối đa 2 TB) 512 GB SSD NVMe PCIe Gen 4 (Có thể tháo ra, lắp thanh khác tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: 2K+ (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 180 Hz | Độ phủ màu:: 100% sRGB | Công nghệ màn hình:: LED-backlit TFT LCD Acer ComfyView 400 nits 3ms | Cổng giao tiếp:: 2 x USB 3.2 1 x USB 2.0 Jack tai nghe 3.5 mm 1 x USB 3.2 Gen 2 Type-C (Hỗ trợ DisplayPort) 1 x USB Type-C USB 4 (hỗ trợ DisplayPort) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Khe đọc thẻ nhớ:: Micro SD | Webcam:: FHD Webcam, IR camera | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: Nhận diện khuôn mặt (FaceID) | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Windows Spatial Sound Acer Purified Voice Acer TrueHarmony DTS:X ULTRA | Tản nhiệt:: Hãng không công bố | Tính năng khác:: NVIDIA Optimus | Thông tin Pin:: 4-cell, 76Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2025 | Kích thước:: Dài 356.78 mm - Rộng 275.5 mm - Dày 19.9 mm - 2.18 kg | Chất liệu:: Vỏ nhôm</t>
+          <t>Công nghệ CPU:: AMD Ryzen 9 - 8940HX | Số nhân:: 16 | Số luồng:: 32 | Tốc độ CPU:: 2.40 GHz (Lên đến 5.30 GHz khi tải nặng) | Card màn hình:: Card rời - NVIDIA GeForce RTX 5070Ti, 12 GB | Số nhân GPU:: 5888 CUDA Cores | Công suất đồ hoạ - TGP:: 140 W | Hiệu năng xử lý AI (TOPS):: Lên đến 992 TOPS | RAM:: 16 GB | Loại RAM:: DDR5 (1 khe 16 GB + 1 khe rời) | Tốc độ Bus RAM:: 5200 MHz | Hỗ trợ RAM tối đa:: 64 GB | Ổ cứng:: 512 GB SSD M.2 NVMe PcIe (Có thể tháo ra, lắp thanh khác tối đa 2 TB) Hỗ trợ thêm 1 khe cắm SSD M.2 PCIe mở rộng (nâng cấp tối đa 2 TB) | Kích thước màn hình:: 16" | Độ phân giải:: WQXGA (2560 x 1600) | Tấm nền:: IPS | Tần số quét:: 300Hz | Độ phủ màu:: 100% DCI-P3 | Công nghệ màn hình:: ROG Nebula Display G-Sync 500 nits Chống chói Anti Glare Dolby Vision 3ms | Cổng giao tiếp:: 2 x USB 3.2 Jack tai nghe 3.5 mm 1 x USB4 Type-C (Hỗ trợ DisplayPort, G-SYNC) 1 x USB4 Type-C (Hỗ trợ DisplayPort, PowerDelivery, G-SYNC) LAN (RJ45) HDMI 2.1 | Kết nối không dây:: Wi-Fi 6E (802.11ax) Bluetooth 5.3 | Webcam:: Full HD Webcam | Đèn bàn phím:: Đèn chuyển màu RGB - 4 vùng | Bảo mật:: TPM 2.0 | Công nghệ âm thanh:: Hi-Res Audio AI noise-canceling technology Công nghệ Smart AMP Dolby Atmos | Tản nhiệt:: ROG intelligent cooling | Tính năng khác:: MUX Switch NVIDIA Optimus | Thông tin Pin:: 4-cell Li-ion, 90 Wh | Hệ điều hành:: Windows 11 Home SL | Thời điểm ra mắt:: 2026 | Kích thước:: Dài 354 mm - Rộng 264 mm - Dày 30.4 mm - 2.34 kg | Chất liệu:: Vỏ nhựa - nắp lưng bằng kim loại</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>https://www.thegioididong.com/laptop/acer-gaming-nitro-propanel-an16s-61-r9cn-ryzen-ai-7-350-nh-qxgsv-001</t>
+          <t>https://www.thegioididong.com/laptop/asus-gaming-rog-strix-g16-g614pr-r9-8940hx-ts103w</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:51:00</t>
+          <t>2026-09-17 13:32:09</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Laptop